--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>584.8264696096763</v>
+        <v>582.0892820026435</v>
       </c>
       <c r="E2" t="n">
-        <v>9128.524785008447</v>
+        <v>9150.25078041489</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6932398233303594</v>
+        <v>0.6823272344686637</v>
       </c>
       <c r="G2" t="n">
-        <v>0.500974987947604</v>
+        <v>0.5010303400220005</v>
       </c>
       <c r="H2" t="n">
-        <v>1.383781306468865</v>
+        <v>1.36184813566121</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.9727724008536</v>
+        <v>226.139229997864</v>
       </c>
       <c r="E3" t="n">
-        <v>4378.620045858894</v>
+        <v>4283.055621618795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2845921263933731</v>
+        <v>0.2777707369480507</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6016587268246919</v>
+        <v>0.6016912639730023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4730125463239495</v>
+        <v>0.4616499417224614</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890864318541067</v>
+        <v>0.8908723397746705</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069906291854682</v>
+        <v>1.0698555782751</v>
       </c>
     </row>
     <row r="4">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.74337530848683</v>
+        <v>38.68081534993758</v>
       </c>
       <c r="E4" t="n">
-        <v>1453.904753550612</v>
+        <v>1382.221078042828</v>
       </c>
       <c r="F4" t="n">
         <v>0.8813840784616267</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715440073326547</v>
+        <v>0.4715709654288769</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049635911666824</v>
+        <v>1.049579952462753</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.33156303389649</v>
+        <v>37.28520827369017</v>
       </c>
       <c r="E5" t="n">
-        <v>278.5250110075654</v>
+        <v>277.9989178071743</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3324848552584848</v>
+        <v>-0.3343719116955194</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652612541281787</v>
+        <v>0.5652610376131099</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5881967901219185</v>
+        <v>-0.5915353959428186</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368351260792592</v>
+        <v>0.7367959771319602</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313875093037939</v>
+        <v>0.8312511743789583</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.10479936656544</v>
+        <v>11.05887157107649</v>
       </c>
       <c r="E6" t="n">
-        <v>166.4650814239544</v>
+        <v>165.830068701925</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2860851484364303</v>
+        <v>-0.291946436895371</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7182898792026249</v>
+        <v>0.7183176283508197</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3982864811543969</v>
+        <v>-0.406430839746546</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750113481575155</v>
+        <v>0.7501433136000963</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075500643807052</v>
+        <v>1.075466140283611</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.08409805450783</v>
+        <v>10.02927837035685</v>
       </c>
       <c r="E7" t="n">
-        <v>282.0258487932642</v>
+        <v>282.2025805341664</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5425101175121356</v>
+        <v>-0.5455695723316265</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8084314356018473</v>
+        <v>0.808446913502758</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6710650942318404</v>
+        <v>-0.6748366073510469</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836866352250343</v>
+        <v>0.6836988096139641</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103276174088312</v>
+        <v>1.103195052765962</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.01367540041642</v>
+        <v>9.939379978128866</v>
       </c>
       <c r="E8" t="n">
-        <v>318.042074538424</v>
+        <v>308.9211929409744</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3143871648358488</v>
+        <v>-0.32084606024298</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174634813000957</v>
+        <v>1.174679133922121</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2676467284607822</v>
+        <v>-0.2731350638465088</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385649931053784</v>
+        <v>0.738584921270337</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731711509429936</v>
+        <v>1.731632251267817</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.465014498482249</v>
+        <v>7.426083538099675</v>
       </c>
       <c r="E9" t="n">
-        <v>244.5450674659975</v>
+        <v>242.4029270157577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.454796863559336</v>
+        <v>0.4447194670556871</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4825541611827975</v>
+        <v>0.4826514317434303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9424783788923816</v>
+        <v>0.921409194725217</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6775835877445416</v>
+        <v>0.6776762126541253</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6526688710644672</v>
+        <v>0.652817540513847</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.082377273124652</v>
+        <v>7.047105880203505</v>
       </c>
       <c r="E10" t="n">
-        <v>197.0452882012497</v>
+        <v>195.3838915772473</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2104741822665284</v>
+        <v>-0.2195853859849038</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9636329697385256</v>
+        <v>0.9636461423626788</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.218417373498168</v>
+        <v>-0.2278693146080799</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713216653540261</v>
+        <v>0.7132460481485489</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371883025006142</v>
+        <v>1.371806750911719</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.842441081035861</v>
+        <v>6.793051534111196</v>
       </c>
       <c r="E11" t="n">
-        <v>358.1456262672045</v>
+        <v>351.4094424218786</v>
       </c>
       <c r="F11" t="n">
-        <v>1.058212667658736</v>
+        <v>1.036097714060763</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8257247333972585</v>
+        <v>0.8258220883500882</v>
       </c>
       <c r="H11" t="n">
-        <v>1.281556219473963</v>
+        <v>1.254625819140761</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627385310318218</v>
+        <v>0.6628154753168209</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09234913920608</v>
+        <v>1.092484059933093</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.596117799839975</v>
+        <v>6.538136828592097</v>
       </c>
       <c r="E12" t="n">
-        <v>109.818677449791</v>
+        <v>110.7166690258441</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2444208780520961</v>
+        <v>-0.2549665752174108</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6619888869686466</v>
+        <v>0.6620686194094275</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3692220260242413</v>
+        <v>-0.3851059659719922</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7882689178888794</v>
+        <v>0.7883416919620069</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041619394459301</v>
+        <v>1.041725927410423</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.859026821949102</v>
+        <v>4.86082322513169</v>
       </c>
       <c r="E13" t="n">
-        <v>294.8656563088996</v>
+        <v>305.3906561635301</v>
       </c>
       <c r="F13" t="n">
-        <v>1.902398966019571</v>
+        <v>1.888071163814943</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8650851720449876</v>
+        <v>0.8651059889092036</v>
       </c>
       <c r="H13" t="n">
-        <v>2.199088630224077</v>
+        <v>2.182473810169292</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021633412591381</v>
+        <v>0.6021855660900303</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039817536213661</v>
+        <v>1.039766054160091</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.687684825064074</v>
+        <v>4.666102828425874</v>
       </c>
       <c r="E14" t="n">
-        <v>94.46632483456315</v>
+        <v>94.391519464368</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3842757395546028</v>
+        <v>-0.389262177912009</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8555654154038301</v>
+        <v>0.8555899756890109</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4491482856085565</v>
+        <v>-0.4549634626078154</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600259326366329</v>
+        <v>0.7600404711549709</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297972789894958</v>
+        <v>1.297891477409515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.234221036367267</v>
+        <v>4.214726309550728</v>
       </c>
       <c r="E15" t="n">
-        <v>226.7068357865199</v>
+        <v>183.3986352908957</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001746484599558507</v>
+        <v>0.5725347124188775</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7950235819321335</v>
+        <v>0.9606717271395359</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0002196770811897242</v>
+        <v>0.59597331351016</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>266</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7165961540387327</v>
+        <v>0.5130012388118733</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137204161662157</v>
+        <v>0.9836246365688821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.233612236535901</v>
+        <v>4.205688582704501</v>
       </c>
       <c r="E16" t="n">
-        <v>193.1682377053591</v>
+        <v>228.6702534093223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5753232396073273</v>
+        <v>-0.01377103182869777</v>
       </c>
       <c r="G16" t="n">
-        <v>0.960655886060418</v>
+        <v>0.7951964489035779</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5988858736573065</v>
+        <v>-0.01731777329700775</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>266</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129348069807539</v>
+        <v>0.7166712962720285</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9835897067636871</v>
+        <v>1.137445029380091</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.552262799613768</v>
+        <v>3.526083894061548</v>
       </c>
       <c r="E17" t="n">
-        <v>71.87869201840833</v>
+        <v>71.77352709278925</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1568994694320897</v>
+        <v>-0.1683604907723388</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7556624070271463</v>
+        <v>0.7557392023339445</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2076316989875788</v>
+        <v>-0.2227759129768473</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7226911261833254</v>
+        <v>0.7227651776907816</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090095372198437</v>
+        <v>1.090197409679418</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.216305160893186</v>
+        <v>3.19601666481437</v>
       </c>
       <c r="E18" t="n">
-        <v>52.93681280386441</v>
+        <v>52.74273776731025</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4497429767323753</v>
+        <v>-0.4547893708910349</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505332672718759</v>
+        <v>0.7505801223238662</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5992312351018796</v>
+        <v>-0.6059171530988118</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641298074767904</v>
+        <v>0.764168312330943</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144777393727622</v>
+        <v>1.14478006525552</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.999459816670167</v>
+        <v>2.992206181666144</v>
       </c>
       <c r="E19" t="n">
-        <v>97.47228985190849</v>
+        <v>97.86053066038644</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1296585122795286</v>
+        <v>0.1277628029421494</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842394192287407</v>
+        <v>0.4842500465915383</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2677570373887337</v>
+        <v>0.2638364288066171</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174826022757066</v>
+        <v>0.7174989318031455</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935143809396153</v>
+        <v>0.6934687650647973</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.657785718778382</v>
+        <v>2.64814226070007</v>
       </c>
       <c r="E20" t="n">
-        <v>111.3290845077204</v>
+        <v>110.4483351329415</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3004753212366778</v>
+        <v>-0.3045806559867418</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7831436427993338</v>
+        <v>0.7831623553498565</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3836784273222646</v>
+        <v>-0.3889112569138728</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321585849165281</v>
+        <v>0.732165567625866</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144538859409692</v>
+        <v>1.144450674230145</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.0892820026435</v>
+        <v>579.0641882901768</v>
       </c>
       <c r="E2" t="n">
-        <v>9150.25078041489</v>
+        <v>9557.373688413805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6823272344686637</v>
+        <v>0.6708534298120381</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5010303400220005</v>
+        <v>0.5011531497354227</v>
       </c>
       <c r="H2" t="n">
-        <v>1.36184813566121</v>
+        <v>1.338619601944449</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.139229997864</v>
+        <v>225.3622169292083</v>
       </c>
       <c r="E3" t="n">
-        <v>4283.055621618795</v>
+        <v>4392.137823600921</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2777707369480507</v>
+        <v>0.2731758324474021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6016912639730023</v>
+        <v>0.6017322298143462</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4616499417224614</v>
+        <v>0.4539823843766614</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908723397746705</v>
+        <v>0.8908560177151418</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0698555782751</v>
+        <v>1.069646630508588</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.68081534993758</v>
+        <v>38.24546957902007</v>
       </c>
       <c r="E4" t="n">
-        <v>1382.221078042828</v>
+        <v>1417.666002009801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8813840784616267</v>
+        <v>0.854064005572897</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115147960783436</v>
+        <v>1.115304683374061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7903741112905044</v>
+        <v>0.7657674340514296</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715709654288769</v>
+        <v>0.4717706334923545</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049579952462753</v>
+        <v>1.049914576592313</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.28520827369017</v>
+        <v>37.17443869300266</v>
       </c>
       <c r="E5" t="n">
-        <v>277.9989178071743</v>
+        <v>283.0506338044627</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3343719116955194</v>
+        <v>-0.3366344653468524</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652610376131099</v>
+        <v>0.5652742134023226</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5915353959428186</v>
+        <v>-0.5955241851926819</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367959771319602</v>
+        <v>0.7367594257189993</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312511743789583</v>
+        <v>0.8310256157422629</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05887157107649</v>
+        <v>10.95931355257601</v>
       </c>
       <c r="E6" t="n">
-        <v>165.830068701925</v>
+        <v>159.8760966510036</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.291946436895371</v>
+        <v>-0.2990241077727509</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7183176283508197</v>
+        <v>0.7184417102278728</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.406430839746546</v>
+        <v>-0.4162120649675358</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501433136000963</v>
+        <v>0.75024935633139</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075466140283611</v>
+        <v>1.075540343195784</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.02927837035685</v>
+        <v>9.938749074762155</v>
       </c>
       <c r="E7" t="n">
-        <v>282.2025805341664</v>
+        <v>294.0244305505442</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5455695723316265</v>
+        <v>-0.5496692075966612</v>
       </c>
       <c r="G7" t="n">
-        <v>0.808446913502758</v>
+        <v>0.8085302688072646</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6748366073510469</v>
+        <v>-0.6798375135757471</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836988096139641</v>
+        <v>0.6837873991273785</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103195052765962</v>
+        <v>1.103181352677034</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.939379978128866</v>
+        <v>9.844550881314616</v>
       </c>
       <c r="E8" t="n">
-        <v>308.9211929409744</v>
+        <v>318.3374975592473</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.32084606024298</v>
+        <v>-0.3276667762001165</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174679133922121</v>
+        <v>1.174785254802081</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2731350638465088</v>
+        <v>-0.2789163167146828</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.738584921270337</v>
+        <v>0.73863491203848</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731632251267817</v>
+        <v>1.731481491841264</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.426083538099675</v>
+        <v>7.409526790463866</v>
       </c>
       <c r="E9" t="n">
-        <v>242.4029270157577</v>
+        <v>243.1785787655618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4447194670556871</v>
+        <v>0.4423228895259819</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4826514317434303</v>
+        <v>0.4826850770615504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.921409194725217</v>
+        <v>0.9163798728121406</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6776762126541253</v>
+        <v>0.6778016348105709</v>
       </c>
       <c r="N9" t="n">
-        <v>0.652817540513847</v>
+        <v>0.6528238613360159</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.047105880203505</v>
+        <v>6.967676605070332</v>
       </c>
       <c r="E10" t="n">
-        <v>195.3838915772473</v>
+        <v>199.4616607558422</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2195853859849038</v>
+        <v>-0.2288095130078455</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9636461423626788</v>
+        <v>0.9637622643738136</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2278693146080799</v>
+        <v>-0.2374128158633708</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132460481485489</v>
+        <v>0.7133399224558298</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371806750911719</v>
+        <v>1.371816378480754</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.793051534111196</v>
+        <v>6.783927677723375</v>
       </c>
       <c r="E11" t="n">
-        <v>351.4094424218786</v>
+        <v>349.0232401251484</v>
       </c>
       <c r="F11" t="n">
-        <v>1.036097714060763</v>
+        <v>1.040939279814487</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258220883500882</v>
+        <v>0.8257921402574</v>
       </c>
       <c r="H11" t="n">
-        <v>1.254625819140761</v>
+        <v>1.260534254406957</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6628154753168209</v>
+        <v>0.6627977460297074</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092484059933093</v>
+        <v>1.092147519257557</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.538136828592097</v>
+        <v>6.426714046065025</v>
       </c>
       <c r="E12" t="n">
-        <v>110.7166690258441</v>
+        <v>112.4300578169914</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2549665752174108</v>
+        <v>-0.2580268526799958</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620686194094275</v>
+        <v>0.6621317608824916</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3851059659719922</v>
+        <v>-0.3896910976390812</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883416919620069</v>
+        <v>0.7883946761524365</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041725927410423</v>
+        <v>1.041639976655417</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.86082322513169</v>
+        <v>4.818859516528363</v>
       </c>
       <c r="E13" t="n">
-        <v>305.3906561635301</v>
+        <v>309.7308228348685</v>
       </c>
       <c r="F13" t="n">
-        <v>1.888071163814943</v>
+        <v>1.870585556756649</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651059889092036</v>
+        <v>0.865159073951417</v>
       </c>
       <c r="H13" t="n">
-        <v>2.182473810169292</v>
+        <v>2.16212903855146</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021855660900303</v>
+        <v>0.6022463969760046</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039766054160091</v>
+        <v>1.039680056632216</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.666102828425874</v>
+        <v>4.622573343347852</v>
       </c>
       <c r="E14" t="n">
-        <v>94.391519464368</v>
+        <v>97.51117278999094</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.389262177912009</v>
+        <v>-0.3948587488152541</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8555899756890109</v>
+        <v>0.8556836058621172</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4549634626078154</v>
+        <v>-0.4614541474327143</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600404711549709</v>
+        <v>0.7601028957873555</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297891477409515</v>
+        <v>1.297822007178715</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.214726309550728</v>
+        <v>4.188874733642876</v>
       </c>
       <c r="E15" t="n">
-        <v>183.3986352908957</v>
+        <v>181.0978618352386</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5725347124188775</v>
+        <v>0.5613940200663394</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9606717271395359</v>
+        <v>0.9607582723830551</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59597331351016</v>
+        <v>0.5843238993653038</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5130012388118733</v>
+        <v>0.5131284024925574</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9836246365688821</v>
+        <v>0.9837159713546554</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.205688582704501</v>
+        <v>4.166269137165456</v>
       </c>
       <c r="E16" t="n">
-        <v>228.6702534093223</v>
+        <v>245.1540209948249</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01377103182869777</v>
+        <v>-0.02228647025123776</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7951964489035779</v>
+        <v>0.7953887020339933</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01731777329700775</v>
+        <v>-0.02801959619774091</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7166712962720285</v>
+        <v>0.7168219225947341</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137445029380091</v>
+        <v>1.137680285763228</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.526083894061548</v>
+        <v>3.497202669645263</v>
       </c>
       <c r="E17" t="n">
-        <v>71.77352709278925</v>
+        <v>73.21051213185697</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1683604907723388</v>
+        <v>-0.1747300934068814</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7557392023339445</v>
+        <v>0.7558587104301945</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2227759129768473</v>
+        <v>-0.2311676653265454</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7227651776907816</v>
+        <v>0.7228687048296636</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090197409679418</v>
+        <v>1.090258750905491</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.19601666481437</v>
+        <v>3.17496698506448</v>
       </c>
       <c r="E18" t="n">
-        <v>52.74273776731025</v>
+        <v>54.28647065626411</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4547893708910349</v>
+        <v>-0.4576325646081489</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505801223238662</v>
+        <v>0.750642126348568</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6059171530988118</v>
+        <v>-0.6096547856090384</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764168312330943</v>
+        <v>0.7642049547672263</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14478006525552</v>
+        <v>1.144648961131802</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.992206181666144</v>
+        <v>2.98175586338371</v>
       </c>
       <c r="E19" t="n">
-        <v>97.86053066038644</v>
+        <v>98.0123321756129</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1277628029421494</v>
+        <v>0.1249208589815176</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842500465915383</v>
+        <v>0.4842737992816937</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2638364288066171</v>
+        <v>0.2579550228957427</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174989318031455</v>
+        <v>0.717509839077101</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934687650647973</v>
+        <v>0.693343374126866</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.64814226070007</v>
+        <v>2.630242250744794</v>
       </c>
       <c r="E20" t="n">
-        <v>110.4483351329415</v>
+        <v>112.4183872828409</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3045806559867418</v>
+        <v>-0.3076553510796221</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7831623553498565</v>
+        <v>0.7831971444149967</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3889112569138728</v>
+        <v>-0.3928198069585953</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732165567625866</v>
+        <v>0.7321623537606732</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144450674230145</v>
+        <v>1.144216024614941</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.0641882901768</v>
+        <v>577.8205404814839</v>
       </c>
       <c r="E2" t="n">
-        <v>9557.373688413805</v>
+        <v>9799.962063072689</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6708534298120381</v>
+        <v>0.6644813011674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011531497354227</v>
+        <v>0.5012500753761301</v>
       </c>
       <c r="H2" t="n">
-        <v>1.338619601944449</v>
+        <v>1.325648281785861</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.3622169292083</v>
+        <v>224.6507541386719</v>
       </c>
       <c r="E3" t="n">
-        <v>4392.137823600921</v>
+        <v>4483.110735839264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2731758324474021</v>
+        <v>0.2664639943766582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6017322298143462</v>
+        <v>0.6018197261001698</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4539823843766614</v>
+        <v>0.4427638091947599</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908560177151418</v>
+        <v>0.8909034273922762</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069646630508588</v>
+        <v>1.069652221503595</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.24546957902007</v>
+        <v>38.39959732020537</v>
       </c>
       <c r="E4" t="n">
-        <v>1417.666002009801</v>
+        <v>1417.984026303446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.854064005572897</v>
+        <v>0.8645588951182819</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115304683374061</v>
+        <v>1.115228382876014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7657674340514296</v>
+        <v>0.7752303549598589</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4717706334923545</v>
+        <v>0.4716866046409713</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049914576592313</v>
+        <v>1.049452788457533</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.17443869300266</v>
+        <v>37.10715551929776</v>
       </c>
       <c r="E5" t="n">
-        <v>283.0506338044627</v>
+        <v>286.7161798100979</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3366344653468524</v>
+        <v>-0.3388949278435518</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652742134023226</v>
+        <v>0.5653020452048918</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5955241851926819</v>
+        <v>-0.5994935463584259</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367594257189993</v>
+        <v>0.7367965438027994</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8310256157422629</v>
+        <v>0.8309476917266765</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95931355257601</v>
+        <v>10.96146888078352</v>
       </c>
       <c r="E6" t="n">
-        <v>159.8760966510036</v>
+        <v>159.1207046799605</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2990241077727509</v>
+        <v>-0.2987167842587876</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7184417102278728</v>
+        <v>0.7184342550208269</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4162120649675358</v>
+        <v>-0.4157886155499754</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.75024935633139</v>
+        <v>0.7502264702761103</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075540343195784</v>
+        <v>1.075288407418739</v>
       </c>
     </row>
     <row r="7">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.938749074762155</v>
+        <v>9.952283934403365</v>
       </c>
       <c r="E7" t="n">
-        <v>294.0244305505442</v>
+        <v>296.4062880342746</v>
       </c>
       <c r="F7" t="n">
         <v>-0.5496692075966612</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6837873991273785</v>
+        <v>0.6837552120021626</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103181352677034</v>
+        <v>1.102916114164445</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.844550881314616</v>
+        <v>9.865046778130907</v>
       </c>
       <c r="E8" t="n">
-        <v>318.3374975592473</v>
+        <v>317.7395504047171</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3276667762001165</v>
+        <v>-0.3261526759819466</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174785254802081</v>
+        <v>1.174756411479618</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2789163167146828</v>
+        <v>-0.2776343017112406</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.73863491203848</v>
+        <v>0.7385598807643202</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731481491841264</v>
+        <v>1.730928328616116</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.409526790463866</v>
+        <v>7.394986120732354</v>
       </c>
       <c r="E9" t="n">
-        <v>243.1785787655618</v>
+        <v>232.4524713525265</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4423228895259819</v>
+        <v>0.4353789228323233</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4826850770615504</v>
+        <v>0.4828054424245203</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9163798728121406</v>
+        <v>0.9017688795013707</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778016348105709</v>
+        <v>0.6779452750371368</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6528238613360159</v>
+        <v>0.6529987416127677</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.967676605070332</v>
+        <v>6.958706988394959</v>
       </c>
       <c r="E10" t="n">
-        <v>199.4616607558422</v>
+        <v>201.3947855797989</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2288095130078455</v>
+        <v>-0.2303675725096919</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9637622643738136</v>
+        <v>0.9637921573392835</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2374128158633708</v>
+        <v>-0.2390220451115329</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7133399224558298</v>
+        <v>0.7133459323926578</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371816378480754</v>
+        <v>1.371605210421205</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.783927677723375</v>
+        <v>6.784238283849463</v>
       </c>
       <c r="E11" t="n">
-        <v>349.0232401251484</v>
+        <v>350.4551160928671</v>
       </c>
       <c r="F11" t="n">
-        <v>1.040939279814487</v>
+        <v>1.039425955502635</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8257921402574</v>
+        <v>0.825800979852143</v>
       </c>
       <c r="H11" t="n">
-        <v>1.260534254406957</v>
+        <v>1.258688208009563</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627977460297074</v>
+        <v>0.6627758333611757</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092147519257557</v>
+        <v>1.091911920813734</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.426714046065025</v>
+        <v>6.427721995064229</v>
       </c>
       <c r="E12" t="n">
-        <v>112.4300578169914</v>
+        <v>111.6510013210019</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2580268526799958</v>
+        <v>-0.260128810118983</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6621317608824916</v>
+        <v>0.6621856103224755</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3896910976390812</v>
+        <v>-0.392833679959164</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883946761524365</v>
+        <v>0.7884315470146451</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041639976655417</v>
+        <v>1.041571963386978</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.818859516528363</v>
+        <v>4.831940072880359</v>
       </c>
       <c r="E13" t="n">
-        <v>309.7308228348685</v>
+        <v>309.9055034430706</v>
       </c>
       <c r="F13" t="n">
-        <v>1.870585556756649</v>
+        <v>1.87376261515613</v>
       </c>
       <c r="G13" t="n">
-        <v>0.865159073951417</v>
+        <v>0.8651471606849114</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16212903855146</v>
+        <v>2.165831086670536</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022463969760046</v>
+        <v>0.6021872537350659</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039680056632216</v>
+        <v>1.039362622297066</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.622573343347852</v>
+        <v>4.622088608295879</v>
       </c>
       <c r="E14" t="n">
-        <v>97.51117278999094</v>
+        <v>97.33811764840848</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3948587488152541</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601028957873555</v>
+        <v>0.7600621594989191</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297822007178715</v>
+        <v>1.297501509264319</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.188874733642876</v>
+        <v>4.178969238857397</v>
       </c>
       <c r="E15" t="n">
-        <v>181.0978618352386</v>
+        <v>179.0660256849422</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5613940200663394</v>
+        <v>0.5530526186305806</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9607582723830551</v>
+        <v>0.9608475166695206</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5843238993653038</v>
+        <v>0.5755883311720112</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5131284024925574</v>
+        <v>0.5132498873274857</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9837159713546554</v>
+        <v>0.9838499860563015</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.166269137165456</v>
+        <v>4.159895535690683</v>
       </c>
       <c r="E16" t="n">
-        <v>245.1540209948249</v>
+        <v>258.3932266247053</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02228647025123776</v>
+        <v>-0.02402185165828541</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7953887020339933</v>
+        <v>0.7954359944565612</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02801959619774091</v>
+        <v>-0.03019960352020158</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168219225947341</v>
+        <v>0.7169017428764093</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137680285763228</v>
+        <v>1.137654593557183</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.497202669645263</v>
+        <v>3.486052566403089</v>
       </c>
       <c r="E17" t="n">
-        <v>73.21051213185697</v>
+        <v>75.2152818493727</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1747300934068814</v>
+        <v>-0.1807128589111862</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7558587104301945</v>
+        <v>0.7560213164687478</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2311676653265454</v>
+        <v>-0.2390314333400894</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7228687048296636</v>
+        <v>0.7229874944829418</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090258750905491</v>
+        <v>1.090461596358424</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.17496698506448</v>
+        <v>3.179230263826859</v>
       </c>
       <c r="E18" t="n">
-        <v>54.28647065626411</v>
+        <v>54.55786770797749</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4576325646081489</v>
+        <v>-0.457389020332128</v>
       </c>
       <c r="G18" t="n">
-        <v>0.750642126348568</v>
+        <v>0.7506358065534827</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6096547856090384</v>
+        <v>-0.6093354677979103</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642049547672263</v>
+        <v>0.7641558113104305</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144648961131802</v>
+        <v>1.144344394013534</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.98175586338371</v>
+        <v>2.985817022641243</v>
       </c>
       <c r="E19" t="n">
-        <v>98.0123321756129</v>
+        <v>97.07490471715613</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1249208589815176</v>
+        <v>0.1239739766726431</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842737992816937</v>
+        <v>0.4842837997530478</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2579550228957427</v>
+        <v>0.2559944741820013</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717509839077101</v>
+        <v>0.7174906328003879</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693343374126866</v>
+        <v>0.6932050627205499</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.630242250744794</v>
+        <v>2.634244997509431</v>
       </c>
       <c r="E20" t="n">
-        <v>112.4183872828409</v>
+        <v>113.0832783043831</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3076553510796221</v>
+        <v>-0.3081674408248938</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7831971444149967</v>
+        <v>0.7832046719834573</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3928198069585953</v>
+        <v>-0.39346987045476</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321623537606732</v>
+        <v>0.7321150960242201</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144216024614941</v>
+        <v>1.143931925008728</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>577.8205404814839</v>
+        <v>578.7710734689255</v>
       </c>
       <c r="E2" t="n">
-        <v>9799.962063072689</v>
+        <v>10135.40314501067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6644813011674</v>
+        <v>0.6716224086468374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5012500753761301</v>
+        <v>0.5011428418953737</v>
       </c>
       <c r="H2" t="n">
-        <v>1.325648281785861</v>
+        <v>1.340181585965974</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.6507541386719</v>
+        <v>224.5215203794248</v>
       </c>
       <c r="E3" t="n">
-        <v>4483.110735839264</v>
+        <v>4628.630036988061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2664639943766582</v>
+        <v>0.2672454607160837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6018197261001698</v>
+        <v>0.6018078464156247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4427638091947599</v>
+        <v>0.44407108067434</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909034273922762</v>
+        <v>0.8909215085957626</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069652221503595</v>
+        <v>1.069881697572591</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.39959732020537</v>
+        <v>38.31316298239572</v>
       </c>
       <c r="E4" t="n">
-        <v>1417.984026303446</v>
+        <v>1441.400863071073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8645588951182819</v>
+        <v>0.8628086313862409</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115228382876014</v>
+        <v>1.11523970891812</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7752303549598589</v>
+        <v>0.7736530760936059</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716866046409713</v>
+        <v>0.4717008701181405</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049452788457533</v>
+        <v>1.049719754745708</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.10715551929776</v>
+        <v>36.99417549803223</v>
       </c>
       <c r="E5" t="n">
-        <v>286.7161798100979</v>
+        <v>299.1769147471856</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3388949278435518</v>
+        <v>-0.340024373888057</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5653020452048918</v>
+        <v>0.5653214564792656</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5994935463584259</v>
+        <v>-0.6014708445804906</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367965438027994</v>
+        <v>0.7369083599798033</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8309476917266765</v>
+        <v>0.8312801710984091</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96146888078352</v>
+        <v>10.91114902762377</v>
       </c>
       <c r="E6" t="n">
-        <v>159.1207046799605</v>
+        <v>160.9208225079655</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2987167842587876</v>
+        <v>-0.3020953319521553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7184342550208269</v>
+        <v>0.7185265607510389</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4157886155499754</v>
+        <v>-0.420437250971475</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7502264702761103</v>
+        <v>0.7502946001138552</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075288407418739</v>
+        <v>1.075754362829823</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.952283934403365</v>
+        <v>9.941853051030019</v>
       </c>
       <c r="E7" t="n">
-        <v>296.4062880342746</v>
+        <v>301.4349205092869</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5496692075966612</v>
+        <v>-0.5503660133299604</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8085302688072646</v>
+        <v>0.8085515992229795</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6798375135757471</v>
+        <v>-0.6806813737785736</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6837552120021626</v>
+        <v>0.6838135146939648</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102916114164445</v>
+        <v>1.103275283320366</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.865046778130907</v>
+        <v>9.819906144365207</v>
       </c>
       <c r="E8" t="n">
-        <v>317.7395504047171</v>
+        <v>321.90385773777</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3261526759819466</v>
+        <v>-0.3314479809485603</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174756411479618</v>
+        <v>1.174870513168629</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2776343017112406</v>
+        <v>-0.2821144774964554</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385598807643202</v>
+        <v>0.7386892228075979</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730928328616116</v>
+        <v>1.731770093711699</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.394986120732354</v>
+        <v>7.359046777648167</v>
       </c>
       <c r="E9" t="n">
-        <v>232.4524713525265</v>
+        <v>231.6036360986473</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4353789228323233</v>
+        <v>0.4289220298845684</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4828054424245203</v>
+        <v>0.4829479612658639</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9017688795013707</v>
+        <v>0.8881330169824362</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779452750371368</v>
+        <v>0.6778524273185044</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6529987416127677</v>
+        <v>0.6532417914510195</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.958706988394959</v>
+        <v>6.900167654442427</v>
       </c>
       <c r="E10" t="n">
-        <v>201.3947855797989</v>
+        <v>214.4940680459108</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2303675725096919</v>
+        <v>-0.2384274409838938</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9637921573392835</v>
+        <v>0.9639945233108127</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2390220451115329</v>
+        <v>-0.2473327754653847</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7133459323926578</v>
+        <v>0.7134548452402274</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371605210421205</v>
+        <v>1.372396262989487</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.784238283849463</v>
+        <v>6.757729087051166</v>
       </c>
       <c r="E11" t="n">
-        <v>350.4551160928671</v>
+        <v>365.89495643924</v>
       </c>
       <c r="F11" t="n">
-        <v>1.039425955502635</v>
+        <v>1.027330332305748</v>
       </c>
       <c r="G11" t="n">
-        <v>0.825800979852143</v>
+        <v>0.8258886868812222</v>
       </c>
       <c r="H11" t="n">
-        <v>1.258688208009563</v>
+        <v>1.243908953620885</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627758333611757</v>
+        <v>0.6629022042437576</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091911920813734</v>
+        <v>1.092469821424379</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.427721995064229</v>
+        <v>6.410637132616488</v>
       </c>
       <c r="E12" t="n">
-        <v>111.6510013210019</v>
+        <v>111.3752859388643</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.260128810118983</v>
+        <v>-0.2612746503352251</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6621856103224755</v>
+        <v>0.6622185672447438</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.392833679959164</v>
+        <v>-0.3945444348114492</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884315470146451</v>
+        <v>0.7884371190333972</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041571963386978</v>
+        <v>1.041854049743916</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.831940072880359</v>
+        <v>4.816333537377607</v>
       </c>
       <c r="E13" t="n">
-        <v>309.9055034430706</v>
+        <v>320.9182166243367</v>
       </c>
       <c r="F13" t="n">
-        <v>1.87376261515613</v>
+        <v>1.865821757002456</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651471606849114</v>
+        <v>0.8651788282148962</v>
       </c>
       <c r="H13" t="n">
-        <v>2.165831086670536</v>
+        <v>2.156573526946057</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021872537350659</v>
+        <v>0.6022772873668327</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039362622297066</v>
+        <v>1.039778510601316</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.622088608295879</v>
+        <v>4.613063019828163</v>
       </c>
       <c r="E14" t="n">
-        <v>97.33811764840848</v>
+        <v>101.2066820850666</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3948587488152541</v>
+        <v>-0.3967211634227827</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8556836058621172</v>
+        <v>0.8557303419123427</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4614541474327143</v>
+        <v>-0.4636053485449756</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600621594989191</v>
+        <v>0.760143410967502</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297501509264319</v>
+        <v>1.297988770047001</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.178969238857397</v>
+        <v>4.179932586303287</v>
       </c>
       <c r="E15" t="n">
-        <v>179.0660256849422</v>
+        <v>182.2594571214911</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5530526186305806</v>
+        <v>0.5572218044616595</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9608475166695206</v>
+        <v>0.9608002875633916</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5755883311720112</v>
+        <v>0.5799559093334421</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5132498873274857</v>
+        <v>0.5131642200858496</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9838499860563015</v>
+        <v>0.9838478952646884</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.159895535690683</v>
+        <v>4.149527186685839</v>
       </c>
       <c r="E16" t="n">
-        <v>258.3932266247053</v>
+        <v>268.4068561544807</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02402185165828541</v>
+        <v>-0.02315426547882116</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7954359944565612</v>
+        <v>0.7954120069442323</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.03019960352020158</v>
+        <v>-0.02910977616213498</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7169017428764093</v>
+        <v>0.7168160268129667</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137654593557183</v>
+        <v>1.13772766331586</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.486052566403089</v>
+        <v>3.463754684253115</v>
       </c>
       <c r="E17" t="n">
-        <v>75.2152818493727</v>
+        <v>77.96487408418584</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1807128589111862</v>
+        <v>-0.1835132115441405</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7560213164687478</v>
+        <v>0.756114262356304</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2390314333400894</v>
+        <v>-0.2427056606130562</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229874944829418</v>
+        <v>0.7229313884538848</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090461596358424</v>
+        <v>1.090744370303005</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.179230263826859</v>
+        <v>3.173678278989037</v>
       </c>
       <c r="E18" t="n">
-        <v>54.55786770797749</v>
+        <v>56.2041320461006</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.457389020332128</v>
+        <v>-0.4579572441727453</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7506358065534827</v>
+        <v>0.7506508458851093</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6093354677979103</v>
+        <v>-0.6100802346166114</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641558113104305</v>
+        <v>0.7642162228121099</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144344394013534</v>
+        <v>1.144702679825564</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.985817022641243</v>
+        <v>2.987719938560129</v>
       </c>
       <c r="E19" t="n">
-        <v>97.07490471715613</v>
+        <v>98.10522627837427</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1239739766726431</v>
+        <v>0.1287105496631662</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842837997530478</v>
+        <v>0.4842442121064034</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2559944741820013</v>
+        <v>0.2657967745309561</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174906328003879</v>
+        <v>0.7174038710034341</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6932050627205499</v>
+        <v>0.6932128791109626</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.634244997509431</v>
+        <v>2.624244741721689</v>
       </c>
       <c r="E20" t="n">
-        <v>113.0832783043831</v>
+        <v>117.0386912399582</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3081674408248938</v>
+        <v>-0.3117491889996166</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7832046719834573</v>
+        <v>0.7832711981981726</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.39346987045476</v>
+        <v>-0.3980092587557931</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321150960242201</v>
+        <v>0.7322662615899954</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143931925008728</v>
+        <v>1.144510155919653</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>578.7710734689255</v>
+        <v>579.2015756819234</v>
       </c>
       <c r="E2" t="n">
-        <v>10135.40314501067</v>
+        <v>10053.54462886117</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6716224086468374</v>
+        <v>0.6728326477156605</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011428418953737</v>
+        <v>0.5011272243442575</v>
       </c>
       <c r="H2" t="n">
-        <v>1.340181585965974</v>
+        <v>1.342638386082667</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.5215203794248</v>
+        <v>224.8851083856695</v>
       </c>
       <c r="E3" t="n">
-        <v>4628.630036988061</v>
+        <v>4593.456258031321</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2672454607160837</v>
+        <v>0.270670567939832</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6018078464156247</v>
+        <v>0.601761042745563</v>
       </c>
       <c r="H3" t="n">
-        <v>0.44407108067434</v>
+        <v>0.4497974257437551</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909215085957626</v>
+        <v>0.8908967483360984</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069881697572591</v>
+        <v>1.069802098576617</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.31316298239572</v>
+        <v>38.47500683149637</v>
       </c>
       <c r="E4" t="n">
-        <v>1441.400863071073</v>
+        <v>1385.314690569496</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8628086313862409</v>
+        <v>0.8722653483829348</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11523970891812</v>
+        <v>1.115185157636293</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7736530760936059</v>
+        <v>0.7821708730698652</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4717008701181405</v>
+        <v>0.4716250891815585</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049719754745708</v>
+        <v>1.049532481721364</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.99417549803223</v>
+        <v>37.10456569883067</v>
       </c>
       <c r="E5" t="n">
-        <v>299.1769147471856</v>
+        <v>304.7371231864975</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.340024373888057</v>
+        <v>-0.3373881853573972</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5653214564792656</v>
+        <v>0.5652818623073639</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6014708445804906</v>
+        <v>-0.5968494796211014</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7369083599798033</v>
+        <v>0.736816016346091</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312801710984091</v>
+        <v>0.8311436889963971</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.91114902762377</v>
+        <v>10.96456975459084</v>
       </c>
       <c r="E6" t="n">
-        <v>160.9208225079655</v>
+        <v>156.9780662272076</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3020953319521553</v>
+        <v>-0.2962568815533143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7185265607510389</v>
+        <v>0.7183813555156954</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.420437250971475</v>
+        <v>-0.4123950034040682</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7502946001138552</v>
+        <v>0.7501950833194658</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075754362829823</v>
+        <v>1.07542782486314</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.941853051030019</v>
+        <v>10.00442072609663</v>
       </c>
       <c r="E7" t="n">
-        <v>301.4349205092869</v>
+        <v>288.4282968953252</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5503660133299604</v>
+        <v>-0.5461807946479365</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8085515992229795</v>
+        <v>0.8084547825246412</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6806813737785736</v>
+        <v>-0.6755860766168319</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6838135146939648</v>
+        <v>0.6836544667647381</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103275283320366</v>
+        <v>1.102920967771244</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.819906144365207</v>
+        <v>9.85570861032687</v>
       </c>
       <c r="E8" t="n">
-        <v>321.90385773777</v>
+        <v>314.9726990389122</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3314479809485603</v>
+        <v>-0.3257740066206353</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174870513168629</v>
+        <v>1.174749670339793</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2821144774964554</v>
+        <v>-0.2773135544072178</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386892228075979</v>
+        <v>0.7386132998249823</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731770093711699</v>
+        <v>1.731467955294948</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.359046777648167</v>
+        <v>7.324084850129344</v>
       </c>
       <c r="E9" t="n">
-        <v>231.6036360986473</v>
+        <v>232.5996077624935</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4289220298845684</v>
+        <v>0.4205637497981034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4829479612658639</v>
+        <v>0.483176371864798</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8881330169824362</v>
+        <v>0.8704145614053023</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778524273185044</v>
+        <v>0.6777560722045571</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532417914510195</v>
+        <v>0.6534782068678218</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.900167654442427</v>
+        <v>6.909386424288039</v>
       </c>
       <c r="E10" t="n">
-        <v>214.4940680459108</v>
+        <v>217.8203006871553</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2384274409838938</v>
+        <v>-0.2347538646013685</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9639945233108127</v>
+        <v>0.9638923470618537</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2473327754653847</v>
+        <v>-0.2435478041888677</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134548452402274</v>
+        <v>0.7134151897278791</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372396262989487</v>
+        <v>1.372217289843321</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.757729087051166</v>
+        <v>6.778468808974691</v>
       </c>
       <c r="E11" t="n">
-        <v>365.89495643924</v>
+        <v>361.2304312615682</v>
       </c>
       <c r="F11" t="n">
-        <v>1.027330332305748</v>
+        <v>1.038518107076895</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258886868812222</v>
+        <v>0.8258065101661807</v>
       </c>
       <c r="H11" t="n">
-        <v>1.243908953620885</v>
+        <v>1.257580431120493</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6629022042437576</v>
+        <v>0.6628235104126851</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092469821424379</v>
+        <v>1.092265483493222</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.410637132616488</v>
+        <v>6.450275053300923</v>
       </c>
       <c r="E12" t="n">
-        <v>111.3752859388643</v>
+        <v>108.797538653151</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2612746503352251</v>
+        <v>-0.254200972274703</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6622185672447438</v>
+        <v>0.6620556466112533</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3945444348114492</v>
+        <v>-0.3839571093092195</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884371190333972</v>
+        <v>0.7883211225001188</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041854049743916</v>
+        <v>1.041476944656251</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.816333537377607</v>
+        <v>4.825629983984519</v>
       </c>
       <c r="E13" t="n">
-        <v>320.9182166243367</v>
+        <v>315.8744019890289</v>
       </c>
       <c r="F13" t="n">
-        <v>1.865821757002456</v>
+        <v>1.87694062651005</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651788282148962</v>
+        <v>0.8651362524613384</v>
       </c>
       <c r="H13" t="n">
-        <v>2.156573526946057</v>
+        <v>2.169531817872732</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022772873668327</v>
+        <v>0.6022129474290832</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039778510601316</v>
+        <v>1.039648670463345</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.613063019828163</v>
+        <v>4.627908035802335</v>
       </c>
       <c r="E14" t="n">
-        <v>101.2066820850666</v>
+        <v>100.4348671986186</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3967211634227827</v>
+        <v>-0.3936162745134909</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8557303419123427</v>
+        <v>0.8556567608278662</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4636053485449756</v>
+        <v>-0.460016553989077</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760143410967502</v>
+        <v>0.76008270371241</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297988770047001</v>
+        <v>1.297813953474348</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.179932586303287</v>
+        <v>4.196438747893245</v>
       </c>
       <c r="E15" t="n">
-        <v>182.2594571214911</v>
+        <v>174.9772092143899</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5572218044616595</v>
+        <v>0.5683544355083938</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9608002875633916</v>
+        <v>0.9606998354038114</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5799559093334421</v>
+        <v>0.5916045934050744</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5131642200858496</v>
+        <v>0.5130538134620493</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9838478952646884</v>
+        <v>0.9835640336468511</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.149527186685839</v>
+        <v>4.170490843596058</v>
       </c>
       <c r="E16" t="n">
-        <v>268.4068561544807</v>
+        <v>258.3379450014606</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02315426547882116</v>
+        <v>-0.01655378491837045</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7954120069442323</v>
+        <v>0.7952520134244689</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02910977616213498</v>
+        <v>-0.02081577240790311</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168160268129667</v>
+        <v>0.7167669320176753</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13772766331586</v>
+        <v>1.137456354699177</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.463754684253115</v>
+        <v>3.47302872619389</v>
       </c>
       <c r="E17" t="n">
-        <v>77.96487408418584</v>
+        <v>77.8621549511204</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1835132115441405</v>
+        <v>-0.1814598738639321</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756114262356304</v>
+        <v>0.7560450585348464</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2427056606130562</v>
+        <v>-0.2400119831688161</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229313884538848</v>
+        <v>0.722908989306424</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090744370303005</v>
+        <v>1.090644735677101</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.173678278989037</v>
+        <v>3.188892770554193</v>
       </c>
       <c r="E18" t="n">
-        <v>56.2041320461006</v>
+        <v>56.50771080003526</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4579572441727453</v>
+        <v>-0.4551145113240044</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7506508458851093</v>
+        <v>0.7505859100747169</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6100802346166114</v>
+        <v>-0.6063456630550128</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642162228121099</v>
+        <v>0.7641379919824659</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144702679825564</v>
+        <v>1.144522153801039</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.987719938560129</v>
+        <v>3.000240508799836</v>
       </c>
       <c r="E19" t="n">
-        <v>98.10522627837427</v>
+        <v>97.56058304917046</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1287105496631662</v>
+        <v>0.1334525200414596</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842442121064034</v>
+        <v>0.4842306643105699</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2657967745309561</v>
+        <v>0.2755970034063506</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174038710034341</v>
+        <v>0.7172532633749448</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6932128791109626</v>
+        <v>0.693069558648403</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.624244741721689</v>
+        <v>2.631808488811493</v>
       </c>
       <c r="E20" t="n">
-        <v>117.0386912399582</v>
+        <v>116.1145007428419</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3117491889996166</v>
+        <v>-0.3086794277812382</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7832711981981726</v>
+        <v>0.7832126936287397</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3980092587557931</v>
+        <v>-0.3941195415910345</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322662615899954</v>
+        <v>0.7322023278023413</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144510155919653</v>
+        <v>1.144360413046229</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.2015756819234</v>
+        <v>578.9870880481417</v>
       </c>
       <c r="E2" t="n">
-        <v>10053.54462886117</v>
+        <v>10037.71858078927</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6728326477156605</v>
+        <v>0.6713468276206058</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011272243442575</v>
+        <v>0.5011465015827912</v>
       </c>
       <c r="H2" t="n">
-        <v>1.342638386082667</v>
+        <v>1.339621897988441</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.8851083856695</v>
+        <v>224.7795174115415</v>
       </c>
       <c r="E3" t="n">
-        <v>4593.456258031321</v>
+        <v>4566.648108288307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.270670567939832</v>
+        <v>0.2684458242642345</v>
       </c>
       <c r="G3" t="n">
-        <v>0.601761042745563</v>
+        <v>0.6017904682724948</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4497974257437551</v>
+        <v>0.4460785579320282</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908967483360984</v>
+        <v>0.8909118685189596</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069802098576617</v>
+        <v>1.069831414271532</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.47500683149637</v>
+        <v>38.32163493305224</v>
       </c>
       <c r="E4" t="n">
-        <v>1385.314690569496</v>
+        <v>1350.159323601379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8722653483829348</v>
+        <v>0.854064005572897</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115185157636293</v>
+        <v>1.115304683374061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7821708730698652</v>
+        <v>0.7657674340514296</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716250891815585</v>
+        <v>0.4717678594458042</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049532481721364</v>
+        <v>1.049922330981965</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.10456569883067</v>
+        <v>37.11049612095075</v>
       </c>
       <c r="E5" t="n">
-        <v>304.7371231864975</v>
+        <v>307.7548311209677</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3373881853573972</v>
+        <v>-0.3377649581934961</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652818623073639</v>
+        <v>0.5652862974105177</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5968494796211014</v>
+        <v>-0.5975113137196868</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.736816016346091</v>
+        <v>0.7368175807436436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8311436889963971</v>
+        <v>0.8311200033723871</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96456975459084</v>
+        <v>10.9679296860364</v>
       </c>
       <c r="E6" t="n">
-        <v>156.9780662272076</v>
+        <v>156.7660894244922</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2962568815533143</v>
+        <v>-0.2993313947458179</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7183813555156954</v>
+        <v>0.7184493526983182</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4123950034040682</v>
+        <v>-0.4166353461404109</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501950833194658</v>
+        <v>0.7502547203422389</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07542782486314</v>
+        <v>1.075573742381381</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.00442072609663</v>
+        <v>10.00514938058981</v>
       </c>
       <c r="E7" t="n">
-        <v>288.4282968953252</v>
+        <v>285.3134357134625</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5461807946479365</v>
+        <v>-0.5460061824701856</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8084547825246412</v>
+        <v>0.8084523718773295</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6755860766168319</v>
+        <v>-0.6753721078241005</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836544667647381</v>
+        <v>0.6836309333808376</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102920967771244</v>
+        <v>1.10283728976435</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.85570861032687</v>
+        <v>9.876579903843584</v>
       </c>
       <c r="E8" t="n">
-        <v>314.9726990389122</v>
+        <v>309.982047334641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3257740066206353</v>
+        <v>-0.3261526759819466</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174749670339793</v>
+        <v>1.174756411479618</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2773135544072178</v>
+        <v>-0.2776343017112406</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386132998249823</v>
+        <v>0.7386123471643496</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731467955294948</v>
+        <v>1.731409054415965</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.324084850129344</v>
+        <v>7.303821198796453</v>
       </c>
       <c r="E9" t="n">
-        <v>232.5996077624935</v>
+        <v>229.7048960559615</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4205637497981034</v>
+        <v>0.4100750966758369</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483176371864798</v>
+        <v>0.483533356743911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8704145614053023</v>
+        <v>0.8480802636601158</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6777560722045571</v>
+        <v>0.6776441673789557</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6534782068678218</v>
+        <v>0.6538278884434117</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.909386424288039</v>
+        <v>6.92142316585856</v>
       </c>
       <c r="E10" t="n">
-        <v>217.8203006871553</v>
+        <v>217.6997872215875</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2347538646013685</v>
+        <v>-0.2351779834314424</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9638923470618537</v>
+        <v>0.9639032918746463</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2435478041888677</v>
+        <v>-0.2439850402150373</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134151897278791</v>
+        <v>0.7134273550947368</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372217289843321</v>
+        <v>1.372203485242992</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.778468808974691</v>
+        <v>6.786433696545373</v>
       </c>
       <c r="E11" t="n">
-        <v>361.2304312615682</v>
+        <v>363.0635444322191</v>
       </c>
       <c r="F11" t="n">
-        <v>1.038518107076895</v>
+        <v>1.036097714060763</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258065101661807</v>
+        <v>0.8258220883500882</v>
       </c>
       <c r="H11" t="n">
-        <v>1.257580431120493</v>
+        <v>1.254625819140761</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6628235104126851</v>
+        <v>0.662839979179581</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092265483493222</v>
+        <v>1.092271210353007</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.450275053300923</v>
+        <v>6.45254730138352</v>
       </c>
       <c r="E12" t="n">
-        <v>108.797538653151</v>
+        <v>105.6120624141403</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.254200972274703</v>
+        <v>-0.2553492966961277</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620556466112533</v>
+        <v>0.6620755277264111</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3839571093092195</v>
+        <v>-0.3856800108184115</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883211225001188</v>
+        <v>0.7883405057018401</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041476944656251</v>
+        <v>1.041493764183097</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.825629983984519</v>
+        <v>4.815419870715756</v>
       </c>
       <c r="E13" t="n">
-        <v>315.8744019890289</v>
+        <v>314.7574689210043</v>
       </c>
       <c r="F13" t="n">
-        <v>1.87694062651005</v>
+        <v>1.864234300751297</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651362524613384</v>
+        <v>0.8651859154436541</v>
       </c>
       <c r="H13" t="n">
-        <v>2.169531817872732</v>
+        <v>2.154721046048636</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022129474290832</v>
+        <v>0.6022864010657409</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039648670463345</v>
+        <v>1.039795168916771</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.627908035802335</v>
+        <v>4.625044888432255</v>
       </c>
       <c r="E14" t="n">
-        <v>100.4348671986186</v>
+        <v>99.22977491809175</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3936162745134909</v>
+        <v>-0.3948587488152541</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8556567608278662</v>
+        <v>0.8556836058621172</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.460016553989077</v>
+        <v>-0.4614541474327143</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.76008270371241</v>
+        <v>0.7601047556427504</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297813953474348</v>
+        <v>1.297842399552065</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.196438747893245</v>
+        <v>4.179647055263742</v>
       </c>
       <c r="E15" t="n">
-        <v>174.9772092143899</v>
+        <v>169.137315413769</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5683544355083938</v>
+        <v>0.5516635639456293</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9606998354038114</v>
+        <v>0.9608644182246325</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5916045934050744</v>
+        <v>0.574132576336759</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5130538134620493</v>
+        <v>0.5132142768743865</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9835640336468511</v>
+        <v>0.9840023546328521</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.170490843596058</v>
+        <v>4.167198187111419</v>
       </c>
       <c r="E16" t="n">
-        <v>258.3379450014606</v>
+        <v>259.2035387740984</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01655378491837045</v>
+        <v>-0.01968183112846889</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7952520134244689</v>
+        <v>0.7953228835070862</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02081577240790311</v>
+        <v>-0.02474696948449305</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7167669320176753</v>
+        <v>0.7168014500003786</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137456354699177</v>
+        <v>1.137568743502804</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.47302872619389</v>
+        <v>3.464907049947759</v>
       </c>
       <c r="E17" t="n">
-        <v>77.8621549511204</v>
+        <v>75.20814173910937</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1814598738639321</v>
+        <v>-0.1859380787203871</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7560450585348464</v>
+        <v>0.7562034463292576</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2400119831688161</v>
+        <v>-0.2458836700929661</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.722908989306424</v>
+        <v>0.7229369563269188</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090644735677101</v>
+        <v>1.090873459410722</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.188892770554193</v>
+        <v>3.190805442056972</v>
       </c>
       <c r="E18" t="n">
-        <v>56.50771080003526</v>
+        <v>56.85419583622923</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4551145113240044</v>
+        <v>-0.4545454810464152</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505859100747169</v>
+        <v>0.7505760014227543</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6063456630550128</v>
+        <v>-0.6055955428694784</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641379919824659</v>
+        <v>0.7641052946253732</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144522153801039</v>
+        <v>1.144414048376073</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.000240508799836</v>
+        <v>2.998767689588735</v>
       </c>
       <c r="E19" t="n">
-        <v>97.56058304917046</v>
+        <v>97.03604289819233</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1334525200414596</v>
+        <v>0.1315550848667304</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842306643105699</v>
+        <v>0.4842329584128261</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2755970034063506</v>
+        <v>0.2716772631460888</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172532633749448</v>
+        <v>0.7173004463564626</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693069558648403</v>
+        <v>0.6930917727910128</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.631808488811493</v>
+        <v>2.633989513917021</v>
       </c>
       <c r="E20" t="n">
-        <v>116.1145007428419</v>
+        <v>115.3070835413969</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3086794277812382</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322023278023413</v>
+        <v>0.7321939569255874</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144360413046229</v>
+        <v>1.144303311409302</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>578.9870880481417</v>
+        <v>579.3494741397047</v>
       </c>
       <c r="E2" t="n">
-        <v>10037.71858078927</v>
+        <v>10153.50955085881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6713468276206058</v>
+        <v>0.6710789562009229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011465015827912</v>
+        <v>0.5011500956745181</v>
       </c>
       <c r="H2" t="n">
-        <v>1.339621897988441</v>
+        <v>1.339077777282853</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.7795174115415</v>
+        <v>225.2131857227373</v>
       </c>
       <c r="E3" t="n">
-        <v>4566.648108288307</v>
+        <v>4577.172599001037</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2684458242642345</v>
+        <v>0.2702888422174128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6017904682724948</v>
+        <v>0.6017658348402224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4460785579320282</v>
+        <v>0.4491595012022881</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909118685189596</v>
+        <v>0.8908932463194367</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069831414271532</v>
+        <v>1.069757589097854</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.32163493305224</v>
+        <v>38.20347391334202</v>
       </c>
       <c r="E4" t="n">
-        <v>1350.159323601379</v>
+        <v>1407.354722151092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.854064005572897</v>
+        <v>0.850569282165099</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115304683374061</v>
+        <v>1.115334566770792</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7657674340514296</v>
+        <v>0.7626135757880584</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4717678594458042</v>
+        <v>0.4717946554774907</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049922330981965</v>
+        <v>1.050002568518951</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.11049612095075</v>
+        <v>37.14917698148039</v>
       </c>
       <c r="E5" t="n">
-        <v>307.7548311209677</v>
+        <v>312.6535384746522</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3377649581934961</v>
+        <v>-0.3366344653468524</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652862974105177</v>
+        <v>0.5652742134023226</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5975113137196868</v>
+        <v>-0.5955241851926819</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368175807436436</v>
+        <v>0.7367623050799179</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8311200033723871</v>
+        <v>0.8310339278853874</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9679296860364</v>
+        <v>10.98438283071996</v>
       </c>
       <c r="E6" t="n">
-        <v>156.7660894244922</v>
+        <v>157.1719719545413</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2993313947458179</v>
+        <v>-0.2971796188318551</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7184493526983182</v>
+        <v>0.7183997881355099</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4166353461404109</v>
+        <v>-0.4136688564498837</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7502547203422389</v>
+        <v>0.7502108125230474</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075573742381381</v>
+        <v>1.075428885328515</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.00514938058981</v>
+        <v>10.0229405994969</v>
       </c>
       <c r="E7" t="n">
-        <v>285.3134357134625</v>
+        <v>284.7430943697216</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5460061824701856</v>
+        <v>-0.5452202022760521</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8084523718773295</v>
+        <v>0.8084431312908955</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6753721078241005</v>
+        <v>-0.674407612821773</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836309333808376</v>
+        <v>0.6835873725518873</v>
       </c>
       <c r="N7" t="n">
-        <v>1.10283728976435</v>
+        <v>1.102746503984881</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.876579903843584</v>
+        <v>9.914278957160986</v>
       </c>
       <c r="E8" t="n">
-        <v>309.982047334641</v>
+        <v>310.6245563570428</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3261526759819466</v>
+        <v>-0.3227425760248134</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174756411479618</v>
+        <v>1.174702505259078</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2776343017112406</v>
+        <v>-0.274744094423833</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386123471643496</v>
+        <v>0.7385482273857866</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731409054415965</v>
+        <v>1.73116689082346</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.303821198796453</v>
+        <v>7.321767349965016</v>
       </c>
       <c r="E9" t="n">
-        <v>229.7048960559615</v>
+        <v>229.3463139912617</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4100750966758369</v>
+        <v>0.4177011177164398</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483533356743911</v>
+        <v>0.4832660215951808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8480802636601158</v>
+        <v>0.8643295805024277</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6776441673789557</v>
+        <v>0.6777834769346163</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6538278884434117</v>
+        <v>0.6535960528158308</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.92142316585856</v>
+        <v>6.938075889821189</v>
       </c>
       <c r="E10" t="n">
-        <v>217.6997872215875</v>
+        <v>218.1132511606066</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2351779834314424</v>
+        <v>-0.2319247769668049</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9639032918746463</v>
+        <v>0.9638250143247279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2439850402150373</v>
+        <v>-0.2406295473969363</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134273550947368</v>
+        <v>0.7133881834806617</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372203485242992</v>
+        <v>1.372006873982328</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.786433696545373</v>
+        <v>6.801246179143399</v>
       </c>
       <c r="E11" t="n">
-        <v>363.0635444322191</v>
+        <v>366.8242873889017</v>
       </c>
       <c r="F11" t="n">
-        <v>1.036097714060763</v>
+        <v>1.045481078817055</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258220883500882</v>
+        <v>0.8257684535730546</v>
       </c>
       <c r="H11" t="n">
-        <v>1.254625819140761</v>
+        <v>1.266070499900203</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662839979179581</v>
+        <v>0.6627567952371481</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092271210353007</v>
+        <v>1.092055371477885</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.45254730138352</v>
+        <v>6.475813409641422</v>
       </c>
       <c r="E12" t="n">
-        <v>105.6120624141403</v>
+        <v>103.6764916555825</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2553492966961277</v>
+        <v>-0.252094465015116</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6620755277264111</v>
+        <v>0.662025773246926</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3856800108184115</v>
+        <v>-0.3807925237996564</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883405057018401</v>
+        <v>0.7882497469562294</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041493764183097</v>
+        <v>1.041288134521902</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.815419870715756</v>
+        <v>4.818047647969911</v>
       </c>
       <c r="E13" t="n">
-        <v>314.7574689210043</v>
+        <v>321.1261800714819</v>
       </c>
       <c r="F13" t="n">
-        <v>1.864234300751297</v>
+        <v>1.862647083101023</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651859154436541</v>
+        <v>0.8651932538994369</v>
       </c>
       <c r="H13" t="n">
-        <v>2.154721046048636</v>
+        <v>2.152868246147377</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022864010657409</v>
+        <v>0.6022955925821654</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039795168916771</v>
+        <v>1.039812399624669</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.625044888432255</v>
+        <v>4.652244897664763</v>
       </c>
       <c r="E14" t="n">
-        <v>99.22977491809175</v>
+        <v>99.24308262182048</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3948587488152541</v>
+        <v>-0.3898847088327175</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8556836058621172</v>
+        <v>0.8555969283212862</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4614541474327143</v>
+        <v>-0.4556873639059063</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601047556427504</v>
+        <v>0.759965136933093</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297842399552065</v>
+        <v>1.297463259816518</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.179647055263742</v>
+        <v>4.16844632525655</v>
       </c>
       <c r="E15" t="n">
-        <v>169.137315413769</v>
+        <v>260.4242948828073</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5516635639456293</v>
+        <v>-0.02141846606044984</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9608644182246325</v>
+        <v>0.7953660797858468</v>
       </c>
       <c r="H15" t="n">
-        <v>0.574132576336759</v>
+        <v>-0.02692906650760965</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>266</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5132142768743865</v>
+        <v>0.7168147572158488</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9840023546328521</v>
+        <v>1.137643489047033</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.167198187111419</v>
+        <v>4.157778809298553</v>
       </c>
       <c r="E16" t="n">
-        <v>259.2035387740984</v>
+        <v>170.0355711659753</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01968183112846889</v>
+        <v>0.5433363217217908</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7953228835070862</v>
+        <v>0.9609779898180677</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02474696948449305</v>
+        <v>0.5653993405454116</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>266</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168014500003786</v>
+        <v>0.5132811864172798</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137568743502804</v>
+        <v>0.9842399053537497</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.464907049947759</v>
+        <v>3.481336389819713</v>
       </c>
       <c r="E17" t="n">
-        <v>75.20814173910937</v>
+        <v>78.228738132023</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1859380787203871</v>
+        <v>-0.181086389490797</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7562034463292576</v>
+        <v>0.7560330926278713</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2458836700929661</v>
+        <v>-0.2395217765684894</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229369563269188</v>
+        <v>0.7229299316245038</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090873459410722</v>
+        <v>1.090609293855753</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.190805442056972</v>
+        <v>3.205498470094329</v>
       </c>
       <c r="E18" t="n">
-        <v>56.85419583622923</v>
+        <v>57.65615466573822</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4545454810464152</v>
+        <v>-0.4515350758954928</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505760014227543</v>
+        <v>0.7505406766286252</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6055955428694784</v>
+        <v>-0.6016130636966353</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641052946253732</v>
+        <v>0.7639727351133858</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144414048376073</v>
+        <v>1.144153455196032</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.998767689588735</v>
+        <v>3.00524428467892</v>
       </c>
       <c r="E19" t="n">
-        <v>97.03604289819233</v>
+        <v>97.70248746509453</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1315550848667304</v>
+        <v>0.1363002887096327</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842329584128261</v>
+        <v>0.484235035845429</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2716772631460888</v>
+        <v>0.2814754790959419</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173004463564626</v>
+        <v>0.7170962102115273</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6930917727910128</v>
+        <v>0.692892432932756</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.633989513917021</v>
+        <v>2.640649712018291</v>
       </c>
       <c r="E20" t="n">
-        <v>115.3070835413969</v>
+        <v>115.6815138657514</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3086794277812382</v>
+        <v>-0.3061184654580112</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7832126936287397</v>
+        <v>0.7831775263083359</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3941195415910345</v>
+        <v>-0.3908672748833357</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321939569255874</v>
+        <v>0.7321185457047884</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144303311409302</v>
+        <v>1.14412587473978</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.3494741397047</v>
+        <v>579.6130766054367</v>
       </c>
       <c r="E2" t="n">
-        <v>10153.50955085881</v>
+        <v>10352.71404692925</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6710789562009229</v>
+        <v>0.6716139408898958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011500956745181</v>
+        <v>0.5011429537747759</v>
       </c>
       <c r="H2" t="n">
-        <v>1.339077777282853</v>
+        <v>1.340164389883317</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.2131857227373</v>
+        <v>225.333294364221</v>
       </c>
       <c r="E3" t="n">
-        <v>4577.172599001037</v>
+        <v>4664.018497554667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2702888422174128</v>
+        <v>0.2706798787119198</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6017658348402224</v>
+        <v>0.6017609271886936</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4491595012022881</v>
+        <v>0.4498129846623342</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908932463194367</v>
+        <v>0.8908916104779495</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069757589097854</v>
+        <v>1.069762145726537</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.20347391334202</v>
+        <v>37.91946923131845</v>
       </c>
       <c r="E4" t="n">
-        <v>1407.354722151092</v>
+        <v>1438.273439131583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.850569282165099</v>
+        <v>0.8195452438715662</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115334566770792</v>
+        <v>1.115698511529031</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7626135757880584</v>
+        <v>0.7345579790622867</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4717946554774907</v>
+        <v>0.4719675346528094</v>
       </c>
       <c r="N4" t="n">
-        <v>1.050002568518951</v>
+        <v>1.050745045771548</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.14917698148039</v>
+        <v>37.18266356348473</v>
       </c>
       <c r="E5" t="n">
-        <v>312.6535384746522</v>
+        <v>321.2942907640908</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3366344653468524</v>
+        <v>-0.3370113544034773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652742134023226</v>
+        <v>0.5652778343017314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5955241851926819</v>
+        <v>-0.596187102966413</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367623050799179</v>
+        <v>0.7367865899114285</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8310339278853874</v>
+        <v>0.8310784871872485</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.98438283071996</v>
+        <v>11.00367779514739</v>
       </c>
       <c r="E6" t="n">
-        <v>157.1719719545413</v>
+        <v>160.7765328354766</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2971796188318551</v>
+        <v>-0.2965644971309774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7183997881355099</v>
+        <v>0.7183873124179597</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4136688564498837</v>
+        <v>-0.4128197867704481</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7502108125230474</v>
+        <v>0.7501982721039605</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075428885328515</v>
+        <v>1.075407558697451</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.0229405994969</v>
+        <v>10.50946835101641</v>
       </c>
       <c r="E7" t="n">
-        <v>284.7430943697216</v>
+        <v>589.6438257370852</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5452202022760521</v>
+        <v>-0.5238603442352328</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8084431312908955</v>
+        <v>0.8091875498136518</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.674407612821773</v>
+        <v>-0.647390514542485</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6835873725518873</v>
+        <v>0.6816853745636298</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102746503984881</v>
+        <v>1.100706522623983</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.914278957160986</v>
+        <v>9.929496928896894</v>
       </c>
       <c r="E8" t="n">
-        <v>310.6245563570428</v>
+        <v>314.2857065640254</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3227425760248134</v>
+        <v>-0.324258752393252</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174702505259078</v>
+        <v>1.174724584640683</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.274744094423833</v>
+        <v>-0.2760295959009268</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385482273857866</v>
+        <v>0.7385810852891527</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73116689082346</v>
+        <v>1.73130112297198</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.321767349965016</v>
+        <v>7.342487880188258</v>
       </c>
       <c r="E9" t="n">
-        <v>229.3463139912617</v>
+        <v>231.7846832337623</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4177011177164398</v>
+        <v>0.4217569752852721</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4832660215951808</v>
+        <v>0.4831407257428416</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8643295805024277</v>
+        <v>0.8729485071597093</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6777834769346163</v>
+        <v>0.6778101068781204</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6535960528158308</v>
+        <v>0.6534615811441767</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.938075889821189</v>
+        <v>6.938569206066443</v>
       </c>
       <c r="E10" t="n">
-        <v>218.1132511606066</v>
+        <v>220.3300779136327</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2319247769668049</v>
+        <v>-0.2350366175740701</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9638250143247279</v>
+        <v>0.9638996191157632</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2406295473969363</v>
+        <v>-0.2438393095223773</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7133881834806617</v>
+        <v>0.71342450958921</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372006873982328</v>
+        <v>1.372202498071922</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.801246179143399</v>
+        <v>6.785562010611871</v>
       </c>
       <c r="E11" t="n">
-        <v>366.8242873889017</v>
+        <v>372.5576952932115</v>
       </c>
       <c r="F11" t="n">
-        <v>1.045481078817055</v>
+        <v>1.035795219779021</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8257684535730546</v>
+        <v>0.8258241205765738</v>
       </c>
       <c r="H11" t="n">
-        <v>1.266070499900203</v>
+        <v>1.254256437866999</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6627567952371481</v>
+        <v>0.6628426810961859</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092055371477885</v>
+        <v>1.092286083389461</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.475813409641422</v>
+        <v>6.433244295789651</v>
       </c>
       <c r="E12" t="n">
-        <v>103.6764916555825</v>
+        <v>106.2235138257523</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.252094465015116</v>
+        <v>-0.2610837104194278</v>
       </c>
       <c r="G12" t="n">
-        <v>0.662025773246926</v>
+        <v>0.6622128987359831</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3807925237996564</v>
+        <v>-0.3942594759446372</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7882497469562294</v>
+        <v>0.7884353441417624</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041288134521902</v>
+        <v>1.04184255366118</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.818047647969911</v>
+        <v>4.807663753010522</v>
       </c>
       <c r="E13" t="n">
-        <v>321.1261800714819</v>
+        <v>323.8541385382235</v>
       </c>
       <c r="F13" t="n">
-        <v>1.862647083101023</v>
+        <v>1.848372871287406</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8651932538994369</v>
+        <v>0.8652706040906909</v>
       </c>
       <c r="H13" t="n">
-        <v>2.152868246147377</v>
+        <v>2.136178974009932</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022955925821654</v>
+        <v>0.6023693284226039</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039812399624669</v>
+        <v>1.040047492963802</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.652244897664763</v>
+        <v>4.658658443867932</v>
       </c>
       <c r="E14" t="n">
-        <v>99.24308262182048</v>
+        <v>101.4981368924105</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3898847088327175</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.759965136933093</v>
+        <v>0.7599713584149111</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297463259816518</v>
+        <v>1.297492372134957</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.16844632525655</v>
+        <v>4.155087657989146</v>
       </c>
       <c r="E15" t="n">
-        <v>260.4242948828073</v>
+        <v>262.5036698690054</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02141846606044984</v>
+        <v>-0.02731677112151143</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7953660797858468</v>
+        <v>0.7955333712240631</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02692906650760965</v>
+        <v>-0.03433768099442509</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168147572158488</v>
+        <v>0.7168237969444292</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137643489047033</v>
+        <v>1.137913338821722</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.157778809298553</v>
+        <v>4.085646070671102</v>
       </c>
       <c r="E16" t="n">
-        <v>170.0355711659753</v>
+        <v>176.8495203521369</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5433363217217908</v>
+        <v>0.5046372463338387</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9609779898180677</v>
+        <v>0.961783439430856</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5653993405454116</v>
+        <v>0.52468905747895</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5132811864172798</v>
+        <v>0.5134152767665373</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9842399053537497</v>
+        <v>0.9853362339536882</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.481336389819713</v>
+        <v>3.470900985152473</v>
       </c>
       <c r="E17" t="n">
-        <v>78.228738132023</v>
+        <v>79.08060543613429</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.181086389490797</v>
+        <v>-0.1850056690145857</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7560330926278713</v>
+        <v>0.7561681965449701</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2395217765684894</v>
+        <v>-0.244662060451498</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229299316245038</v>
+        <v>0.7229326876194417</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090609293855753</v>
+        <v>1.090823890674279</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.205498470094329</v>
+        <v>3.204889906829793</v>
       </c>
       <c r="E18" t="n">
-        <v>57.65615466573822</v>
+        <v>59.27276967326621</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4515350758954928</v>
+        <v>-0.453081520973547</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505406766286252</v>
+        <v>0.7505552346039996</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6016130636966353</v>
+        <v>-0.6036617960736724</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7639727351133858</v>
+        <v>0.764049876255534</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144153455196032</v>
+        <v>1.144307487120441</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.00524428467892</v>
+        <v>3.006791725528708</v>
       </c>
       <c r="E19" t="n">
-        <v>97.70248746509453</v>
+        <v>97.22912075406811</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1363002887096327</v>
+        <v>0.1325036946719962</v>
       </c>
       <c r="G19" t="n">
-        <v>0.484235035845429</v>
+        <v>0.4842312905162684</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2814754790959419</v>
+        <v>0.2736372003773774</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170962102115273</v>
+        <v>0.7172685872584618</v>
       </c>
       <c r="N19" t="n">
-        <v>0.692892432932756</v>
+        <v>0.6930635082041686</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.640649712018291</v>
+        <v>2.640605705900379</v>
       </c>
       <c r="E20" t="n">
-        <v>115.6815138657514</v>
+        <v>117.6451728715989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3061184654580112</v>
+        <v>-0.3086794277812382</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7831775263083359</v>
+        <v>0.7832126936287397</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3908672748833357</v>
+        <v>-0.3941195415910345</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321185457047884</v>
+        <v>0.7321955815616353</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14412587473978</v>
+        <v>1.144313951495119</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.6130766054367</v>
+        <v>578.2077978607023</v>
       </c>
       <c r="E2" t="n">
-        <v>10352.71404692925</v>
+        <v>10448.71905111378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6716139408898958</v>
+        <v>0.6676153816232715</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011429537747759</v>
+        <v>0.5011998349606499</v>
       </c>
       <c r="H2" t="n">
-        <v>1.340164389883317</v>
+        <v>1.332034320553372</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.333294364221</v>
+        <v>224.8127973626142</v>
       </c>
       <c r="E3" t="n">
-        <v>4664.018497554667</v>
+        <v>4728.338623740928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2706798787119198</v>
+        <v>0.2683713741491733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6017609271886936</v>
+        <v>0.6017915154887103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4498129846623342</v>
+        <v>0.4459540675498407</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908916104779495</v>
+        <v>0.8908973545804569</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069762145726537</v>
+        <v>1.069702006585754</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.91946923131845</v>
+        <v>37.80076609167723</v>
       </c>
       <c r="E4" t="n">
-        <v>1438.273439131583</v>
+        <v>1468.14608863757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8195452438715662</v>
+        <v>0.8188497110766171</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115698511529031</v>
+        <v>1.115708713248758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7345579790622867</v>
+        <v>0.7339278624904374</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4719675346528094</v>
+        <v>0.472047445964898</v>
       </c>
       <c r="N4" t="n">
-        <v>1.050745045771548</v>
+        <v>1.050813292009979</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.18266356348473</v>
+        <v>37.17354484686152</v>
       </c>
       <c r="E5" t="n">
-        <v>321.2942907640908</v>
+        <v>329.3401209567326</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3370113544034773</v>
+        <v>-0.3366344653468524</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652778343017314</v>
+        <v>0.5652742134023226</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.596187102966413</v>
+        <v>-0.5955241851926819</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367865899114285</v>
+        <v>0.7367139265833648</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8310784871872485</v>
+        <v>0.8308968924234457</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.00367779514739</v>
+        <v>10.98634744390679</v>
       </c>
       <c r="E6" t="n">
-        <v>160.7765328354766</v>
+        <v>161.5987104449233</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2965644971309774</v>
+        <v>-0.2956415409800245</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7183873124179597</v>
+        <v>0.7183700036474856</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4128197867704481</v>
+        <v>-0.4115449412961569</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501982721039605</v>
+        <v>0.750150884458941</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075407558697451</v>
+        <v>1.075191682070771</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.50946835101641</v>
+        <v>10.54138528623009</v>
       </c>
       <c r="E7" t="n">
-        <v>589.6438257370852</v>
+        <v>709.0977379857818</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5238603442352328</v>
+        <v>-0.5100979399611381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8091875498136518</v>
+        <v>0.8106615322168872</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.647390514542485</v>
+        <v>-0.6292366415440873</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6816853745636298</v>
+        <v>0.6792566490776941</v>
       </c>
       <c r="N7" t="n">
-        <v>1.100706522623983</v>
+        <v>1.098658055130972</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.929496928896894</v>
+        <v>9.913596110672273</v>
       </c>
       <c r="E8" t="n">
-        <v>314.2857065640254</v>
+        <v>315.7623878406235</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.324258752393252</v>
+        <v>-0.3216048391620528</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174724584640683</v>
+        <v>1.174687918721582</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2760295959009268</v>
+        <v>-0.2737789620855698</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385810852891527</v>
+        <v>0.7384857526275412</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73130112297198</v>
+        <v>1.730827169621266</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.342487880188258</v>
+        <v>7.332176623000998</v>
       </c>
       <c r="E9" t="n">
-        <v>231.7846832337623</v>
+        <v>229.1999727985812</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4217569752852721</v>
+        <v>0.4212796524827178</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4831407257428416</v>
+        <v>0.4831548636044818</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8729485071597093</v>
+        <v>0.8719350341210349</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778101068781204</v>
+        <v>0.6779327891346981</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6534615811441767</v>
+        <v>0.6535248047180567</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.938569206066443</v>
+        <v>6.922565776671657</v>
       </c>
       <c r="E10" t="n">
-        <v>220.3300779136327</v>
+        <v>223.7507259245415</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2350366175740701</v>
+        <v>-0.234612477487237</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9638996191157632</v>
+        <v>0.9638887477673815</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2438393095223773</v>
+        <v>-0.2434020295710069</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.71342450958921</v>
+        <v>0.7134325826937199</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372202498071922</v>
+        <v>1.372046818018383</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.785562010611871</v>
+        <v>6.773554974538484</v>
       </c>
       <c r="E11" t="n">
-        <v>372.5576952932115</v>
+        <v>375.77913377675</v>
       </c>
       <c r="F11" t="n">
-        <v>1.035795219779021</v>
+        <v>1.030956969756657</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258241205765738</v>
+        <v>0.8258592035229272</v>
       </c>
       <c r="H11" t="n">
-        <v>1.254256437866999</v>
+        <v>1.248344712220715</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6628426810961859</v>
+        <v>0.6628781765674822</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092286083389461</v>
+        <v>1.092267005586169</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.433244295789651</v>
+        <v>6.435236133172095</v>
       </c>
       <c r="E12" t="n">
-        <v>106.2235138257523</v>
+        <v>104.6541696177022</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2610837104194278</v>
+        <v>-0.2580268526799958</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6622128987359831</v>
+        <v>0.6621317608824916</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3942594759446372</v>
+        <v>-0.3896910976390812</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7884353441417624</v>
+        <v>0.7883890759177616</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04184255366118</v>
+        <v>1.041535552658218</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.807663753010522</v>
+        <v>4.788339556702033</v>
       </c>
       <c r="E13" t="n">
-        <v>323.8541385382235</v>
+        <v>320.8948292890531</v>
       </c>
       <c r="F13" t="n">
-        <v>1.848372871287406</v>
+        <v>1.837284099923719</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8652706040906909</v>
+        <v>0.8653448301822979</v>
       </c>
       <c r="H13" t="n">
-        <v>2.136178974009932</v>
+        <v>2.123181459969742</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6023693284226039</v>
+        <v>0.6024472381379559</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040047492963802</v>
+        <v>1.040153181657001</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.658658443867932</v>
+        <v>4.65030008515139</v>
       </c>
       <c r="E14" t="n">
-        <v>101.4981368924105</v>
+        <v>102.94199015803</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3898847088327175</v>
+        <v>-0.389262177912009</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8555969283212862</v>
+        <v>0.8555899756890109</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4556873639059063</v>
+        <v>-0.4549634626078154</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7599713584149111</v>
+        <v>0.7598952988503076</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297492372134957</v>
+        <v>1.297204737349072</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.155087657989146</v>
+        <v>4.145719554150672</v>
       </c>
       <c r="E15" t="n">
-        <v>262.5036698690054</v>
+        <v>266.9023756157339</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02731677112151143</v>
+        <v>-0.02627659676945127</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7955333712240631</v>
+        <v>0.7955015561182401</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.03433768099442509</v>
+        <v>-0.03303148380711102</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168237969444292</v>
+        <v>0.7168838057962917</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137913338821722</v>
+        <v>1.137833940251976</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.085646070671102</v>
+        <v>4.082002287076956</v>
       </c>
       <c r="E16" t="n">
-        <v>176.8495203521369</v>
+        <v>180.5503750564928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5046372463338387</v>
+        <v>0.501883248931652</v>
       </c>
       <c r="G16" t="n">
-        <v>0.961783439430856</v>
+        <v>0.9618583134525115</v>
       </c>
       <c r="H16" t="n">
-        <v>0.52468905747895</v>
+        <v>0.5217850091976471</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5134152767665373</v>
+        <v>0.5135620903351305</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9853362339536882</v>
+        <v>0.9855828585850943</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.470900985152473</v>
+        <v>3.47112421947224</v>
       </c>
       <c r="E17" t="n">
-        <v>79.08060543613429</v>
+        <v>79.72606622107693</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1850056690145857</v>
+        <v>-0.182206703952189</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7561681965449701</v>
+        <v>0.7560695595561721</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.244662060451498</v>
+        <v>-0.2409919849955974</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229326876194417</v>
+        <v>0.7229776850024532</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090823890674279</v>
+        <v>1.090625698054473</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.204889906829793</v>
+        <v>3.184297290564414</v>
       </c>
       <c r="E18" t="n">
-        <v>59.27276967326621</v>
+        <v>60.22696648918843</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.453081520973547</v>
+        <v>-0.4572266410074158</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7505552346039996</v>
+        <v>0.750631698053379</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6036617960736724</v>
+        <v>-0.6091224793639096</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764049876255534</v>
+        <v>0.764174431284779</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144307487120441</v>
+        <v>1.144480725954956</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.006791725528708</v>
+        <v>2.990430060184217</v>
       </c>
       <c r="E19" t="n">
-        <v>97.22912075406811</v>
+        <v>96.64017992018361</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1325036946719962</v>
+        <v>0.1306066907083261</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842312905162684</v>
+        <v>0.4842356679894789</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2736372003773774</v>
+        <v>0.2697172045392654</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172685872584618</v>
+        <v>0.7172760917094523</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6930635082041686</v>
+        <v>0.6929983674657018</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.640605705900379</v>
+        <v>2.633347964370308</v>
       </c>
       <c r="E20" t="n">
-        <v>117.6451728715989</v>
+        <v>119.0997329586566</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3086794277812382</v>
+        <v>-0.3091913119138329</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7832126936287397</v>
+        <v>0.783221209335663</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3941195415910345</v>
+        <v>-0.3947688191131755</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321955815616353</v>
+        <v>0.7321818854898762</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144313951495119</v>
+        <v>1.14417512099155</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>578.2077978607023</v>
+        <v>569.9293397158275</v>
       </c>
       <c r="E2" t="n">
-        <v>10448.71905111378</v>
+        <v>12392.81151065961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6676153816232715</v>
+        <v>0.6359342207612297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5011998349606499</v>
+        <v>0.5019375891731342</v>
       </c>
       <c r="H2" t="n">
-        <v>1.332034320553372</v>
+        <v>1.266958750407266</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.8127973626142</v>
+        <v>222.368641761101</v>
       </c>
       <c r="E3" t="n">
-        <v>4728.338623740928</v>
+        <v>5490.521509215389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2683713741491733</v>
+        <v>0.2491658660836025</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6017915154887103</v>
+        <v>0.6021974102878452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4459540675498407</v>
+        <v>0.4137611052902126</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908973545804569</v>
+        <v>0.8909782362421141</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069702006585754</v>
+        <v>1.068947211886858</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.80076609167723</v>
+        <v>36.81651243426753</v>
       </c>
       <c r="E4" t="n">
-        <v>1468.14608863757</v>
+        <v>1728.725834956775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8188497110766171</v>
+        <v>0.7562042270232114</v>
       </c>
       <c r="G4" t="n">
-        <v>1.115708713248758</v>
+        <v>1.11699967438542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7339278624904374</v>
+        <v>0.6769959243177756</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.472047445964898</v>
+        <v>0.4734268407263782</v>
       </c>
       <c r="N4" t="n">
-        <v>1.050813292009979</v>
+        <v>1.053552549845547</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.17354484686152</v>
+        <v>36.67066595691477</v>
       </c>
       <c r="E5" t="n">
-        <v>329.3401209567326</v>
+        <v>371.6941587543757</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3366344653468524</v>
+        <v>-0.3475406028128432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5652742134023226</v>
+        <v>0.5655444519461287</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5955241851926819</v>
+        <v>-0.614523936388909</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367139265833648</v>
+        <v>0.7370331488038034</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8308968924234457</v>
+        <v>0.8304319445232865</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.98634744390679</v>
+        <v>10.73559563853456</v>
       </c>
       <c r="E6" t="n">
-        <v>161.5987104449233</v>
+        <v>190.0583237322766</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2956415409800245</v>
+        <v>-0.3195311724888245</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7183700036474856</v>
+        <v>0.7193673769133215</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4115449412961569</v>
+        <v>-0.4441835739895189</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750150884458941</v>
+        <v>0.7509544023776188</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075191682070771</v>
+        <v>1.076253522892788</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.54138528623009</v>
+        <v>10.32581747371083</v>
       </c>
       <c r="E7" t="n">
-        <v>709.0977379857818</v>
+        <v>826.1159566563948</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5100979399611381</v>
+        <v>-0.5238603442352328</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8106615322168872</v>
+        <v>0.8091875498136518</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6292366415440873</v>
+        <v>-0.647390514542485</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6792566490776941</v>
+        <v>0.6790580903560431</v>
       </c>
       <c r="N7" t="n">
-        <v>1.098658055130972</v>
+        <v>1.094728436699745</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.913596110672273</v>
+        <v>9.555080876287306</v>
       </c>
       <c r="E8" t="n">
-        <v>315.7623878406235</v>
+        <v>390.0221408881284</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3216048391620528</v>
+        <v>-0.3532642797343808</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174687918721582</v>
+        <v>1.17573521673002</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2737789620855698</v>
+        <v>-0.3004624465675929</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7384857526275412</v>
+        <v>0.7391371144951295</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730827169621266</v>
+        <v>1.731349781823923</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.332176623000998</v>
+        <v>7.262039945444715</v>
       </c>
       <c r="E9" t="n">
-        <v>229.1999727985812</v>
+        <v>239.2231035044618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4212796524827178</v>
+        <v>0.4041250385663624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4831548636044818</v>
+        <v>0.4837707882247094</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8719350341210349</v>
+        <v>0.8353646983303342</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779327891346981</v>
+        <v>0.6789822578812882</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6535248047180567</v>
+        <v>0.6544076179409695</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.922565776671657</v>
+        <v>6.757515479376679</v>
       </c>
       <c r="E10" t="n">
-        <v>223.7507259245415</v>
+        <v>246.1814769156303</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.234612477487237</v>
+        <v>-0.2606478789649065</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9638887477673815</v>
+        <v>0.9649710355457617</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2434020295710069</v>
+        <v>-0.2701095363110987</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7134325826937199</v>
+        <v>0.7141555834748825</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372046818018383</v>
+        <v>1.372958447008914</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.773554974538484</v>
+        <v>6.58103083589969</v>
       </c>
       <c r="E11" t="n">
-        <v>375.77913377675</v>
+        <v>462.0117411144421</v>
       </c>
       <c r="F11" t="n">
-        <v>1.030956969756657</v>
+        <v>0.9494864812313419</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8258592035229272</v>
+        <v>0.827186647483609</v>
       </c>
       <c r="H11" t="n">
-        <v>1.248344712220715</v>
+        <v>1.147850348068096</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6628781765674822</v>
+        <v>0.6639773951928222</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092267005586169</v>
+        <v>1.094226149588095</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.435236133172095</v>
+        <v>6.326393493929204</v>
       </c>
       <c r="E12" t="n">
-        <v>104.6541696177022</v>
+        <v>120.2858244147099</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2580268526799958</v>
+        <v>-0.2816275562590831</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6621317608824916</v>
+        <v>0.6632306325362753</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3896910976390812</v>
+        <v>-0.4246298986253164</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883890759177616</v>
+        <v>0.7890940521443157</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041535552658218</v>
+        <v>1.042662192716886</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.788339556702033</v>
+        <v>4.710527798329638</v>
       </c>
       <c r="E13" t="n">
-        <v>320.8948292890531</v>
+        <v>338.2407141627378</v>
       </c>
       <c r="F13" t="n">
-        <v>1.837284099923719</v>
+        <v>1.775719344424268</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8653448301822979</v>
+        <v>0.8659834853401818</v>
       </c>
       <c r="H13" t="n">
-        <v>2.123181459969742</v>
+        <v>2.050523335011079</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6024472381379559</v>
+        <v>0.6032044395072048</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040153181657001</v>
+        <v>1.040697278236597</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.65030008515139</v>
+        <v>4.529179327162871</v>
       </c>
       <c r="E14" t="n">
-        <v>102.94199015803</v>
+        <v>124.0583820299797</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.389262177912009</v>
+        <v>-0.4134125111970282</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8555899756890109</v>
+        <v>0.8564999916496132</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4549634626078154</v>
+        <v>-0.4826766085552417</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7598952988503076</v>
+        <v>0.7606420101692554</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297204737349072</v>
+        <v>1.297949963124983</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.145719554150672</v>
+        <v>4.096936629045261</v>
       </c>
       <c r="E15" t="n">
-        <v>266.9023756157339</v>
+        <v>303.4569120671786</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02627659676945127</v>
+        <v>-0.04495346649111043</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7955015561182401</v>
+        <v>0.7962244398814111</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.03303148380711102</v>
+        <v>-0.05645828517623216</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168838057962917</v>
+        <v>0.7175470189711293</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137833940251976</v>
+        <v>1.138246040130289</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.082002287076956</v>
+        <v>4.032277822357307</v>
       </c>
       <c r="E16" t="n">
-        <v>180.5503750564928</v>
+        <v>198.6724656976214</v>
       </c>
       <c r="F16" t="n">
-        <v>0.501883248931652</v>
+        <v>0.4785296626125881</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9618583134525115</v>
+        <v>0.9625879364957803</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5217850091976471</v>
+        <v>0.497128256515072</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5135620903351305</v>
+        <v>0.5148559148493914</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9855828585850943</v>
+        <v>0.9873619815641594</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.47112421947224</v>
+        <v>3.400579438246268</v>
       </c>
       <c r="E17" t="n">
-        <v>79.72606622107693</v>
+        <v>90.05633720679268</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.182206703952189</v>
+        <v>-0.2060071922995719</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7560695595561721</v>
+        <v>0.7572537739389276</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2409919849955974</v>
+        <v>-0.2720451180163895</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229776850024532</v>
+        <v>0.7238168626044065</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090625698054473</v>
+        <v>1.091994428531949</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.184297290564414</v>
+        <v>3.127239432878625</v>
       </c>
       <c r="E18" t="n">
-        <v>60.22696648918843</v>
+        <v>70.07486889535036</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4572266410074158</v>
+        <v>-0.4696911545886991</v>
       </c>
       <c r="G18" t="n">
-        <v>0.750631698053379</v>
+        <v>0.7511929865989578</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6091224793639096</v>
+        <v>-0.625260303234773</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764174431284779</v>
+        <v>0.7645922578780164</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144480725954956</v>
+        <v>1.144278400571657</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.990430060184217</v>
+        <v>2.949608058253664</v>
       </c>
       <c r="E19" t="n">
-        <v>96.64017992018361</v>
+        <v>98.17514437091604</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1306066907083261</v>
+        <v>0.1069671654656605</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4842356679894789</v>
+        <v>0.4846417844502613</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2697172045392654</v>
+        <v>0.2207138734168279</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172760917094523</v>
+        <v>0.7180405158711588</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6929983674657018</v>
+        <v>0.693298219590705</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.633347964370308</v>
+        <v>2.565113598421556</v>
       </c>
       <c r="E20" t="n">
-        <v>119.0997329586566</v>
+        <v>137.6923011212803</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3091913119138329</v>
+        <v>-0.3341469417348597</v>
       </c>
       <c r="G20" t="n">
-        <v>0.783221209335663</v>
+        <v>0.784243135975997</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3947688191131755</v>
+        <v>-0.4260756982195465</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321818854898762</v>
+        <v>0.7330134382767036</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14417512099155</v>
+        <v>1.14528333790196</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.9293397158275</v>
+        <v>569.3195440402651</v>
       </c>
       <c r="E2" t="n">
-        <v>12392.81151065961</v>
+        <v>12943.23911853171</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6359342207612297</v>
+        <v>0.632713152292623</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5019375891731342</v>
+        <v>0.5020412816014574</v>
       </c>
       <c r="H2" t="n">
-        <v>1.266958750407266</v>
+        <v>1.260281127229889</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.368641761101</v>
+        <v>222.816577085032</v>
       </c>
       <c r="E3" t="n">
-        <v>5490.521509215389</v>
+        <v>5699.88696436487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2491658660836025</v>
+        <v>0.2533196919425902</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6021974102878452</v>
+        <v>0.6020866374169849</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4137611052902126</v>
+        <v>0.4207362797974696</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909782362421141</v>
+        <v>0.8907964134817563</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068947211886858</v>
+        <v>1.068311784053863</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.81651243426753</v>
+        <v>36.76452886874831</v>
       </c>
       <c r="E4" t="n">
-        <v>1728.725834956775</v>
+        <v>382.0364811462384</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7562042270232114</v>
+        <v>-0.3452881868035144</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11699967438542</v>
+        <v>0.5654604687695873</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6769959243177756</v>
+        <v>-0.6106318759202453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J4" t="n">
         <v>266</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4734268407263782</v>
+        <v>0.7367608040783651</v>
       </c>
       <c r="N4" t="n">
-        <v>1.053552549845547</v>
+        <v>0.8298303842988218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.67066595691477</v>
+        <v>36.59080082162487</v>
       </c>
       <c r="E5" t="n">
-        <v>371.6941587543757</v>
+        <v>1814.330241940049</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3475406028128432</v>
+        <v>0.7465665886228618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5655444519461287</v>
+        <v>1.117264256106974</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.614523936388909</v>
+        <v>0.668209498820108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J5" t="n">
         <v>266</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7370331488038034</v>
+        <v>0.4736628946704516</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8304319445232865</v>
+        <v>1.054109773545606</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.73559563853456</v>
+        <v>10.7706758308424</v>
       </c>
       <c r="E6" t="n">
-        <v>190.0583237322766</v>
+        <v>196.6062422095326</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3195311724888245</v>
+        <v>-0.3140380527794325</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193673769133215</v>
+        <v>0.7190362623075586</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4441835739895189</v>
+        <v>-0.4367485608745373</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7509544023776188</v>
+        <v>0.7507227804675547</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076253522892788</v>
+        <v>1.07520421502916</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.32581747371083</v>
+        <v>10.50344370528225</v>
       </c>
       <c r="E7" t="n">
-        <v>826.1159566563948</v>
+        <v>876.4540489082533</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5238603442352328</v>
+        <v>-0.5087604643736845</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8091875498136518</v>
+        <v>0.8108453149448663</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.647390514542485</v>
+        <v>-0.6274445384299689</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6790580903560431</v>
+        <v>0.675171418592479</v>
       </c>
       <c r="N7" t="n">
-        <v>1.094728436699745</v>
+        <v>1.090467261584653</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.555080876287306</v>
+        <v>9.602255192669846</v>
       </c>
       <c r="E8" t="n">
-        <v>390.0221408881284</v>
+        <v>403.9133728300207</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3532642797343808</v>
+        <v>-0.3502668276980562</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17573521673002</v>
+        <v>1.175578428074376</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3004624465675929</v>
+        <v>-0.297952751882153</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7391371144951295</v>
+        <v>0.7390146564759339</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731349781823923</v>
+        <v>1.730474604424206</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.262039945444715</v>
+        <v>7.279034577943364</v>
       </c>
       <c r="E9" t="n">
-        <v>239.2231035044618</v>
+        <v>240.609583305259</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4041250385663624</v>
+        <v>0.407456230382409</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4837707882247094</v>
+        <v>0.4836347408744286</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8353646983303342</v>
+        <v>0.8424875137086177</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6789822578812882</v>
+        <v>0.6790015930558542</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6544076179409695</v>
+        <v>0.6541070855037412</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.757515479376679</v>
+        <v>6.777568645139681</v>
       </c>
       <c r="E10" t="n">
-        <v>246.1814769156303</v>
+        <v>252.48232223234</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2606478789649065</v>
+        <v>-0.2567231094391778</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9649710355457617</v>
+        <v>0.9647535020941361</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2701095363110987</v>
+        <v>-0.2661022829996713</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7141555834748825</v>
+        <v>0.7140489783465046</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372958447008914</v>
+        <v>1.372160572790097</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.58103083589969</v>
+        <v>6.570857589481787</v>
       </c>
       <c r="E11" t="n">
-        <v>462.0117411144421</v>
+        <v>475.8797047260851</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9494864812313419</v>
+        <v>0.9497854422137446</v>
       </c>
       <c r="G11" t="n">
-        <v>0.827186647483609</v>
+        <v>0.8271792080376786</v>
       </c>
       <c r="H11" t="n">
-        <v>1.147850348068096</v>
+        <v>1.14822209381559</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6639773951928222</v>
+        <v>0.6640298013572975</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094226149588095</v>
+        <v>1.094076653314304</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.326393493929204</v>
+        <v>6.325641648730147</v>
       </c>
       <c r="E12" t="n">
-        <v>120.2858244147099</v>
+        <v>123.7968470659059</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2816275562590831</v>
+        <v>-0.2808694804024378</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632306325362753</v>
+        <v>0.6631783612456044</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4246298986253164</v>
+        <v>-0.4235202726984322</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890940521443157</v>
+        <v>0.789106743860681</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042662192716886</v>
+        <v>1.042381446346508</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.710527798329638</v>
+        <v>4.719396609392672</v>
       </c>
       <c r="E13" t="n">
-        <v>338.2407141627378</v>
+        <v>334.4093586214278</v>
       </c>
       <c r="F13" t="n">
-        <v>1.775719344424268</v>
+        <v>1.786742425983087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8659834853401818</v>
+        <v>0.8658407671935601</v>
       </c>
       <c r="H13" t="n">
-        <v>2.050523335011079</v>
+        <v>2.063592399067134</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6032044395072048</v>
+        <v>0.6030809946118486</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040697278236597</v>
+        <v>1.040097956464667</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.529179327162871</v>
+        <v>4.546627973441211</v>
       </c>
       <c r="E14" t="n">
-        <v>124.0583820299797</v>
+        <v>126.9333475878567</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4134125111970282</v>
+        <v>-0.4090973341425282</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8564999916496132</v>
+        <v>0.8562401701711435</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4826766085552417</v>
+        <v>-0.477783393484983</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7606420101692554</v>
+        <v>0.7604084439339924</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297949963124983</v>
+        <v>1.296889875981319</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.096936629045261</v>
+        <v>4.101822959813641</v>
       </c>
       <c r="E15" t="n">
-        <v>303.4569120671786</v>
+        <v>308.2525195412063</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04495346649111043</v>
+        <v>-0.04219271997073515</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7962244398814111</v>
+        <v>0.7960972884736953</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05645828517623216</v>
+        <v>-0.05299945192832959</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7175470189711293</v>
+        <v>0.717499465489303</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138246040130289</v>
+        <v>1.137753806091993</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.032277822357307</v>
+        <v>4.009197093448595</v>
       </c>
       <c r="E16" t="n">
-        <v>198.6724656976214</v>
+        <v>200.6966106405018</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4785296626125881</v>
+        <v>0.4648387509534777</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9625879364957803</v>
+        <v>0.9630949251253322</v>
       </c>
       <c r="H16" t="n">
-        <v>0.497128256515072</v>
+        <v>0.4826510230992921</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5148559148493914</v>
+        <v>0.5151923086447219</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9873619815641594</v>
+        <v>0.9883233034872704</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.400579438246268</v>
+        <v>3.409880547151793</v>
       </c>
       <c r="E17" t="n">
-        <v>90.05633720679268</v>
+        <v>92.04841854972315</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2060071922995719</v>
+        <v>-0.2017446139519165</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7572537739389276</v>
+        <v>0.7569838597162832</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2720451180163895</v>
+        <v>-0.2665111169312515</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7238168626044065</v>
+        <v>0.7237596598004088</v>
       </c>
       <c r="N17" t="n">
-        <v>1.091994428531949</v>
+        <v>1.091293486931986</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.127239432878625</v>
+        <v>3.136310907206709</v>
       </c>
       <c r="E18" t="n">
-        <v>70.07486889535036</v>
+        <v>72.10327748677227</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4696911545886991</v>
+        <v>-0.4661378855975322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7511929865989578</v>
+        <v>0.7509819991322213</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.625260303234773</v>
+        <v>-0.6207044724589489</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645922578780164</v>
+        <v>0.7643052702555341</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144278400571657</v>
+        <v>1.143291440044255</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.949608058253664</v>
+        <v>2.966579394779276</v>
       </c>
       <c r="E19" t="n">
-        <v>98.17514437091604</v>
+        <v>99.49609470619347</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1069671654656605</v>
+        <v>0.1164067124195427</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4846417844502613</v>
+        <v>0.4844012853698449</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2207138734168279</v>
+        <v>0.2403104944914939</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7180405158711588</v>
+        <v>0.7174247163644455</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693298219590705</v>
+        <v>0.6922168903212066</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.565113598421556</v>
+        <v>2.568489043839325</v>
       </c>
       <c r="E20" t="n">
-        <v>137.6923011212803</v>
+        <v>140.1097717536239</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341469417348597</v>
+        <v>-0.33110455915953</v>
       </c>
       <c r="G20" t="n">
-        <v>0.784243135975997</v>
+        <v>0.784054399454307</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4260756982195465</v>
+        <v>-0.4222979418136994</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7330134382767036</v>
+        <v>0.732899250539802</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14528333790196</v>
+        <v>1.144592890667236</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.3195440402651</v>
+        <v>567.1903083646077</v>
       </c>
       <c r="E2" t="n">
-        <v>12943.23911853171</v>
+        <v>13394.85718207355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.632713152292623</v>
+        <v>0.6256794714264575</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5020412816014574</v>
+        <v>0.5022861967530432</v>
       </c>
       <c r="H2" t="n">
-        <v>1.260281127229889</v>
+        <v>1.245663280159941</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.816577085032</v>
+        <v>222.200713005572</v>
       </c>
       <c r="E3" t="n">
-        <v>5699.88696436487</v>
+        <v>5863.424854367889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2533196919425902</v>
+        <v>0.2490546543387164</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6020866374169849</v>
+        <v>0.6022005510178963</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4207362797974696</v>
+        <v>0.4135742717567108</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907964134817563</v>
+        <v>0.8908021928688569</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068311784053863</v>
+        <v>1.067999827312248</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.76452886874831</v>
+        <v>36.64028683065106</v>
       </c>
       <c r="E4" t="n">
-        <v>382.0364811462384</v>
+        <v>399.191553860784</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3452881868035144</v>
+        <v>-0.3494160067235528</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5654604687695873</v>
+        <v>0.5656256177622272</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6106318759202453</v>
+        <v>-0.6177513813924129</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7367608040783651</v>
+        <v>0.7370502402822007</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8298303842988218</v>
+        <v>0.8299939360794149</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.59080082162487</v>
+        <v>36.41278404038973</v>
       </c>
       <c r="E5" t="n">
-        <v>1814.330241940049</v>
+        <v>1922.073772022955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7465665886228618</v>
+        <v>0.7321371478654011</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117264256106974</v>
+        <v>1.11769365788235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.668209498820108</v>
+        <v>0.6550427683848118</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736628946704516</v>
+        <v>0.4741170640495141</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054109773545606</v>
+        <v>1.055011344145067</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.7706758308424</v>
+        <v>10.76621342741615</v>
       </c>
       <c r="E6" t="n">
-        <v>196.6062422095326</v>
+        <v>1054.251053108911</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3140380527794325</v>
+        <v>-0.5076897721815923</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7190362623075586</v>
+        <v>0.8109975552152507</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4367485608745373</v>
+        <v>-0.6260065383882001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J6" t="n">
         <v>266</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7507227804675547</v>
+        <v>0.673995933420158</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07520421502916</v>
+        <v>1.088242236721304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.50344370528225</v>
+        <v>10.73401162128982</v>
       </c>
       <c r="E7" t="n">
-        <v>876.4540489082533</v>
+        <v>203.7533533819409</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5087604643736845</v>
+        <v>-0.3189214176975504</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8108453149448663</v>
+        <v>0.719327600142371</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6274445384299689</v>
+        <v>-0.4433604627911243</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J7" t="n">
         <v>266</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.675171418592479</v>
+        <v>0.7509659015844995</v>
       </c>
       <c r="N7" t="n">
-        <v>1.090467261584653</v>
+        <v>1.075463556967151</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.602255192669846</v>
+        <v>9.532609695153774</v>
       </c>
       <c r="E8" t="n">
-        <v>403.9133728300207</v>
+        <v>415.7978792970117</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3502668276980562</v>
+        <v>-0.3592478857407406</v>
       </c>
       <c r="G8" t="n">
-        <v>1.175578428074376</v>
+        <v>1.176084771669703</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.297952751882153</v>
+        <v>-0.3054608769661321</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7390146564759339</v>
+        <v>0.7393141336133768</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730474604424206</v>
+        <v>1.731077022708577</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.279034577943364</v>
+        <v>7.243433144225708</v>
       </c>
       <c r="E9" t="n">
-        <v>240.609583305259</v>
+        <v>242.0977873286141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.407456230382409</v>
+        <v>0.3958064361738709</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4836347408744286</v>
+        <v>0.4841452279034419</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8424875137086177</v>
+        <v>0.8175365848133705</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6790015930558542</v>
+        <v>0.6794553983676203</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6541070855037412</v>
+        <v>0.6549156453420346</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.777568645139681</v>
+        <v>6.741677034846178</v>
       </c>
       <c r="E10" t="n">
-        <v>252.48232223234</v>
+        <v>259.3183810871328</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2567231094391778</v>
+        <v>-0.2640074764300814</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9647535020941361</v>
+        <v>0.9651727228194259</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2661022829996713</v>
+        <v>-0.2735339180109367</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7140489783465046</v>
+        <v>0.7143321246275918</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372160572790097</v>
+        <v>1.372631551854448</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.570857589481787</v>
+        <v>6.552805586663439</v>
       </c>
       <c r="E11" t="n">
-        <v>475.8797047260851</v>
+        <v>495.6841947957664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9497854422137446</v>
+        <v>0.939627749871232</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8271792080376786</v>
+        <v>0.8274426844654238</v>
       </c>
       <c r="H11" t="n">
-        <v>1.14822209381559</v>
+        <v>1.135580466794853</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6640298013572975</v>
+        <v>0.6642873138929227</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094076653314304</v>
+        <v>1.09431571446136</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.325641648730147</v>
+        <v>6.45874307103416</v>
       </c>
       <c r="E12" t="n">
-        <v>123.7968470659059</v>
+        <v>125.7668466322481</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2808694804024378</v>
+        <v>-0.2823854151986434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6631783612456044</v>
+        <v>0.6632840230263736</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4235202726984322</v>
+        <v>-0.4257383042489101</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789106743860681</v>
+        <v>0.7892089692531572</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042381446346508</v>
+        <v>1.042174169862971</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.719396609392672</v>
+        <v>4.701057376394826</v>
       </c>
       <c r="E13" t="n">
-        <v>334.4093586214278</v>
+        <v>290.5601319988635</v>
       </c>
       <c r="F13" t="n">
-        <v>1.786742425983087</v>
+        <v>1.769425764453139</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8658407671935601</v>
+        <v>0.8660705506961682</v>
       </c>
       <c r="H13" t="n">
-        <v>2.063592399067134</v>
+        <v>2.043050376243404</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6030809946118486</v>
+        <v>0.6033518622519504</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040097956464667</v>
+        <v>1.040333743953197</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.546627973441211</v>
+        <v>4.526100922037779</v>
       </c>
       <c r="E14" t="n">
-        <v>126.9333475878567</v>
+        <v>130.4285243174117</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4090973341425282</v>
+        <v>-0.4127965827589142</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8562401701711435</v>
+        <v>0.8564602933095871</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.477783393484983</v>
+        <v>-0.4819798255488996</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7604084439339924</v>
+        <v>0.7605589809874408</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296889875981319</v>
+        <v>1.296847439062733</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.101822959813641</v>
+        <v>4.089256194564032</v>
       </c>
       <c r="E15" t="n">
-        <v>308.2525195412063</v>
+        <v>311.9304071928688</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04219271997073515</v>
+        <v>-0.04529840778784988</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7960972884736953</v>
+        <v>0.796240823847482</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05299945192832959</v>
+        <v>-0.05689033572652723</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.717499465489303</v>
+        <v>0.7176327836596852</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137753806091993</v>
+        <v>1.137615412438044</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.009197093448595</v>
+        <v>3.957043077892993</v>
       </c>
       <c r="E16" t="n">
-        <v>200.6966106405018</v>
+        <v>206.3299475668613</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4648387509534777</v>
+        <v>0.4443673415536176</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9630949251253322</v>
+        <v>0.9639632243573716</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4826510230992921</v>
+        <v>0.4609795584783394</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5151923086447219</v>
+        <v>0.5158256074529085</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9883233034872704</v>
+        <v>0.989947402458443</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.409880547151793</v>
+        <v>3.389469423476913</v>
       </c>
       <c r="E17" t="n">
-        <v>92.04841854972315</v>
+        <v>93.27071848007586</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2017446139519165</v>
+        <v>-0.2091538110536131</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569838597162832</v>
+        <v>0.7574693279091695</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2665111169312515</v>
+        <v>-0.2761218221613501</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7237596598004088</v>
+        <v>0.7240852724107839</v>
       </c>
       <c r="N17" t="n">
-        <v>1.091293486931986</v>
+        <v>1.091951935345716</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.136310907206709</v>
+        <v>3.139795045457254</v>
       </c>
       <c r="E18" t="n">
-        <v>72.10327748677227</v>
+        <v>73.88148268614391</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4661378855975322</v>
+        <v>-0.4662995373844766</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7509819991322213</v>
+        <v>0.7509907114787703</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6207044724589489</v>
+        <v>-0.6209125229608894</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643052702555341</v>
+        <v>0.7641928101992054</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143291440044255</v>
+        <v>1.14257908329627</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.966579394779276</v>
+        <v>2.974603581362296</v>
       </c>
       <c r="E19" t="n">
-        <v>99.49609470619347</v>
+        <v>100.6674539300742</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1164067124195427</v>
+        <v>0.1220808610717241</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4844012853698449</v>
+        <v>0.484306924680697</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2403104944914939</v>
+        <v>0.2520733337691008</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174247163644455</v>
+        <v>0.7167659719138046</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6922168903212066</v>
+        <v>0.6911094229093856</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568489043839325</v>
+        <v>2.566019562491107</v>
       </c>
       <c r="E20" t="n">
-        <v>140.1097717536239</v>
+        <v>136.5898755675067</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.33110455915953</v>
+        <v>-0.3341469417348597</v>
       </c>
       <c r="G20" t="n">
-        <v>0.784054399454307</v>
+        <v>0.784243135975997</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4222979418136994</v>
+        <v>-0.4260756982195465</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732899250539802</v>
+        <v>0.7330512694270508</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144592890667236</v>
+        <v>1.144547531035</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.1903083646077</v>
+        <v>567.9551466825387</v>
       </c>
       <c r="E2" t="n">
-        <v>13394.85718207355</v>
+        <v>13749.69609061166</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6256794714264575</v>
+        <v>0.6280819677220346</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5022861967530432</v>
+        <v>0.502199686955193</v>
       </c>
       <c r="H2" t="n">
-        <v>1.245663280159941</v>
+        <v>1.250661806521741</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.200713005572</v>
+        <v>222.6871976591443</v>
       </c>
       <c r="E3" t="n">
-        <v>5863.424854367889</v>
+        <v>6003.90550818181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2490546543387164</v>
+        <v>0.2522252410913655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022005510178963</v>
+        <v>0.6021145893946901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4135742717567108</v>
+        <v>0.418899069270069</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908021928688569</v>
+        <v>0.8907350833731323</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067999827312248</v>
+        <v>1.067950862805915</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.64028683065106</v>
+        <v>36.70878376567256</v>
       </c>
       <c r="E4" t="n">
-        <v>399.191553860784</v>
+        <v>407.6941289020384</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3494160067235528</v>
+        <v>-0.3471653463794985</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5656256177622272</v>
+        <v>0.5655294382394525</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6177513813924129</v>
+        <v>-0.6138767019100855</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370502402822007</v>
+        <v>0.7368594864581887</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8299939360794149</v>
+        <v>0.8297809462300417</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.41278404038973</v>
+        <v>36.65864869286036</v>
       </c>
       <c r="E5" t="n">
-        <v>1922.073772022955</v>
+        <v>1980.514412911345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7321371478654011</v>
+        <v>0.7458787365814061</v>
       </c>
       <c r="G5" t="n">
-        <v>1.11769365788235</v>
+        <v>1.117283818896502</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6550427683848118</v>
+        <v>0.6675821523291025</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4741170640495141</v>
+        <v>0.4738138291246633</v>
       </c>
       <c r="N5" t="n">
-        <v>1.055011344145067</v>
+        <v>1.054131530148905</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.76621342741615</v>
+        <v>10.76075593587865</v>
       </c>
       <c r="E6" t="n">
-        <v>1054.251053108911</v>
+        <v>206.2492769168666</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5076897721815923</v>
+        <v>-0.3170912649539506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8109975552152507</v>
+        <v>0.7192127480493791</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6260065383882001</v>
+        <v>-0.4408866024885588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J6" t="n">
         <v>266</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.673995933420158</v>
+        <v>0.750871085819654</v>
       </c>
       <c r="N6" t="n">
-        <v>1.088242236721304</v>
+        <v>1.075341285729151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.73401162128982</v>
+        <v>10.68882031084767</v>
       </c>
       <c r="E7" t="n">
-        <v>203.7533533819409</v>
+        <v>1145.453808678887</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3189214176975504</v>
+        <v>-0.5038479400694775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.719327600142371</v>
+        <v>0.8115811000885006</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4433604627911243</v>
+        <v>-0.6208226633352284</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J7" t="n">
         <v>266</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7509659015844995</v>
+        <v>0.673219141303065</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075463556967151</v>
+        <v>1.087957530622924</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.532609695153774</v>
+        <v>9.55569339123999</v>
       </c>
       <c r="E8" t="n">
-        <v>415.7978792970117</v>
+        <v>422.8967580082952</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3592478857407406</v>
+        <v>-0.3570058016237638</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176084771669703</v>
+        <v>1.175948068886341</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3054608769661321</v>
+        <v>-0.3035897681790143</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7393141336133768</v>
+        <v>0.7392394519903861</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731077022708577</v>
+        <v>1.730999099747054</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.243433144225708</v>
+        <v>7.262948656823051</v>
       </c>
       <c r="E9" t="n">
-        <v>242.0977873286141</v>
+        <v>230.0612469314395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3958064361738709</v>
+        <v>0.4012714362106762</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4841452279034419</v>
+        <v>0.4838936471799128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8175365848133705</v>
+        <v>0.8292554336045715</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6794553983676203</v>
+        <v>0.6792639601872787</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6549156453420346</v>
+        <v>0.654503624018029</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.741677034846178</v>
+        <v>6.767709097073414</v>
       </c>
       <c r="E10" t="n">
-        <v>259.3183810871328</v>
+        <v>264.8706461059537</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2640074764300814</v>
+        <v>-0.25868619869854</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9651727228194259</v>
+        <v>0.9648598761705988</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2735339180109367</v>
+        <v>-0.26810753052063</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7143321246275918</v>
+        <v>0.7141264168677641</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372631551854448</v>
+        <v>1.372027789038946</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.552805586663439</v>
+        <v>6.550162464199346</v>
       </c>
       <c r="E11" t="n">
-        <v>495.6841947957664</v>
+        <v>501.8794621248427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.939627749871232</v>
+        <v>0.940523437791849</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8274426844654238</v>
+        <v>0.8274185635464038</v>
       </c>
       <c r="H11" t="n">
-        <v>1.135580466794853</v>
+        <v>1.136696080108072</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6642873138929227</v>
+        <v>0.6642330171723688</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09431571446136</v>
+        <v>1.094382858462218</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.45874307103416</v>
+        <v>6.449422062147036</v>
       </c>
       <c r="E12" t="n">
-        <v>125.7668466322481</v>
+        <v>128.8959933854009</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2823854151986434</v>
+        <v>-0.2840898041666079</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632840230263736</v>
+        <v>0.6634082422931938</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4257383042489101</v>
+        <v>-0.428227727748149</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7892089692531572</v>
+        <v>0.7892506181661185</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042174169862971</v>
+        <v>1.042603926141271</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.701057376394826</v>
+        <v>4.703722838174103</v>
       </c>
       <c r="E13" t="n">
-        <v>290.5601319988635</v>
+        <v>279.7743765437344</v>
       </c>
       <c r="F13" t="n">
-        <v>1.769425764453139</v>
+        <v>1.766280428040206</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8660705506961682</v>
+        <v>0.866115586198097</v>
       </c>
       <c r="H13" t="n">
-        <v>2.043050376243404</v>
+        <v>2.039312600057776</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033518622519504</v>
+        <v>0.6033841258003048</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040333743953197</v>
+        <v>1.040622703268997</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.526100922037779</v>
+        <v>4.538064977739108</v>
       </c>
       <c r="E14" t="n">
-        <v>130.4285243174117</v>
+        <v>131.3295928301198</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4127965827589142</v>
+        <v>-0.4103311170244239</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8564602933095871</v>
+        <v>0.8563101024858599</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4819798255488996</v>
+        <v>-0.4791851875076992</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7605589809874408</v>
+        <v>0.7604320062051098</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296847439062733</v>
+        <v>1.296626871902299</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.089256194564032</v>
+        <v>4.106504939957189</v>
       </c>
       <c r="E15" t="n">
-        <v>311.9304071928688</v>
+        <v>313.7964348473743</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04529840778784988</v>
+        <v>-0.03908429838098848</v>
       </c>
       <c r="G15" t="n">
-        <v>0.796240823847482</v>
+        <v>0.7959625767750664</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05689033572652723</v>
+        <v>-0.04910318590522558</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7176327836596852</v>
+        <v>0.7174058320293847</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137615412438044</v>
+        <v>1.137054063330226</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.957043077892993</v>
+        <v>3.984490773101524</v>
       </c>
       <c r="E16" t="n">
-        <v>206.3299475668613</v>
+        <v>206.1674373800192</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4443673415536176</v>
+        <v>0.4539109406024837</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9639632243573716</v>
+        <v>0.9635419341593063</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4609795584783394</v>
+        <v>0.4710858183858107</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158256074529085</v>
+        <v>0.5155589654185249</v>
       </c>
       <c r="N16" t="n">
-        <v>0.989947402458443</v>
+        <v>0.9891736208048618</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.389469423476913</v>
+        <v>3.393084896337106</v>
       </c>
       <c r="E17" t="n">
-        <v>93.27071848007586</v>
+        <v>92.44717588795845</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2091538110536131</v>
+        <v>-0.2102635728138735</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7574693279091695</v>
+        <v>0.7575486609554525</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2761218221613501</v>
+        <v>-0.2775578436752567</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7240852724107839</v>
+        <v>0.7240720152284941</v>
       </c>
       <c r="N17" t="n">
-        <v>1.091951935345716</v>
+        <v>1.09223442351648</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.139795045457254</v>
+        <v>3.13986135408437</v>
       </c>
       <c r="E18" t="n">
-        <v>73.88148268614391</v>
+        <v>74.75982928736177</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4662995373844766</v>
+        <v>-0.4675115023866554</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7509907114787703</v>
+        <v>0.751058719860259</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6209125229608894</v>
+        <v>-0.6224699747492979</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641928101992054</v>
+        <v>0.7643459101950747</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14257908329627</v>
+        <v>1.143108360584774</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.974603581362296</v>
+        <v>2.964797538594926</v>
       </c>
       <c r="E19" t="n">
-        <v>100.6674539300742</v>
+        <v>104.4147363846019</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1220808610717241</v>
+        <v>0.1126282851497467</v>
       </c>
       <c r="G19" t="n">
-        <v>0.484306924680697</v>
+        <v>0.48448500570536</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2520733337691008</v>
+        <v>0.2324701153253887</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7167659719138046</v>
+        <v>0.7176084234219164</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6911094229093856</v>
+        <v>0.6922953760160379</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.566019562491107</v>
+        <v>2.568293010235193</v>
       </c>
       <c r="E20" t="n">
-        <v>136.5898755675067</v>
+        <v>137.3630597397741</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341469417348597</v>
+        <v>-0.3326262206779702</v>
       </c>
       <c r="G20" t="n">
-        <v>0.784243135975997</v>
+        <v>0.7841465523743212</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4260756982195465</v>
+        <v>-0.4241888454024438</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7330512694270508</v>
+        <v>0.7329731902421531</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144547531035</v>
+        <v>1.144481796864347</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.9551466825387</v>
+        <v>567.2717655942369</v>
       </c>
       <c r="E2" t="n">
-        <v>13749.69609061166</v>
+        <v>14010.70026302124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6280819677220346</v>
+        <v>0.6240897989272098</v>
       </c>
       <c r="G2" t="n">
-        <v>0.502199686955193</v>
+        <v>0.5023450674125842</v>
       </c>
       <c r="H2" t="n">
-        <v>1.250661806521741</v>
+        <v>1.242352795741965</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.6871976591443</v>
+        <v>222.4080097790519</v>
       </c>
       <c r="E3" t="n">
-        <v>6003.90550818181</v>
+        <v>6090.40144057185</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2522252410913655</v>
+        <v>0.2493419568386281</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6021145893946901</v>
+        <v>0.6021924559854884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.418899069270069</v>
+        <v>0.4140569254235838</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907350833731323</v>
+        <v>0.8907544921107259</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067950862805915</v>
+        <v>1.067803129922456</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.70878376567256</v>
+        <v>36.64854320705675</v>
       </c>
       <c r="E4" t="n">
-        <v>407.6941289020384</v>
+        <v>414.2303407421546</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3471653463794985</v>
+        <v>-0.3486660208721484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5655294382394525</v>
+        <v>0.5655919321166144</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6138767019100855</v>
+        <v>-0.6164621542024754</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7368594864581887</v>
+        <v>0.7369399072375362</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8297809462300417</v>
+        <v>0.8297230191492774</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.65864869286036</v>
+        <v>36.52620870833372</v>
       </c>
       <c r="E5" t="n">
-        <v>1980.514412911345</v>
+        <v>2004.805165920136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458787365814061</v>
+        <v>0.7420968644746844</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117283818896502</v>
+        <v>1.117392996436376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6675821523291025</v>
+        <v>0.6641323749490128</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738138291246633</v>
+        <v>0.4739953780860656</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054131530148905</v>
+        <v>1.054333266462793</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.76075593587865</v>
+        <v>10.74039648385111</v>
       </c>
       <c r="E6" t="n">
-        <v>206.2492769168666</v>
+        <v>206.7829689211976</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3170912649539506</v>
+        <v>-0.3173963829055477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7192127480493791</v>
+        <v>0.7192314234961007</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4408866024885588</v>
+        <v>-0.4412993822804914</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.750871085819654</v>
+        <v>0.7508757313584544</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075341285729151</v>
+        <v>1.075064644140443</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.68882031084767</v>
+        <v>10.64164264701577</v>
       </c>
       <c r="E7" t="n">
-        <v>1145.453808678887</v>
+        <v>1172.009278011537</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5038479400694775</v>
+        <v>-0.5084036372328833</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8115811000885006</v>
+        <v>0.8108955468808543</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6208226633352284</v>
+        <v>-0.6269656297762153</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.673219141303065</v>
+        <v>0.6739925788235945</v>
       </c>
       <c r="N7" t="n">
-        <v>1.087957530622924</v>
+        <v>1.087972424241832</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.55569339123999</v>
+        <v>9.486215709273342</v>
       </c>
       <c r="E8" t="n">
-        <v>422.8967580082952</v>
+        <v>430.1110676274357</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3570058016237638</v>
+        <v>-0.3607414276350116</v>
       </c>
       <c r="G8" t="n">
-        <v>1.175948068886341</v>
+        <v>1.176179651879046</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3035897681790143</v>
+        <v>-0.3067060606419239</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7392394519903861</v>
+        <v>0.7393656176819965</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730999099747054</v>
+        <v>1.731134336195855</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.262948656823051</v>
+        <v>7.261062367875469</v>
       </c>
       <c r="E9" t="n">
-        <v>230.0612469314395</v>
+        <v>230.1358627454167</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4012714362106762</v>
+        <v>0.4034114903718926</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4838936471799128</v>
+        <v>0.4838009625529851</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8292554336045715</v>
+        <v>0.8338377175669873</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6792639601872787</v>
+        <v>0.6793075959125008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654503624018029</v>
+        <v>0.6542309063863004</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.767709097073414</v>
+        <v>6.73762718842238</v>
       </c>
       <c r="E10" t="n">
-        <v>264.8706461059537</v>
+        <v>267.2268654482675</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.25868619869854</v>
+        <v>-0.2624681760944916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9648598761705988</v>
+        <v>0.9650785383168493</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.26810753052063</v>
+        <v>-0.2719656128217821</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7141264168677641</v>
+        <v>0.7142792381772384</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372027789038946</v>
+        <v>1.372235158355798</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.550162464199346</v>
+        <v>6.543528988608327</v>
       </c>
       <c r="E11" t="n">
-        <v>501.8794621248427</v>
+        <v>513.757332425231</v>
       </c>
       <c r="F11" t="n">
-        <v>0.940523437791849</v>
+        <v>0.9387321741222354</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8274185635464038</v>
+        <v>0.8274669742922232</v>
       </c>
       <c r="H11" t="n">
-        <v>1.136696080108072</v>
+        <v>1.134464822508697</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6642330171723688</v>
+        <v>0.6643269500515534</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094382858462218</v>
+        <v>1.094284878980319</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.449422062147036</v>
+        <v>6.431542664749114</v>
       </c>
       <c r="E12" t="n">
-        <v>128.8959933854009</v>
+        <v>131.4819857280323</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2840898041666079</v>
+        <v>-0.2874952812949587</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634082422931938</v>
+        <v>0.6636736616672905</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.428227727748149</v>
+        <v>-0.4331877214664643</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7892506181661185</v>
+        <v>0.789402496660074</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042603926141271</v>
+        <v>1.042919856237784</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.703722838174103</v>
+        <v>4.6885381445908</v>
       </c>
       <c r="E13" t="n">
-        <v>279.7743765437344</v>
+        <v>277.4788883001602</v>
       </c>
       <c r="F13" t="n">
-        <v>1.766280428040206</v>
+        <v>1.759992664879897</v>
       </c>
       <c r="G13" t="n">
-        <v>0.866115586198097</v>
+        <v>0.8662086620684837</v>
       </c>
       <c r="H13" t="n">
-        <v>2.039312600057776</v>
+        <v>2.031834524347841</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033841258003048</v>
+        <v>0.6035003032211018</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040622703268997</v>
+        <v>1.040633668214613</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.538064977739108</v>
+        <v>4.525649972499776</v>
       </c>
       <c r="E14" t="n">
-        <v>131.3295928301198</v>
+        <v>133.0247500906884</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4103311170244239</v>
+        <v>-0.4127965827589142</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8563101024858599</v>
+        <v>0.8564602933095871</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4791851875076992</v>
+        <v>-0.4819798255488996</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7604320062051098</v>
+        <v>0.7605430645647927</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296626871902299</v>
+        <v>1.296668323044864</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.106504939957189</v>
+        <v>4.094256437910102</v>
       </c>
       <c r="E15" t="n">
-        <v>313.7964348473743</v>
+        <v>316.3002560589715</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03908429838098848</v>
+        <v>-0.04305568542546356</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7959625767750664</v>
+        <v>0.7961362745184881</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.04910318590522558</v>
+        <v>-0.05408079848076777</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174058320293847</v>
+        <v>0.7175541726266088</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137054063330226</v>
+        <v>1.137208151963301</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.984490773101524</v>
+        <v>3.959247763389542</v>
       </c>
       <c r="E16" t="n">
-        <v>206.1674373800192</v>
+        <v>207.2584727340307</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4539109406024837</v>
+        <v>0.4457296687544701</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9635419341593063</v>
+        <v>0.9639013182434829</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4710858183858107</v>
+        <v>0.4624225118466723</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5155589654185249</v>
+        <v>0.5158745527249324</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9891736208048618</v>
+        <v>0.9898617378309563</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.393084896337106</v>
+        <v>3.346400650107429</v>
       </c>
       <c r="E17" t="n">
-        <v>92.44717588795845</v>
+        <v>108.4672690152193</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2102635728138735</v>
+        <v>-0.2226271272930453</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7575486609554525</v>
+        <v>0.7585497275636498</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2775578436752567</v>
+        <v>-0.2934904848072267</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7240720152284941</v>
+        <v>0.7244281073221879</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09223442351648</v>
+        <v>1.093898953321205</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.13986135408437</v>
+        <v>3.124989108826691</v>
       </c>
       <c r="E18" t="n">
-        <v>74.75982928736177</v>
+        <v>75.29263321976097</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4675115023866554</v>
+        <v>-0.4697718358633503</v>
       </c>
       <c r="G18" t="n">
-        <v>0.751058719860259</v>
+        <v>0.7511982519924409</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6224699747492979</v>
+        <v>-0.6253633240191264</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643459101950747</v>
+        <v>0.7644788426179537</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143108360584774</v>
+        <v>1.14318863170632</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.964797538594926</v>
+        <v>2.961915649107912</v>
       </c>
       <c r="E19" t="n">
-        <v>104.4147363846019</v>
+        <v>104.7121945252457</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1126282851497467</v>
+        <v>0.1145170644866114</v>
       </c>
       <c r="G19" t="n">
-        <v>0.48448500570536</v>
+        <v>0.4844410648645057</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2324701153253887</v>
+        <v>0.2363900849706886</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176084234219164</v>
+        <v>0.7173793035080103</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6922953760160379</v>
+        <v>0.6918112991398153</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568293010235193</v>
+        <v>2.564565461794216</v>
       </c>
       <c r="E20" t="n">
-        <v>137.3630597397741</v>
+        <v>138.4405510987041</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3326262206779702</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7329731902421531</v>
+        <v>0.7329644411867965</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144481796864347</v>
+        <v>1.144136922713216</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.2717655942369</v>
+        <v>565.1978468996783</v>
       </c>
       <c r="E2" t="n">
-        <v>14010.70026302124</v>
+        <v>14413.33958603742</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6240897989272098</v>
+        <v>0.6159357193918902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5023450674125842</v>
+        <v>0.5026674597951427</v>
       </c>
       <c r="H2" t="n">
-        <v>1.242352795741965</v>
+        <v>1.225334378403784</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.4080097790519</v>
+        <v>222.0011823129019</v>
       </c>
       <c r="E3" t="n">
-        <v>6090.40144057185</v>
+        <v>6190.834330826448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2493419568386281</v>
+        <v>0.245997384177989</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6021924559854884</v>
+        <v>0.6022904692411151</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4140569254235838</v>
+        <v>0.4084364550678434</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907544921107259</v>
+        <v>0.8906885839167858</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067803129922456</v>
+        <v>1.067212994796941</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.64854320705675</v>
+        <v>36.59230965208134</v>
       </c>
       <c r="E4" t="n">
-        <v>414.2303407421546</v>
+        <v>418.3878717138805</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3486660208721484</v>
+        <v>-0.3509152750188053</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5655919321166144</v>
+        <v>0.5656978650153378</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6164621542024754</v>
+        <v>-0.620322784865541</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7369399072375362</v>
+        <v>0.7370287373494864</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8297230191492774</v>
+        <v>0.8294461378969561</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.52620870833372</v>
+        <v>36.45231422991905</v>
       </c>
       <c r="E5" t="n">
-        <v>2004.805165920136</v>
+        <v>2029.455498742668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7420968644746844</v>
+        <v>0.7307646100318694</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117392996436376</v>
+        <v>1.117736587770073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6641323749490128</v>
+        <v>0.6537896477825539</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4739953780860656</v>
+        <v>0.4744516882133983</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054333266462793</v>
+        <v>1.054995704837385</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.74039648385111</v>
+        <v>10.71104071227342</v>
       </c>
       <c r="E6" t="n">
-        <v>206.7829689211976</v>
+        <v>209.7817124841683</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3173963829055477</v>
+        <v>-0.3234909644461372</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7192314234961007</v>
+        <v>0.7196441079608846</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4412993822804914</v>
+        <v>-0.4495151990652027</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7508757313584544</v>
+        <v>0.7512213604555482</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075064644140443</v>
+        <v>1.075486418091428</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.64164264701577</v>
+        <v>10.57059791940747</v>
       </c>
       <c r="E7" t="n">
-        <v>1172.009278011537</v>
+        <v>1208.5608777109</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5084036372328833</v>
+        <v>-0.5108999503585144</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8108955468808543</v>
+        <v>0.8105547405340563</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6269656297762153</v>
+        <v>-0.6303090029698598</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6739925788235945</v>
+        <v>0.6736626497526579</v>
       </c>
       <c r="N7" t="n">
-        <v>1.087972424241832</v>
+        <v>1.086285661897199</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.486215709273342</v>
+        <v>9.473325619756904</v>
       </c>
       <c r="E8" t="n">
-        <v>430.1110676274357</v>
+        <v>438.856384058101</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3607414276350116</v>
+        <v>-0.3648437877205097</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176179651879046</v>
+        <v>1.17645601405859</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3067060606419239</v>
+        <v>-0.3101210613577089</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7393656176819965</v>
+        <v>0.7394999771108012</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731134336195855</v>
+        <v>1.730745005500749</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.261062367875469</v>
+        <v>7.260488601602943</v>
       </c>
       <c r="E9" t="n">
-        <v>230.1358627454167</v>
+        <v>230.9513639252051</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4034114903718926</v>
+        <v>0.4024602458318987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4838009625529851</v>
+        <v>0.4838417554755938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8338377175669873</v>
+        <v>0.8318013922471389</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6793075959125008</v>
+        <v>0.6795052905575221</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6542309063863004</v>
+        <v>0.6540567252399694</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.73762718842238</v>
+        <v>6.738154755074584</v>
       </c>
       <c r="E10" t="n">
-        <v>267.2268654482675</v>
+        <v>268.8139835328638</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2624681760944916</v>
+        <v>-0.2645670056763917</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9650785383168493</v>
+        <v>0.9652077035077554</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2719656128217821</v>
+        <v>-0.2741037029800974</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7142792381772384</v>
+        <v>0.7143723913721726</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372235158355798</v>
+        <v>1.371717468257612</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.543528988608327</v>
+        <v>6.545422703548801</v>
       </c>
       <c r="E11" t="n">
-        <v>513.757332425231</v>
+        <v>521.209582190588</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9387321741222354</v>
+        <v>0.9342559787816793</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8274669742922232</v>
+        <v>0.8275909565187601</v>
       </c>
       <c r="H11" t="n">
-        <v>1.134464822508697</v>
+        <v>1.128886162206995</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643269500515534</v>
+        <v>0.6645219242517941</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094284878980319</v>
+        <v>1.094067905536112</v>
       </c>
     </row>
     <row r="12">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.431542664749114</v>
+        <v>6.259714059981445</v>
       </c>
       <c r="E12" t="n">
-        <v>131.4819857280323</v>
+        <v>133.8443997470289</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2874952812949587</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789402496660074</v>
+        <v>0.7894817187697555</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042919856237784</v>
+        <v>1.042355563116904</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.6885381445908</v>
+        <v>4.698102477429143</v>
       </c>
       <c r="E13" t="n">
-        <v>277.4788883001602</v>
+        <v>273.9845384960166</v>
       </c>
       <c r="F13" t="n">
-        <v>1.759992664879897</v>
+        <v>1.766280428040206</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8662086620684837</v>
+        <v>0.866115586198097</v>
       </c>
       <c r="H13" t="n">
-        <v>2.031834524347841</v>
+        <v>2.039312600057776</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6035003032211018</v>
+        <v>0.6034202157887328</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040633668214613</v>
+        <v>1.039716503898291</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.525649972499776</v>
+        <v>4.527149211130435</v>
       </c>
       <c r="E14" t="n">
-        <v>133.0247500906884</v>
+        <v>134.2053636277265</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4127965827589142</v>
+        <v>-0.4134125111970282</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8564602933095871</v>
+        <v>0.8564999916496132</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4819798255488996</v>
+        <v>-0.4826766085552417</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7605430645647927</v>
+        <v>0.7604780300160837</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296668323044864</v>
+        <v>1.295785938926584</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.094256437910102</v>
+        <v>4.099998667883153</v>
       </c>
       <c r="E15" t="n">
-        <v>316.3002560589715</v>
+        <v>318.3567654136871</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04305568542546356</v>
+        <v>-0.04184747472101114</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7961362745184881</v>
+        <v>0.7960818846856746</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05408079848076777</v>
+        <v>-0.05256679686604628</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7175541726266088</v>
+        <v>0.7174749111455776</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137208151963301</v>
+        <v>1.136275619894379</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.959247763389542</v>
+        <v>3.975192141397437</v>
       </c>
       <c r="E16" t="n">
-        <v>207.2584727340307</v>
+        <v>207.6125968290982</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4457296687544701</v>
+        <v>0.4498187394397628</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9639013182434829</v>
+        <v>0.9637190428533403</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4624225118466723</v>
+        <v>0.4667529844672963</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158745527249324</v>
+        <v>0.5161292058033023</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898617378309563</v>
+        <v>0.9895280359069298</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.346400650107429</v>
+        <v>3.345424375784122</v>
       </c>
       <c r="E17" t="n">
-        <v>108.4672690152193</v>
+        <v>110.0363029122565</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2226271272930453</v>
+        <v>-0.2244678886903808</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7585497275636498</v>
+        <v>0.7587172439234741</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2934904848072267</v>
+        <v>-0.2958518347752501</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244281073221879</v>
+        <v>0.7247250014463449</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093898953321205</v>
+        <v>1.093886912679602</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.124989108826691</v>
+        <v>3.126996590830752</v>
       </c>
       <c r="E18" t="n">
-        <v>75.29263321976097</v>
+        <v>75.56100605935544</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4697718358633503</v>
+        <v>-0.4704171661713256</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7511982519924409</v>
+        <v>0.7512411272288644</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6253633240191264</v>
+        <v>-0.6261866518231952</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644788426179537</v>
+        <v>0.7644003691118328</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14318863170632</v>
+        <v>1.142403359827117</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.961915649107912</v>
+        <v>2.957274630378648</v>
       </c>
       <c r="E19" t="n">
-        <v>104.7121945252457</v>
+        <v>105.8214975996448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1145170644866114</v>
+        <v>0.1088533349629</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4844410648645057</v>
+        <v>0.4845853667903742</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2363900849706886</v>
+        <v>0.2246319068276542</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173793035080103</v>
+        <v>0.7176700183492563</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6918112991398153</v>
+        <v>0.6918537937943315</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564565461794216</v>
+        <v>2.565730108850213</v>
       </c>
       <c r="E20" t="n">
-        <v>138.4405510987041</v>
+        <v>139.4574472042207</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3326262206779702</v>
+        <v>-0.3336401392721948</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7841465523743212</v>
+        <v>0.78421044924365</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4241888454024438</v>
+        <v>-0.4254471992741002</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7329644411867965</v>
+        <v>0.7329804790953945</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144136922713216</v>
+        <v>1.143521307371843</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.1978468996783</v>
+        <v>565.7793415898459</v>
       </c>
       <c r="E2" t="n">
-        <v>14413.33958603742</v>
+        <v>15883.61968411752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6159357193918902</v>
+        <v>0.617770427469801</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5026674597951427</v>
+        <v>0.5025919377953417</v>
       </c>
       <c r="H2" t="n">
-        <v>1.225334378403784</v>
+        <v>1.229168995785525</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.0011823129019</v>
+        <v>221.6651719148003</v>
       </c>
       <c r="E3" t="n">
-        <v>6190.834330826448</v>
+        <v>6743.998121834199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.245997384177989</v>
+        <v>0.243932561833657</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022904692411151</v>
+        <v>0.6023551081205867</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4084364550678434</v>
+        <v>0.4049647102599545</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906885839167858</v>
+        <v>0.890824936784434</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067212994796941</v>
+        <v>1.067651330554781</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.59230965208134</v>
+        <v>36.45653064947427</v>
       </c>
       <c r="E4" t="n">
-        <v>418.3878717138805</v>
+        <v>439.0826096698087</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3509152750188053</v>
+        <v>-0.3535367351856972</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5656978650153378</v>
+        <v>0.5658399347451938</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.620322784865541</v>
+        <v>-0.6247999009559126</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370287373494864</v>
+        <v>0.7373580970729319</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8294461378969561</v>
+        <v>0.8301499211503169</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.45231422991905</v>
+        <v>36.29163197346144</v>
       </c>
       <c r="E5" t="n">
-        <v>2029.455498742668</v>
+        <v>2140.567155181409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7307646100318694</v>
+        <v>0.7232209308327986</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117736587770073</v>
+        <v>1.117979022647268</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6537896477825539</v>
+        <v>0.6469002693094191</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4744516882133983</v>
+        <v>0.4745424454172419</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054995704837385</v>
+        <v>1.055584977465847</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.71104071227342</v>
+        <v>10.63796262305468</v>
       </c>
       <c r="E6" t="n">
-        <v>209.7817124841683</v>
+        <v>230.0073652346156</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3234909644461372</v>
+        <v>-0.3268366558629665</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7196441079608846</v>
+        <v>0.719902861383578</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4495151990652027</v>
+        <v>-0.4540010512457481</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7512213604555482</v>
+        <v>0.7514008115823461</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075486418091428</v>
+        <v>1.076291825684529</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.57059791940747</v>
+        <v>10.51913571559923</v>
       </c>
       <c r="E7" t="n">
-        <v>1208.5608777109</v>
+        <v>1283.540964292854</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5108999503585144</v>
+        <v>-0.513036900926235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8105547405340563</v>
+        <v>0.8102827241201326</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6303090029698598</v>
+        <v>-0.6331578912574374</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6736626497526579</v>
+        <v>0.6745092663302618</v>
       </c>
       <c r="N7" t="n">
-        <v>1.086285661897199</v>
+        <v>1.087449210116283</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.473325619756904</v>
+        <v>9.446867177308828</v>
       </c>
       <c r="E8" t="n">
-        <v>438.856384058101</v>
+        <v>489.5008950641386</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3648437877205097</v>
+        <v>-0.3655889012157372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17645601405859</v>
+        <v>1.176508694069987</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3101210613577089</v>
+        <v>-0.3107405011611324</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394999771108012</v>
+        <v>0.7395391106122005</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730745005500749</v>
+        <v>1.731174194828287</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.260488601602943</v>
+        <v>7.244344372288922</v>
       </c>
       <c r="E9" t="n">
-        <v>230.9513639252051</v>
+        <v>235.2044871698001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4024602458318987</v>
+        <v>0.3991322681639431</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4838417554755938</v>
+        <v>0.4839895728126938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8318013922471389</v>
+        <v>0.8246712131511336</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6795052905575221</v>
+        <v>0.6795876381515574</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6540567252399694</v>
+        <v>0.654434156107962</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.738154755074584</v>
+        <v>6.71853142993008</v>
       </c>
       <c r="E10" t="n">
-        <v>268.8139835328638</v>
+        <v>280.082306112736</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2645670056763917</v>
+        <v>-0.264846727012168</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9652077035077554</v>
+        <v>0.9652253401851795</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2741037029800974</v>
+        <v>-0.2743884935318388</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7143723913721726</v>
+        <v>0.7143863606610436</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371717468257612</v>
+        <v>1.3719754857538</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.545422703548801</v>
+        <v>6.516459648034927</v>
       </c>
       <c r="E11" t="n">
-        <v>521.209582190588</v>
+        <v>565.141248596179</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9342559787816793</v>
+        <v>0.9262059049548113</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8275909565187601</v>
+        <v>0.8278247586699232</v>
       </c>
       <c r="H11" t="n">
-        <v>1.128886162206995</v>
+        <v>1.118842961936725</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6645219242517941</v>
+        <v>0.6646365361679675</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094067905536112</v>
+        <v>1.094730215072624</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.259714059981445</v>
+        <v>6.250483970273632</v>
       </c>
       <c r="E12" t="n">
-        <v>133.8443997470289</v>
+        <v>140.3167567511894</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2874952812949587</v>
+        <v>-0.2871171125039707</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6636736616672905</v>
+        <v>0.663643053158667</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4331877214664643</v>
+        <v>-0.432637863287217</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7894817187697555</v>
+        <v>0.7894527163215376</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042355563116904</v>
+        <v>1.042425816224233</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.698102477429143</v>
+        <v>4.690763801461245</v>
       </c>
       <c r="E13" t="n">
-        <v>273.9845384960166</v>
+        <v>285.7452577819891</v>
       </c>
       <c r="F13" t="n">
-        <v>1.766280428040206</v>
+        <v>1.763136061347545</v>
       </c>
       <c r="G13" t="n">
-        <v>0.866115586198097</v>
+        <v>0.866161623375439</v>
       </c>
       <c r="H13" t="n">
-        <v>2.039312600057776</v>
+        <v>2.035573978071886</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6034202157887328</v>
+        <v>0.6034748969935803</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039716503898291</v>
+        <v>1.040022246952824</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.527149211130435</v>
+        <v>4.493961713741166</v>
       </c>
       <c r="E14" t="n">
-        <v>134.2053636277265</v>
+        <v>142.0786500272378</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4134125111970282</v>
+        <v>-0.4177190952765462</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8564999916496132</v>
+        <v>0.8568019535216201</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4826766085552417</v>
+        <v>-0.4875328464876167</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7604780300160837</v>
+        <v>0.7608014213722788</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295785938926584</v>
+        <v>1.296988859258688</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.099998667883153</v>
+        <v>4.093533442885094</v>
       </c>
       <c r="E15" t="n">
-        <v>318.3567654136871</v>
+        <v>334.5637339551578</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04184747472101114</v>
+        <v>-0.04409096540893487</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7960818846856746</v>
+        <v>0.7961839563412239</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05256679686604628</v>
+        <v>-0.05537786218595771</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7174749111455776</v>
+        <v>0.7175877084962458</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136275619894379</v>
+        <v>1.136770763332506</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.975192141397437</v>
+        <v>3.981046012733538</v>
       </c>
       <c r="E16" t="n">
-        <v>207.6125968290982</v>
+        <v>213.5602028046733</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4498187394397628</v>
+        <v>0.455275702620672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9637190428533403</v>
+        <v>0.9634840465775089</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4667529844672963</v>
+        <v>0.4725306083042099</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5161292058033023</v>
+        <v>0.5159353740352407</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9895280359069298</v>
+        <v>0.9890638201012572</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.345424375784122</v>
+        <v>3.333875530353017</v>
       </c>
       <c r="E17" t="n">
-        <v>110.0363029122565</v>
+        <v>114.5848177393233</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2244678886903808</v>
+        <v>-0.226123561416152</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7587172439234741</v>
+        <v>0.7588720216985293</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2958518347752501</v>
+        <v>-0.2979732483878318</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7247250014463449</v>
+        <v>0.7247006110431368</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093886912679602</v>
+        <v>1.094237643844596</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.126996590830752</v>
+        <v>3.117097868579168</v>
       </c>
       <c r="E18" t="n">
-        <v>75.56100605935544</v>
+        <v>78.22220211295856</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4704171661713256</v>
+        <v>-0.4719489708861689</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7512411272288644</v>
+        <v>0.7513483134573192</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6261866518231952</v>
+        <v>-0.6281360621074692</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644003691118328</v>
+        <v>0.7645804208588932</v>
       </c>
       <c r="N18" t="n">
-        <v>1.142403359827117</v>
+        <v>1.143007212242116</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.957274630378648</v>
+        <v>2.951592899636228</v>
       </c>
       <c r="E19" t="n">
-        <v>105.8214975996448</v>
+        <v>107.0710026202162</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1088533349629</v>
+        <v>0.1079101413440182</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4845853667903742</v>
+        <v>0.4846130560048412</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2246319068276542</v>
+        <v>0.2226727901918932</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176700183492563</v>
+        <v>0.7177837253469505</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6918537937943315</v>
+        <v>0.6921069331449778</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.565730108850213</v>
+        <v>2.562032005676069</v>
       </c>
       <c r="E20" t="n">
-        <v>139.4574472042207</v>
+        <v>143.2398733227694</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3336401392721948</v>
+        <v>-0.3341469417348597</v>
       </c>
       <c r="G20" t="n">
-        <v>0.78421044924365</v>
+        <v>0.784243135975997</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4254471992741002</v>
+        <v>-0.4260756982195465</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7329804790953945</v>
+        <v>0.7330272635951963</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143521307371843</v>
+        <v>1.143813811418303</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.7793415898459</v>
+        <v>565.0174216043429</v>
       </c>
       <c r="E2" t="n">
-        <v>15883.61968411752</v>
+        <v>16370.12772780197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.617770427469801</v>
+        <v>0.6167427688046794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5025919377953417</v>
+        <v>0.5026340257973174</v>
       </c>
       <c r="H2" t="n">
-        <v>1.229168995785525</v>
+        <v>1.227021524908414</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.6651719148003</v>
+        <v>221.4894763063852</v>
       </c>
       <c r="E3" t="n">
-        <v>6743.998121834199</v>
+        <v>6895.320846891379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.243932561833657</v>
+        <v>0.2448398581427194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6023551081205867</v>
+        <v>0.6023263168574736</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4049647102599545</v>
+        <v>0.4064903878351624</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890824936784434</v>
+        <v>0.8907613816581882</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067651330554781</v>
+        <v>1.067434743125411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.45653064947427</v>
+        <v>36.77059212884742</v>
       </c>
       <c r="E4" t="n">
-        <v>439.0826096698087</v>
+        <v>2230.794738307779</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3535367351856972</v>
+        <v>0.7555153474062146</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5658399347451938</v>
+        <v>1.117017997394056</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6247999009559126</v>
+        <v>0.6763681061261253</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J4" t="n">
         <v>266</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7373580970729319</v>
+        <v>0.4739070004599086</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8301499211503169</v>
+        <v>1.053177105877451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.29163197346144</v>
+        <v>36.35119212064637</v>
       </c>
       <c r="E5" t="n">
-        <v>2140.567155181409</v>
+        <v>446.2620644271929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7232209308327986</v>
+        <v>-0.3546593367610835</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117979022647268</v>
+        <v>0.5659069110806786</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6469002693094191</v>
+        <v>-0.6267096757730203</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J5" t="n">
         <v>266</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4745424454172419</v>
+        <v>0.7374627983078632</v>
       </c>
       <c r="N5" t="n">
-        <v>1.055584977465847</v>
+        <v>0.8302965434250227</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.63796262305468</v>
+        <v>10.55496410175869</v>
       </c>
       <c r="E6" t="n">
-        <v>230.0073652346156</v>
+        <v>235.4939005623505</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3268366558629665</v>
+        <v>-0.3347267304008547</v>
       </c>
       <c r="G6" t="n">
-        <v>0.719902861383578</v>
+        <v>0.7206039380553386</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4540010512457481</v>
+        <v>-0.4645086055235371</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7514008115823461</v>
+        <v>0.7517525565276038</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076291825684529</v>
+        <v>1.077754041457197</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.51913571559923</v>
+        <v>10.31694972442009</v>
       </c>
       <c r="E7" t="n">
-        <v>1283.540964292854</v>
+        <v>1348.8583982811</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.513036900926235</v>
+        <v>-0.5269532170217098</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102827241201326</v>
+        <v>0.8089622539911812</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6331578912574374</v>
+        <v>-0.6513940723709642</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6745092663302618</v>
+        <v>0.6780405468898337</v>
       </c>
       <c r="N7" t="n">
-        <v>1.087449210116283</v>
+        <v>1.091269553905199</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.446867177308828</v>
+        <v>9.357632098553303</v>
       </c>
       <c r="E8" t="n">
-        <v>489.5008950641386</v>
+        <v>502.2584140760506</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3655889012157372</v>
+        <v>-0.3726556265405251</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176508694069987</v>
+        <v>1.17704645416916</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3107405011611324</v>
+        <v>-0.3166023101471989</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395391106122005</v>
+        <v>0.7398145440168422</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731174194828287</v>
+        <v>1.732465454157174</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.244344372288922</v>
+        <v>7.259059804140338</v>
       </c>
       <c r="E9" t="n">
-        <v>235.2044871698001</v>
+        <v>227.5100510047623</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3991322681639431</v>
+        <v>0.4055524300291005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4839895728126938</v>
+        <v>0.4837115207949513</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8246712131511336</v>
+        <v>0.8384179673095217</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6795876381515574</v>
+        <v>0.6793685304443479</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654434156107962</v>
+        <v>0.6537925571596283</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.71853142993008</v>
+        <v>6.717295408583096</v>
       </c>
       <c r="E10" t="n">
-        <v>280.082306112736</v>
+        <v>285.8786666962584</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.264846727012168</v>
+        <v>-0.2637276685295878</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9652253401851795</v>
+        <v>0.9651553788191279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2743884935318388</v>
+        <v>-0.2732489237663058</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7143863606610436</v>
+        <v>0.7143343751378682</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3719754857538</v>
+        <v>1.371661346137609</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.516459648034927</v>
+        <v>6.512085374568179</v>
       </c>
       <c r="E11" t="n">
-        <v>565.141248596179</v>
+        <v>577.2927858603218</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9262059049548113</v>
+        <v>0.9273979337588671</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8278247586699232</v>
+        <v>0.8277892589188758</v>
       </c>
       <c r="H11" t="n">
-        <v>1.118842961936725</v>
+        <v>1.120330958352956</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6646365361679675</v>
+        <v>0.6646342814646862</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094730215072624</v>
+        <v>1.094587893115668</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.250483970273632</v>
+        <v>6.255523611901522</v>
       </c>
       <c r="E12" t="n">
-        <v>140.3167567511894</v>
+        <v>145.2506944024412</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2871171125039707</v>
+        <v>-0.2854146796884077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663643053158667</v>
+        <v>0.6635087714925725</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.432637863287217</v>
+        <v>-0.4301596180052953</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7894527163215376</v>
+        <v>0.7893815277107564</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042425816224233</v>
+        <v>1.042033648357694</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.690763801461245</v>
+        <v>4.667003961684774</v>
       </c>
       <c r="E13" t="n">
-        <v>285.7452577819891</v>
+        <v>285.7324683526504</v>
       </c>
       <c r="F13" t="n">
-        <v>1.763136061347545</v>
+        <v>1.745859400877651</v>
       </c>
       <c r="G13" t="n">
-        <v>0.866161623375439</v>
+        <v>0.8664327254889482</v>
       </c>
       <c r="H13" t="n">
-        <v>2.035573978071886</v>
+        <v>2.014997067305395</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6034748969935803</v>
+        <v>0.6037686153697824</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040022246952824</v>
+        <v>1.040766959916228</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.493961713741166</v>
+        <v>4.477825222058009</v>
       </c>
       <c r="E14" t="n">
-        <v>142.0786500272378</v>
+        <v>145.2113967496407</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4177190952765462</v>
+        <v>-0.4201761312367652</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8568019535216201</v>
+        <v>0.8569934064532733</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4875328464876167</v>
+        <v>-0.4902909731542665</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7608014213722788</v>
+        <v>0.7609495077558223</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296988859258688</v>
+        <v>1.297422532738698</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.093533442885094</v>
+        <v>4.068469393364327</v>
       </c>
       <c r="E15" t="n">
-        <v>334.5637339551578</v>
+        <v>342.4170258243782</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04409096540893487</v>
+        <v>-0.05219012818052948</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7961839563412239</v>
+        <v>0.7965913577950395</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05537786218595771</v>
+        <v>-0.06551681444924468</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7175877084962458</v>
+        <v>0.7179244574512695</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136770763332506</v>
+        <v>1.137790895568985</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.981046012733538</v>
+        <v>3.987917238793929</v>
       </c>
       <c r="E16" t="n">
-        <v>213.5602028046733</v>
+        <v>215.2047862450962</v>
       </c>
       <c r="F16" t="n">
-        <v>0.455275702620672</v>
+        <v>0.4621047182358107</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9634840465775089</v>
+        <v>0.9632032281767168</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4725306083042099</v>
+        <v>0.4797582739735475</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159353740352407</v>
+        <v>0.5158076128681764</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9890638201012572</v>
+        <v>0.9884479210189699</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.333875530353017</v>
+        <v>3.320638437245279</v>
       </c>
       <c r="E17" t="n">
-        <v>114.5848177393233</v>
+        <v>115.0136118569076</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.226123561416152</v>
+        <v>-0.2292483226282661</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7588720216985293</v>
+        <v>0.7591747441345083</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2979732483878318</v>
+        <v>-0.301970428283437</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7247006110431368</v>
+        <v>0.7247911567533127</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094237643844596</v>
+        <v>1.094719244496653</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.117097868579168</v>
+        <v>3.101598025098119</v>
       </c>
       <c r="E18" t="n">
-        <v>78.22220211295856</v>
+        <v>79.46865436924378</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4719489708861689</v>
+        <v>-0.4756525602749975</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7513483134573192</v>
+        <v>0.7516390254664167</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6281360621074692</v>
+        <v>-0.6328204685485023</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645804208588932</v>
+        <v>0.7648929388252659</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143007212242116</v>
+        <v>1.143821057901478</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.951592899636228</v>
+        <v>2.960326913274503</v>
       </c>
       <c r="E19" t="n">
-        <v>107.0710026202162</v>
+        <v>106.9307985222595</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1079101413440182</v>
+        <v>0.1126282851497467</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4846130560048412</v>
+        <v>0.48448500570536</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2226727901918932</v>
+        <v>0.2324701153253887</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177837253469505</v>
+        <v>0.7173584749954113</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6921069331449778</v>
+        <v>0.6914562226455527</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.562032005676069</v>
+        <v>2.550919351624128</v>
       </c>
       <c r="E20" t="n">
-        <v>143.2398733227694</v>
+        <v>144.8051624944491</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341469417348597</v>
+        <v>-0.3381975925970834</v>
       </c>
       <c r="G20" t="n">
-        <v>0.784243135975997</v>
+        <v>0.7845223406748751</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4260756982195465</v>
+        <v>-0.4310872680899734</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7330272635951963</v>
+        <v>0.7332757181953898</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143813811418303</v>
+        <v>1.14451301199945</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.0174216043429</v>
+        <v>565.7407504538787</v>
       </c>
       <c r="E2" t="n">
-        <v>16370.12772780197</v>
+        <v>16478.2716772208</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6167427688046794</v>
+        <v>0.619131756516951</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5026340257973174</v>
+        <v>0.5025370210515029</v>
       </c>
       <c r="H2" t="n">
-        <v>1.227021524908414</v>
+        <v>1.232012231101873</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.4894763063852</v>
+        <v>221.61500386142</v>
       </c>
       <c r="E3" t="n">
-        <v>6895.320846891379</v>
+        <v>6928.407984468324</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2448398581427194</v>
+        <v>0.2441547402576556</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6023263168574736</v>
+        <v>0.6023480013960246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4064903878351624</v>
+        <v>0.4053383421075413</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907613816581882</v>
+        <v>0.8908472624023553</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067434743125411</v>
+        <v>1.067782164455073</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.77059212884742</v>
+        <v>36.76591696333075</v>
       </c>
       <c r="E4" t="n">
-        <v>2230.794738307779</v>
+        <v>2258.996226749617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7555153474062146</v>
+        <v>0.754826541101739</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117017997394056</v>
+        <v>1.117036408987482</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6763681061261253</v>
+        <v>0.6757403205737389</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4739070004599086</v>
+        <v>0.4738724912003083</v>
       </c>
       <c r="N4" t="n">
-        <v>1.053177105877451</v>
+        <v>1.05332105638859</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.35119212064637</v>
+        <v>36.5249943159637</v>
       </c>
       <c r="E5" t="n">
-        <v>446.2620644271929</v>
+        <v>445.1896645109302</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3546593367610835</v>
+        <v>-0.3512899454591246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5659069110806786</v>
+        <v>0.5657169424282571</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6267096757730203</v>
+        <v>-0.6209641591274675</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7374627983078632</v>
+        <v>0.7371352884187593</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8302965434250227</v>
+        <v>0.8298093554335259</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.55496410175869</v>
+        <v>10.60599094474573</v>
       </c>
       <c r="E6" t="n">
-        <v>235.4939005623505</v>
+        <v>239.76235224618</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3347267304008547</v>
+        <v>-0.3295706900414724</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7206039380553386</v>
+        <v>0.7201313210559975</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4645086055235371</v>
+        <v>-0.4576535978996044</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7517525565276038</v>
+        <v>0.7515145535873476</v>
       </c>
       <c r="N6" t="n">
-        <v>1.077754041457197</v>
+        <v>1.076914029408792</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.31694972442009</v>
+        <v>10.42394160343399</v>
       </c>
       <c r="E7" t="n">
-        <v>1348.8583982811</v>
+        <v>1373.15438270054</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5269532170217098</v>
+        <v>-0.5198757746332078</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8089622539911812</v>
+        <v>0.8095354983768299</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6513940723709642</v>
+        <v>-0.6421902136170579</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6780405468898337</v>
+        <v>0.6765147578464713</v>
       </c>
       <c r="N7" t="n">
-        <v>1.091269553905199</v>
+        <v>1.089795753766758</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.357632098553303</v>
+        <v>9.402658253331095</v>
       </c>
       <c r="E8" t="n">
-        <v>502.2584140760506</v>
+        <v>495.0477678912362</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3726556265405251</v>
+        <v>-0.3693109067981065</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17704645416916</v>
+        <v>1.176783314553511</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3166023101471989</v>
+        <v>-0.3138308490873093</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7398145440168422</v>
+        <v>0.7396849439723651</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732465454157174</v>
+        <v>1.732109006161994</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.259059804140338</v>
+        <v>7.266240863246133</v>
       </c>
       <c r="E9" t="n">
-        <v>227.5100510047623</v>
+        <v>227.5939175442334</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4055524300291005</v>
+        <v>0.4038871782375704</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4837115207949513</v>
+        <v>0.4837808062944794</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8384179673095217</v>
+        <v>0.8348557300797967</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6793685304443479</v>
+        <v>0.6793932469117343</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6537925571596283</v>
+        <v>0.6540362182556466</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.717295408583096</v>
+        <v>6.735939804760334</v>
       </c>
       <c r="E10" t="n">
-        <v>285.8786666962584</v>
+        <v>284.3329778342632</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2637276685295878</v>
+        <v>-0.2626081485290588</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9651553788191279</v>
+        <v>0.9650869785661033</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2732489237663058</v>
+        <v>-0.2721082704060871</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7143343751378682</v>
+        <v>0.7142867794915442</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371661346137609</v>
+        <v>1.37173748594048</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.512085374568179</v>
+        <v>6.532791882889827</v>
       </c>
       <c r="E11" t="n">
-        <v>577.2927858603218</v>
+        <v>580.4537271349745</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9273979337588671</v>
+        <v>0.9354493564496646</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8277892589188758</v>
+        <v>0.8275574818489101</v>
       </c>
       <c r="H11" t="n">
-        <v>1.120330958352956</v>
+        <v>1.130373873679089</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6646342814646862</v>
+        <v>0.6644566602687507</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094587893115668</v>
+        <v>1.094200143542041</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.255523611901522</v>
+        <v>6.308640191706465</v>
       </c>
       <c r="E12" t="n">
-        <v>145.2506944024412</v>
+        <v>148.1888772385617</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2854146796884077</v>
+        <v>-0.2765063399182617</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6635087714925725</v>
+        <v>0.6628995337235635</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4301596180052953</v>
+        <v>-0.417116509895703</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7893815277107564</v>
+        <v>0.7888888053756189</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042033648357694</v>
+        <v>1.04062785294706</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.667003961684774</v>
+        <v>4.68263557816773</v>
       </c>
       <c r="E13" t="n">
-        <v>285.7324683526504</v>
+        <v>276.7333337169877</v>
       </c>
       <c r="F13" t="n">
-        <v>1.745859400877651</v>
+        <v>1.752138421763711</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8664327254889482</v>
+        <v>0.8663306393531642</v>
       </c>
       <c r="H13" t="n">
-        <v>2.014997067305395</v>
+        <v>2.022482343544867</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6037686153697824</v>
+        <v>0.6036519387888953</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040766959916228</v>
+        <v>1.040644068338529</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.477825222058009</v>
+        <v>4.497429940015448</v>
       </c>
       <c r="E14" t="n">
-        <v>145.2113967496407</v>
+        <v>145.4020821034823</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4201761312367652</v>
+        <v>-0.4177190952765462</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8569934064532733</v>
+        <v>0.8568019535216201</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4902909731542665</v>
+        <v>-0.4875328464876167</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7609495077558223</v>
+        <v>0.7608108314033066</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297422532738698</v>
+        <v>1.297146636565815</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.068469393364327</v>
+        <v>4.065930402257529</v>
       </c>
       <c r="E15" t="n">
-        <v>342.4170258243782</v>
+        <v>339.2889550100684</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05219012818052948</v>
+        <v>-0.05339478586214819</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965913577950395</v>
+        <v>0.7966571745116849</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06551681444924468</v>
+        <v>-0.06702354233472735</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7179244574512695</v>
+        <v>0.7179538919765868</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137790895568985</v>
+        <v>1.13815121085998</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.987917238793929</v>
+        <v>3.982191659030468</v>
       </c>
       <c r="E16" t="n">
-        <v>215.2047862450962</v>
+        <v>215.0080974875695</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4621047182358107</v>
+        <v>0.4484553678475516</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9632032281767168</v>
+        <v>0.9637792273824297</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4797582739735475</v>
+        <v>0.4653092275764557</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158076128681764</v>
+        <v>0.5160333145776661</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9884479210189699</v>
+        <v>0.9896627878014319</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.320638437245279</v>
+        <v>3.343146456306732</v>
       </c>
       <c r="E17" t="n">
-        <v>115.0136118569076</v>
+        <v>114.1410113477918</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2292483226282661</v>
+        <v>-0.2229953742540847</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7591747441345083</v>
+        <v>0.7585828552033946</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.301970428283437</v>
+        <v>-0.2939631086103233</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7247911567533127</v>
+        <v>0.7245947995368019</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094719244496653</v>
+        <v>1.09378049551065</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.101598025098119</v>
+        <v>3.100660836119228</v>
       </c>
       <c r="E18" t="n">
-        <v>79.46865436924378</v>
+        <v>80.12988805297051</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4756525602749975</v>
+        <v>-0.4758938529742335</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7516390254664167</v>
+        <v>0.7516595184109949</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6328204685485023</v>
+        <v>-0.633124228879947</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7648929388252659</v>
+        <v>0.7649285723965203</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143821057901478</v>
+        <v>1.144126339475102</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.960326913274503</v>
+        <v>2.966981842190737</v>
       </c>
       <c r="E19" t="n">
-        <v>106.9307985222595</v>
+        <v>107.6198751065282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1126282851497467</v>
+        <v>0.1154617799206612</v>
       </c>
       <c r="G19" t="n">
-        <v>0.48448500570536</v>
+        <v>0.484420654882315</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2324701153253887</v>
+        <v>0.2383502411735756</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173584749954113</v>
+        <v>0.7171670620938836</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6914562226455527</v>
+        <v>0.6913133228525675</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.550919351624128</v>
+        <v>2.554743117034911</v>
       </c>
       <c r="E20" t="n">
-        <v>144.8051624944491</v>
+        <v>144.9545847532645</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3381975925970834</v>
+        <v>-0.337691627995255</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845223406748751</v>
+        <v>0.7844857188087971</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4310872680899734</v>
+        <v>-0.4304624289502976</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7332757181953898</v>
+        <v>0.7332461265106505</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14451301199945</v>
+        <v>1.144634306574842</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.7407504538787</v>
+        <v>564.8202923725758</v>
       </c>
       <c r="E2" t="n">
-        <v>16478.2716772208</v>
+        <v>16209.79835836253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.619131756516951</v>
+        <v>0.6158602071280674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5025370210515029</v>
+        <v>0.5026706052311884</v>
       </c>
       <c r="H2" t="n">
-        <v>1.232012231101873</v>
+        <v>1.225176488776026</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.61500386142</v>
+        <v>222.0110556512082</v>
       </c>
       <c r="E3" t="n">
-        <v>6928.407984468324</v>
+        <v>6763.303569367197</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2441547402576556</v>
+        <v>0.2475535586867668</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6023480013960246</v>
+        <v>0.6022438371281097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4053383421075413</v>
+        <v>0.4110520414243891</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908472624023553</v>
+        <v>0.8906142385978733</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067782164455073</v>
+        <v>1.067034616451119</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.76591696333075</v>
+        <v>36.94323837077167</v>
       </c>
       <c r="E4" t="n">
-        <v>2258.996226749617</v>
+        <v>2252.327310876265</v>
       </c>
       <c r="F4" t="n">
-        <v>0.754826541101739</v>
+        <v>0.7682714739660019</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117036408987482</v>
+        <v>1.116693365893722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6757403205737389</v>
+        <v>0.6879878554227212</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4738724912003083</v>
+        <v>0.4736330755119318</v>
       </c>
       <c r="N4" t="n">
-        <v>1.05332105638859</v>
+        <v>1.05218588035153</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.5249943159637</v>
+        <v>36.58779686801991</v>
       </c>
       <c r="E5" t="n">
-        <v>445.1896645109302</v>
+        <v>450.900048670175</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3512899454591246</v>
+        <v>-0.3490410430936187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5657169424282571</v>
+        <v>0.5656085717431806</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6209641591274675</v>
+        <v>-0.6171070604851154</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7371352884187593</v>
+        <v>0.7367948832530751</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8298093554335259</v>
+        <v>0.8290468892502458</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.60599094474573</v>
+        <v>10.62250739585134</v>
       </c>
       <c r="E6" t="n">
-        <v>239.76235224618</v>
+        <v>240.8301333831578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3295706900414724</v>
+        <v>-0.3265326880645726</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7201313210559975</v>
+        <v>0.7198784073447965</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4576535978996044</v>
+        <v>-0.4535942247093611</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7515145535873476</v>
+        <v>0.7513957410762319</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076914029408792</v>
+        <v>1.076079571278777</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.42394160343399</v>
+        <v>10.46299647998671</v>
       </c>
       <c r="E7" t="n">
-        <v>1373.15438270054</v>
+        <v>1383.809035986462</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5198757746332078</v>
+        <v>-0.5164152082815419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8095354983768299</v>
+        <v>0.8098900303697445</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6421902136170579</v>
+        <v>-0.6376362085180619</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6765147578464713</v>
+        <v>0.6752253936444165</v>
       </c>
       <c r="N7" t="n">
-        <v>1.089795753766758</v>
+        <v>1.087905894782902</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.402658253331095</v>
+        <v>9.456887875567475</v>
       </c>
       <c r="E8" t="n">
-        <v>495.0477678912362</v>
+        <v>492.9362367981447</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3693109067981065</v>
+        <v>-0.3640984370633876</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176783314553511</v>
+        <v>1.176404082313439</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3138308490873093</v>
+        <v>-0.3095011676152767</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7396849439723651</v>
+        <v>0.7394665738999612</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732109006161994</v>
+        <v>1.730579602660785</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.266240863246133</v>
+        <v>7.285102003633199</v>
       </c>
       <c r="E9" t="n">
-        <v>227.5939175442334</v>
+        <v>227.2777831814609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4038871782375704</v>
+        <v>0.4131718220972231</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4837808062944794</v>
+        <v>0.4834197952599637</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8348557300797967</v>
+        <v>0.8546853607329753</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6793932469117343</v>
+        <v>0.6790320498674061</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6540362182556466</v>
+        <v>0.653027113791312</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.735939804760334</v>
+        <v>6.755925197913723</v>
       </c>
       <c r="E10" t="n">
-        <v>284.3329778342632</v>
+        <v>281.7285293164902</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2626081485290588</v>
+        <v>-0.258265655270458</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9650869785661033</v>
+        <v>0.9648366788266048</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2721082704060871</v>
+        <v>-0.2676781065004185</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7142867794915442</v>
+        <v>0.7140578191667408</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37173748594048</v>
+        <v>1.370577804958666</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.532791882889827</v>
+        <v>6.533723487407837</v>
       </c>
       <c r="E11" t="n">
-        <v>580.4537271349745</v>
+        <v>576.0876109741308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9354493564496646</v>
+        <v>0.9381351859521758</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8275574818489101</v>
+        <v>0.8274832613404035</v>
       </c>
       <c r="H11" t="n">
-        <v>1.130373873679089</v>
+        <v>1.133721042806995</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6644566602687507</v>
+        <v>0.6644481170452042</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094200143542041</v>
+        <v>1.093797188779683</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.308640191706465</v>
+        <v>6.319497844048133</v>
       </c>
       <c r="E12" t="n">
-        <v>148.1888772385617</v>
+        <v>151.6049369633961</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2765063399182617</v>
+        <v>-0.2755568845018452</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6628995337235635</v>
+        <v>0.6628438213218311</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.417116509895703</v>
+        <v>-0.4157191719043782</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888888053756189</v>
+        <v>0.7887846663612537</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04062785294706</v>
+        <v>1.040126550090379</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.68263557816773</v>
+        <v>4.653006879564349</v>
       </c>
       <c r="E13" t="n">
-        <v>276.7333337169877</v>
+        <v>275.3196494113195</v>
       </c>
       <c r="F13" t="n">
-        <v>1.752138421763711</v>
+        <v>1.739584272045498</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8663306393531642</v>
+        <v>0.8665388139248739</v>
       </c>
       <c r="H13" t="n">
-        <v>2.022482343544867</v>
+        <v>2.007508774092045</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6036519387888953</v>
+        <v>0.6038773548433042</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040644068338529</v>
+        <v>1.041006100966135</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.497429940015448</v>
+        <v>4.503711301854202</v>
       </c>
       <c r="E14" t="n">
-        <v>145.4020821034823</v>
+        <v>143.8499573505673</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4177190952765462</v>
+        <v>-0.4152592439756052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8568019535216201</v>
+        <v>0.8566242462882918</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4875328464876167</v>
+        <v>-0.4847624215341813</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7608108314033066</v>
+        <v>0.7606138574762686</v>
       </c>
       <c r="N14" t="n">
-        <v>1.297146636565815</v>
+        <v>1.296197282268719</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.065930402257529</v>
+        <v>4.059991699684429</v>
       </c>
       <c r="E15" t="n">
-        <v>339.2889550100684</v>
+        <v>333.7869150112305</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05339478586214819</v>
+        <v>-0.0537388974338181</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966571745116849</v>
+        <v>0.7966762238887208</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06702354233472735</v>
+        <v>-0.06745387376004372</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7179538919765868</v>
+        <v>0.7179888391863544</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13815121085998</v>
+        <v>1.137931343596577</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.982191659030468</v>
+        <v>3.975475797960068</v>
       </c>
       <c r="E16" t="n">
-        <v>215.0080974875695</v>
+        <v>208.4007952006384</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4484553678475516</v>
+        <v>0.4525465259667365</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9637792273824297</v>
+        <v>0.9636003961357377</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4653092275764557</v>
+        <v>0.4696412826121218</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5160333145776661</v>
+        <v>0.5160683294696736</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9896627878014319</v>
+        <v>0.9892833229851882</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.343146456306732</v>
+        <v>3.34004597604475</v>
       </c>
       <c r="E17" t="n">
-        <v>114.1410113477918</v>
+        <v>111.6919905581702</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2229953742540847</v>
+        <v>-0.2231794799863015</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7585828552033946</v>
+        <v>0.7585994894651571</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2939631086103233</v>
+        <v>-0.2941993543175885</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245947995368019</v>
+        <v>0.7246960785146547</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09378049551065</v>
+        <v>1.093666646621947</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.100660836119228</v>
+        <v>3.099944604563095</v>
       </c>
       <c r="E18" t="n">
-        <v>80.12988805297051</v>
+        <v>79.89874026185151</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4758938529742335</v>
+        <v>-0.4750894268514942</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7516595184109949</v>
+        <v>0.7515919385697418</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.633124228879947</v>
+        <v>-0.6321108602569314</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649285723965203</v>
+        <v>0.7648374725599968</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144126339475102</v>
+        <v>1.143583238625554</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.966981842190737</v>
+        <v>2.944753668453361</v>
       </c>
       <c r="E19" t="n">
-        <v>107.6198751065282</v>
+        <v>107.020004753662</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1154617799206612</v>
+        <v>0.1041395451226113</v>
       </c>
       <c r="G19" t="n">
-        <v>0.484420654882315</v>
+        <v>0.4847342032910743</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2383502411735756</v>
+        <v>0.2148384504653519</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7171670620938836</v>
+        <v>0.7180502676965046</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6913133228525675</v>
+        <v>0.6924286417637777</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.554743117034911</v>
+        <v>2.551580874778547</v>
       </c>
       <c r="E20" t="n">
-        <v>144.9545847532645</v>
+        <v>144.0872717167603</v>
       </c>
       <c r="F20" t="n">
         <v>-0.337691627995255</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7332461265106505</v>
+        <v>0.7332441512308497</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144634306574842</v>
+        <v>1.144327038530777</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>564.8202923725758</v>
+        <v>566.2880551517562</v>
       </c>
       <c r="E2" t="n">
-        <v>16209.79835836253</v>
+        <v>15736.47987989837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6158602071280674</v>
+        <v>0.621250675244287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5026706052311884</v>
+        <v>0.5024534394257953</v>
       </c>
       <c r="H2" t="n">
-        <v>1.225176488776026</v>
+        <v>1.236434317086681</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.0110556512082</v>
+        <v>222.372502904738</v>
       </c>
       <c r="E3" t="n">
-        <v>6763.303569367197</v>
+        <v>6567.46946024091</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2475535586867668</v>
+        <v>0.2500556567134793</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022438371281097</v>
+        <v>0.6021726104645188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4110520414243891</v>
+        <v>0.4152557794360411</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906142385978733</v>
+        <v>0.8906520966852489</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067034616451119</v>
+        <v>1.067414920454257</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.94323837077167</v>
+        <v>37.08926658619181</v>
       </c>
       <c r="E4" t="n">
-        <v>2252.327310876265</v>
+        <v>2263.529243051199</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7682714739660019</v>
+        <v>0.7703423937186575</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116693365893722</v>
+        <v>1.116643581619015</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6879878554227212</v>
+        <v>0.6898731219157168</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736330755119318</v>
+        <v>0.473505266495567</v>
       </c>
       <c r="N4" t="n">
-        <v>1.05218588035153</v>
+        <v>1.052309677289337</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.58779686801991</v>
+        <v>36.6414483001825</v>
       </c>
       <c r="E5" t="n">
-        <v>450.900048670175</v>
+        <v>448.6133383238529</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3490410430936187</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367948832530751</v>
+        <v>0.7369224586878963</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8290468892502458</v>
+        <v>0.8295488231113807</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.62250739585134</v>
+        <v>10.67687072340218</v>
       </c>
       <c r="E6" t="n">
-        <v>240.8301333831578</v>
+        <v>239.5010049976995</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3265326880645726</v>
+        <v>-0.3250122909804974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7198784073447965</v>
+        <v>0.7197589296919386</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4535942247093611</v>
+        <v>-0.4515571500024387</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7513957410762319</v>
+        <v>0.7512884950435814</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076079571278777</v>
+        <v>1.07621236248358</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.46299647998671</v>
+        <v>10.52019067610469</v>
       </c>
       <c r="E7" t="n">
-        <v>1383.809035986462</v>
+        <v>1393.346969241663</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5164152082815419</v>
+        <v>-0.5153490636623019</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8098900303697445</v>
+        <v>0.8100090035092964</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6376362085180619</v>
+        <v>-0.6362263399907843</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6752253936444165</v>
+        <v>0.6755597926528011</v>
       </c>
       <c r="N7" t="n">
-        <v>1.087905894782902</v>
+        <v>1.089075069489014</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.456887875567475</v>
+        <v>9.435311454454929</v>
       </c>
       <c r="E8" t="n">
-        <v>492.9362367981447</v>
+        <v>489.4960750532518</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3640984370633876</v>
+        <v>-0.3667061265012828</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176404082313439</v>
+        <v>1.176589116866041</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3095011676152767</v>
+        <v>-0.3116688071006809</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394665738999612</v>
+        <v>0.7395862722767853</v>
       </c>
       <c r="N8" t="n">
-        <v>1.730579602660785</v>
+        <v>1.731880191603114</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.285102003633199</v>
+        <v>7.289159127014065</v>
       </c>
       <c r="E9" t="n">
-        <v>227.2777831814609</v>
+        <v>227.8970689372774</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4131718220972231</v>
+        <v>0.410313240896937</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834197952599637</v>
+        <v>0.483524380571417</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8546853607329753</v>
+        <v>0.8485885249716655</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6790320498674061</v>
+        <v>0.679114442401743</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653027113791312</v>
+        <v>0.6535299877231729</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.755925197913723</v>
+        <v>6.75816002291096</v>
       </c>
       <c r="E10" t="n">
-        <v>281.7285293164902</v>
+        <v>278.0330634961019</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.258265655270458</v>
+        <v>-0.2602276376076003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9648366788266048</v>
+        <v>0.9649468129174181</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2676781065004185</v>
+        <v>-0.269680809474699</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7140578191667408</v>
+        <v>0.71418391940318</v>
       </c>
       <c r="N10" t="n">
-        <v>1.370577804958666</v>
+        <v>1.371568871441162</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.533723487407837</v>
+        <v>6.546888115947513</v>
       </c>
       <c r="E11" t="n">
-        <v>576.0876109741308</v>
+        <v>563.4861205988838</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9381351859521758</v>
+        <v>0.9372397972085635</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8274832613404035</v>
+        <v>0.8275078326470651</v>
       </c>
       <c r="H11" t="n">
-        <v>1.133721042806995</v>
+        <v>1.132605348532453</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6644481170452042</v>
+        <v>0.6643949826022159</v>
       </c>
       <c r="N11" t="n">
-        <v>1.093797188779683</v>
+        <v>1.094214924079428</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.319497844048133</v>
+        <v>6.310920590578467</v>
       </c>
       <c r="E12" t="n">
-        <v>151.6049369633961</v>
+        <v>148.3474224707446</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2755568845018452</v>
+        <v>-0.2789733424350338</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6628438213218311</v>
+        <v>0.6630525812395264</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4157191719043782</v>
+        <v>-0.4207409040072121</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887846663612537</v>
+        <v>0.7890508129259768</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040126550090379</v>
+        <v>1.041255044124305</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.653006879564349</v>
+        <v>4.653836127085808</v>
       </c>
       <c r="E13" t="n">
-        <v>275.3196494113195</v>
+        <v>271.8593867139675</v>
       </c>
       <c r="F13" t="n">
-        <v>1.739584272045498</v>
+        <v>1.727045706859391</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8665388139248739</v>
+        <v>0.8667629917633163</v>
       </c>
       <c r="H13" t="n">
-        <v>2.007508774092045</v>
+        <v>1.992523588652466</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6038773548433042</v>
+        <v>0.6039976153666677</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041006100966135</v>
+        <v>1.041932921608427</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.503711301854202</v>
+        <v>4.520619703132652</v>
       </c>
       <c r="E14" t="n">
-        <v>143.8499573505673</v>
+        <v>141.1182767928447</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4152592439756052</v>
+        <v>-0.4146438418897163</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8566242462882918</v>
+        <v>0.8565819682624118</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4847624215341813</v>
+        <v>-0.4840679085631781</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7606138574762686</v>
+        <v>0.7606328751181211</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296197282268719</v>
+        <v>1.296725933528017</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.059991699684429</v>
+        <v>4.06946189662334</v>
       </c>
       <c r="E15" t="n">
-        <v>333.7869150112305</v>
+        <v>332.317344292043</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0537388974338181</v>
+        <v>-0.05219012818052948</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966762238887208</v>
+        <v>0.7965913577950395</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06745387376004372</v>
+        <v>-0.06551681444924468</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7179888391863544</v>
+        <v>0.7178955152131324</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137931343596577</v>
+        <v>1.138153942924805</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.975475797960068</v>
+        <v>3.990020110460822</v>
       </c>
       <c r="E16" t="n">
-        <v>208.4007952006384</v>
+        <v>201.0801313413799</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4525465259667365</v>
+        <v>0.455275702620672</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9636003961357377</v>
+        <v>0.9634840465775089</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4696412826121218</v>
+        <v>0.4725306083042099</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5160683294696736</v>
+        <v>0.5158066890708599</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9892833229851882</v>
+        <v>0.9890896887991827</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.34004597604475</v>
+        <v>3.344645982883484</v>
       </c>
       <c r="E17" t="n">
-        <v>111.6919905581702</v>
+        <v>108.825595994021</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2231794799863015</v>
+        <v>-0.2246518997153446</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7585994894651571</v>
+        <v>0.7587342537551848</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2941993543175885</v>
+        <v>-0.2960877258453543</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7246960785146547</v>
+        <v>0.7245560568732885</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093666646621947</v>
+        <v>1.094122272789702</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.099944604563095</v>
+        <v>3.117504436994185</v>
       </c>
       <c r="E18" t="n">
-        <v>79.89874026185151</v>
+        <v>79.50339760621438</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4750894268514942</v>
+        <v>-0.4719489708861689</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7515919385697418</v>
+        <v>0.7513483134573192</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6321108602569314</v>
+        <v>-0.6281360621074692</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7648374725599968</v>
+        <v>0.7646277222221984</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143583238625554</v>
+        <v>1.143393008058422</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.944753668453361</v>
+        <v>2.9641019525801</v>
       </c>
       <c r="E19" t="n">
-        <v>107.020004753662</v>
+        <v>105.7050550235136</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1041395451226113</v>
+        <v>0.1173518618991753</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4847342032910743</v>
+        <v>0.4843829564519142</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2148384504653519</v>
+        <v>0.2422708320680254</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7180502676965046</v>
+        <v>0.7170571387306</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6924286417637777</v>
+        <v>0.6912685426140345</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.551580874778547</v>
+        <v>2.559642543034034</v>
       </c>
       <c r="E20" t="n">
-        <v>144.0872717167603</v>
+        <v>141.9136881803325</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.337691627995255</v>
+        <v>-0.335666721348072</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7844857188087971</v>
+        <v>0.7843441486225612</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4304624289502976</v>
+        <v>-0.42795846942641</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7332441512308497</v>
+        <v>0.7331318686570408</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144327038530777</v>
+        <v>1.144439755466729</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.2880551517562</v>
+        <v>566.0787388966037</v>
       </c>
       <c r="E2" t="n">
-        <v>15736.47987989837</v>
+        <v>15513.91948997482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.621250675244287</v>
+        <v>0.6217095170600178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5024534394257953</v>
+        <v>0.5024356443247437</v>
       </c>
       <c r="H2" t="n">
-        <v>1.236434317086681</v>
+        <v>1.237391343712435</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.372502904738</v>
+        <v>222.1116794272941</v>
       </c>
       <c r="E3" t="n">
-        <v>6567.46946024091</v>
+        <v>6496.731609067771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2500556567134793</v>
+        <v>0.2494253705986393</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6021726104645188</v>
+        <v>0.6021901171345884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4152557794360411</v>
+        <v>0.4141970509006099</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906520966852489</v>
+        <v>0.8906916702250682</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067414920454257</v>
+        <v>1.06753118987904</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.08926658619181</v>
+        <v>37.10974748099303</v>
       </c>
       <c r="E4" t="n">
-        <v>2263.529243051199</v>
+        <v>2233.164848853095</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7703423937186575</v>
+        <v>0.7744862047081169</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116643581619015</v>
+        <v>1.116546407370324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6898731219157168</v>
+        <v>0.6936444375224644</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.473505266495567</v>
+        <v>0.47340982011676</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052309677289337</v>
+        <v>1.0520432613327</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.6414483001825</v>
+        <v>36.59629219020186</v>
       </c>
       <c r="E5" t="n">
-        <v>448.6133383238529</v>
+        <v>444.6407889910653</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3490410430936187</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7369224586878963</v>
+        <v>0.7369323186609389</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8295488231113807</v>
+        <v>0.8295893035005296</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.67687072340218</v>
+        <v>10.63530851259105</v>
       </c>
       <c r="E6" t="n">
-        <v>239.5010049976995</v>
+        <v>240.1044950229358</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3250122909804974</v>
+        <v>-0.3271405864372909</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7197589296919386</v>
+        <v>0.7199275015478341</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4515571500024387</v>
+        <v>-0.4544076809594622</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7512884950435814</v>
+        <v>0.7513819589781783</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07621236248358</v>
+        <v>1.076636465874714</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.52019067610469</v>
+        <v>10.46903644485002</v>
       </c>
       <c r="E7" t="n">
-        <v>1393.346969241663</v>
+        <v>1403.909896438421</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5153490636623019</v>
+        <v>-0.5158822155756835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8100090035092964</v>
+        <v>0.8099489356967926</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6362263399907843</v>
+        <v>-0.6369317778433453</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6755597926528011</v>
+        <v>0.6757543084862988</v>
       </c>
       <c r="N7" t="n">
-        <v>1.089075069489014</v>
+        <v>1.089346444929455</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.435311454454929</v>
+        <v>9.428645749869078</v>
       </c>
       <c r="E8" t="n">
-        <v>489.4960750532518</v>
+        <v>484.6638512224642</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3667061265012828</v>
+        <v>-0.365961368987834</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176589116866041</v>
+        <v>1.176535314644173</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3116688071006809</v>
+        <v>-0.3110500504598233</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395862722767853</v>
+        <v>0.7395586480144026</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731880191603114</v>
+        <v>1.731797647057568</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.289159127014065</v>
+        <v>7.281180427112619</v>
       </c>
       <c r="E9" t="n">
-        <v>227.8970689372774</v>
+        <v>226.8271865872634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.410313240896937</v>
+        <v>0.4088845392129115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483524380571417</v>
+        <v>0.4835788390912433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8485885249716655</v>
+        <v>0.8455385268331845</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.679114442401743</v>
+        <v>0.6791644959750578</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6535299877231729</v>
+        <v>0.6536749178235672</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.75816002291096</v>
+        <v>6.748111458623623</v>
       </c>
       <c r="E10" t="n">
-        <v>278.0330634961019</v>
+        <v>275.6199205017251</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2602276376076003</v>
+        <v>-0.2603677252564541</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9649468129174181</v>
+        <v>0.9649548627194603</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.269680809474699</v>
+        <v>-0.2698237350943848</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.71418391940318</v>
+        <v>0.71419122123187</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371568871441162</v>
+        <v>1.371642915114935</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.546888115947513</v>
+        <v>6.521901885897186</v>
       </c>
       <c r="E11" t="n">
-        <v>563.4861205988838</v>
+        <v>557.3048655083566</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9372397972085635</v>
+        <v>0.9294844653678798</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8275078326470651</v>
+        <v>0.8277278560203283</v>
       </c>
       <c r="H11" t="n">
-        <v>1.132605348532453</v>
+        <v>1.122934861509666</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643949826022159</v>
+        <v>0.6645109046800233</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094214924079428</v>
+        <v>1.094735599764526</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.310920590578467</v>
+        <v>6.293697843487706</v>
       </c>
       <c r="E12" t="n">
-        <v>148.3474224707446</v>
+        <v>147.6834775535888</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2789733424350338</v>
+        <v>-0.2803007812210765</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6630525812395264</v>
+        <v>0.6631398924116469</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4207409040072121</v>
+        <v>-0.4226872556282266</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890508129259768</v>
+        <v>0.7891225490748726</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041255044124305</v>
+        <v>1.041523721901561</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.653836127085808</v>
+        <v>4.63865438984447</v>
       </c>
       <c r="E13" t="n">
-        <v>271.8593867139675</v>
+        <v>270.4839167630265</v>
       </c>
       <c r="F13" t="n">
-        <v>1.727045706859391</v>
+        <v>1.716087272244886</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8667629917633163</v>
+        <v>0.8669722653142872</v>
       </c>
       <c r="H13" t="n">
-        <v>1.992523588652466</v>
+        <v>1.979402733976485</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039976153666677</v>
+        <v>0.604131814266207</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041932921608427</v>
+        <v>1.042452965825556</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.520619703132652</v>
+        <v>4.517700381286635</v>
       </c>
       <c r="E14" t="n">
-        <v>141.1182767928447</v>
+        <v>139.3284661866222</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4146438418897163</v>
+        <v>-0.4134125111970282</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8565819682624118</v>
+        <v>0.8564999916496132</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4840679085631781</v>
+        <v>-0.4826766085552417</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7606328751181211</v>
+        <v>0.76055693002139</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296725933528017</v>
+        <v>1.296518293577396</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.06946189662334</v>
+        <v>4.060057913169937</v>
       </c>
       <c r="E15" t="n">
-        <v>332.317344292043</v>
+        <v>327.0493000510694</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05219012818052948</v>
+        <v>-0.05339478586214819</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965913577950395</v>
+        <v>0.7966571745116849</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06551681444924468</v>
+        <v>-0.06702354233472735</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7178955152131324</v>
+        <v>0.7179313346349234</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138153942924805</v>
+        <v>1.138345089573284</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.990020110460822</v>
+        <v>3.962367154339503</v>
       </c>
       <c r="E16" t="n">
-        <v>201.0801313413799</v>
+        <v>198.1553018927156</v>
       </c>
       <c r="F16" t="n">
-        <v>0.455275702620672</v>
+        <v>0.4416437325945946</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9634840465775089</v>
+        <v>0.9640887573992107</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4725306083042099</v>
+        <v>0.4580944743988113</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158066890708599</v>
+        <v>0.5160565966103917</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9890896887991827</v>
+        <v>0.9902250538821425</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.344645982883484</v>
+        <v>3.323924602784666</v>
       </c>
       <c r="E17" t="n">
-        <v>108.825595994021</v>
+        <v>107.9707803090375</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2246518997153446</v>
+        <v>-0.2290646080947427</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7587342537551848</v>
+        <v>0.7591565619684604</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2960877258453543</v>
+        <v>-0.3017356624051145</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245560568732885</v>
+        <v>0.7245943432732118</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094122272789702</v>
+        <v>1.09482787830544</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.117504436994185</v>
+        <v>3.112540602296107</v>
       </c>
       <c r="E18" t="n">
-        <v>79.50339760621438</v>
+        <v>78.21870470960552</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4719489708861689</v>
+        <v>-0.4723518772958639</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7513483134573192</v>
+        <v>0.7513777732854701</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6281360621074692</v>
+        <v>-0.6286476577959724</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646277222221984</v>
+        <v>0.7646669762783269</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143393008058422</v>
+        <v>1.143537040874405</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.9641019525801</v>
+        <v>2.95815946184781</v>
       </c>
       <c r="E19" t="n">
-        <v>105.7050550235136</v>
+        <v>106.0695621410307</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1173518618991753</v>
+        <v>0.1079101413440182</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4843829564519142</v>
+        <v>0.4846130560048412</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2422708320680254</v>
+        <v>0.2226727901918932</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170571387306</v>
+        <v>0.7178492387816372</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6912685426140345</v>
+        <v>0.6923854174881561</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.559642543034034</v>
+        <v>2.559031705754179</v>
       </c>
       <c r="E20" t="n">
-        <v>141.9136881803325</v>
+        <v>140.8436463389792</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.335666721348072</v>
+        <v>-0.3346536395926935</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7843441486225612</v>
+        <v>0.7842763148250534</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.42795846942641</v>
+        <v>-0.4267037436510419</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7331318686570408</v>
+        <v>0.7330745528566429</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144439755466729</v>
+        <v>1.144291841752433</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.0787388966037</v>
+        <v>566.7658517070221</v>
       </c>
       <c r="E2" t="n">
-        <v>15513.91948997482</v>
+        <v>15538.9835799124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6217095170600178</v>
+        <v>0.6230854901104925</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5024356443247437</v>
+        <v>0.5023829293197475</v>
       </c>
       <c r="H2" t="n">
-        <v>1.237391343712435</v>
+        <v>1.240260076022453</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.1116794272941</v>
+        <v>222.2645016548149</v>
       </c>
       <c r="E3" t="n">
-        <v>6496.731609067771</v>
+        <v>6480.101567042692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2494253705986393</v>
+        <v>0.2490361193090049</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6021901171345884</v>
+        <v>0.6022010753533102</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4141970509006099</v>
+        <v>0.4135431328529194</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906916702250682</v>
+        <v>0.8907426650689023</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06753118987904</v>
+        <v>1.067723761024062</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.10974748099303</v>
+        <v>36.98827704512574</v>
       </c>
       <c r="E4" t="n">
-        <v>2233.164848853095</v>
+        <v>2248.144143500798</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7744862047081169</v>
+        <v>0.7665462098472597</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116546407370324</v>
+        <v>1.116735462345519</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6936444375224644</v>
+        <v>0.6864170035733046</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.47340982011676</v>
+        <v>0.4735524632855084</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0520432613327</v>
+        <v>1.052648882293967</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.59629219020186</v>
+        <v>36.65815069233209</v>
       </c>
       <c r="E5" t="n">
-        <v>444.6407889910653</v>
+        <v>443.9151174214174</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3490410430936187</v>
+        <v>-0.3475406028128432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5656085717431806</v>
+        <v>0.5655444519461287</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6171070604851154</v>
+        <v>-0.614523936388909</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7369323186609389</v>
+        <v>0.7367901602224809</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8295893035005296</v>
+        <v>0.8294222654550378</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.63530851259105</v>
+        <v>10.70902502655492</v>
       </c>
       <c r="E6" t="n">
-        <v>240.1044950229358</v>
+        <v>243.673727347538</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3271405864372909</v>
+        <v>-0.3210549111220211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7199275015478341</v>
+        <v>0.7194700830386538</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4544076809594622</v>
+        <v>-0.4462380280859744</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7513819589781783</v>
+        <v>0.7510805264548271</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076636465874714</v>
+        <v>1.075633619694986</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.46903644485002</v>
+        <v>10.49181892908708</v>
       </c>
       <c r="E7" t="n">
-        <v>1403.909896438421</v>
+        <v>1417.341699233821</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5158822155756835</v>
+        <v>-0.5154379333672071</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8099489356967926</v>
+        <v>0.8099989114899693</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6369317778433453</v>
+        <v>-0.6363439827580436</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6757543084862988</v>
+        <v>0.6757934163461783</v>
       </c>
       <c r="N7" t="n">
-        <v>1.089346444929455</v>
+        <v>1.089591026458023</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.428645749869078</v>
+        <v>9.456516306331842</v>
       </c>
       <c r="E8" t="n">
-        <v>484.6638512224642</v>
+        <v>488.0546119290651</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.365961368987834</v>
+        <v>-0.3633528493715977</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176535314644173</v>
+        <v>1.176352898933633</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3110500504598233</v>
+        <v>-0.3088808211387739</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395586480144026</v>
+        <v>0.7394624908176659</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731797647057568</v>
+        <v>1.7314856734959</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.281180427112619</v>
+        <v>7.283318349711405</v>
       </c>
       <c r="E9" t="n">
-        <v>226.8271865872634</v>
+        <v>226.8618498974971</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4088845392129115</v>
+        <v>0.4100750966758369</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4835788390912433</v>
+        <v>0.483533356743911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8455385268331845</v>
+        <v>0.8480802636601158</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6791644959750578</v>
+        <v>0.6791000646138861</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536749178235672</v>
+        <v>0.6536200070579347</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.748111458623623</v>
+        <v>6.761893642870032</v>
       </c>
       <c r="E10" t="n">
-        <v>275.6199205017251</v>
+        <v>275.9079126850893</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2603677252564541</v>
+        <v>-0.2577048300863667</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9649548627194603</v>
+        <v>0.9648060908694359</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2698237350943848</v>
+        <v>-0.2671053100982558</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.71419122123187</v>
+        <v>0.7140766662130914</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371642915114935</v>
+        <v>1.371355348086766</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.521901885897186</v>
+        <v>6.515960842802135</v>
       </c>
       <c r="E11" t="n">
-        <v>557.3048655083566</v>
+        <v>561.2517796769536</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9294844653678798</v>
+        <v>0.9297825912928859</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8277278560203283</v>
+        <v>0.8277191591654924</v>
       </c>
       <c r="H11" t="n">
-        <v>1.122934861509666</v>
+        <v>1.123306837829263</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6645109046800233</v>
+        <v>0.6644795998752154</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094735599764526</v>
+        <v>1.094787389444279</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.293697843487706</v>
+        <v>6.310067290582637</v>
       </c>
       <c r="E12" t="n">
-        <v>147.6834775535888</v>
+        <v>146.973310446876</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2803007812210765</v>
+        <v>-0.2766961904680564</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6631398924116469</v>
+        <v>0.6629108863827258</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4226872556282266</v>
+        <v>-0.4173957558275914</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891225490748726</v>
+        <v>0.7889325892489113</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041523721901561</v>
+        <v>1.041022637340351</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.63865438984447</v>
+        <v>4.636103632642828</v>
       </c>
       <c r="E13" t="n">
-        <v>270.4839167630265</v>
+        <v>274.5136134815581</v>
       </c>
       <c r="F13" t="n">
-        <v>1.716087272244886</v>
+        <v>1.723913504479288</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8669722653142872</v>
+        <v>0.8668215352977922</v>
       </c>
       <c r="H13" t="n">
-        <v>1.979402733976485</v>
+        <v>1.988775583300484</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.604131814266207</v>
+        <v>0.6040071102155709</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042452965825556</v>
+        <v>1.042165925734737</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.517700381286635</v>
+        <v>4.517039217583304</v>
       </c>
       <c r="E14" t="n">
-        <v>139.3284661866222</v>
+        <v>138.8731257366147</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4134125111970282</v>
+        <v>-0.4140282642687257</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8564999916496132</v>
+        <v>0.8565405500079426</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4826766085552417</v>
+        <v>-0.4833726368995449</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.76055693002139</v>
+        <v>0.7606111298875377</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296518293577396</v>
+        <v>1.296808146762055</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.060057913169937</v>
+        <v>4.075866272761591</v>
       </c>
       <c r="E15" t="n">
-        <v>327.0493000510694</v>
+        <v>326.5515423142537</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05339478586214819</v>
+        <v>-0.04805672087573953</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966571745116849</v>
+        <v>0.7963758145257916</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06702354233472735</v>
+        <v>-0.06034427464921859</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7179313346349234</v>
+        <v>0.7177407312790247</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138345089573284</v>
+        <v>1.137760314158435</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.962367154339503</v>
+        <v>3.955324584986753</v>
       </c>
       <c r="E16" t="n">
-        <v>198.1553018927156</v>
+        <v>198.9546992689867</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4416437325945946</v>
+        <v>0.4443673415536176</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9640887573992107</v>
+        <v>0.9639632243573716</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4580944743988113</v>
+        <v>0.4609795584783394</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5160565966103917</v>
+        <v>0.5159441518664352</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902250538821425</v>
+        <v>0.9899842514452819</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.323924602784666</v>
+        <v>3.328988148291044</v>
       </c>
       <c r="E17" t="n">
-        <v>107.9707803090375</v>
+        <v>107.9072027592894</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2290646080947427</v>
+        <v>-0.2272268098392293</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7591565619684604</v>
+        <v>0.7589773178209217</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3017356624051145</v>
+        <v>-0.299385507977516</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245943432732118</v>
+        <v>0.7245214223407672</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09482787830544</v>
+        <v>1.094574066393103</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.112540602296107</v>
+        <v>3.118063737912202</v>
       </c>
       <c r="E18" t="n">
-        <v>78.21870470960552</v>
+        <v>77.99292311972808</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4723518772958639</v>
+        <v>-0.4710622832587276</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7513777732854701</v>
+        <v>0.7512853393483612</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6286476577959724</v>
+        <v>-0.6270084861063716</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646669762783269</v>
+        <v>0.764575370963833</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143537040874405</v>
+        <v>1.14337934971188</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.95815946184781</v>
+        <v>2.953846585508366</v>
       </c>
       <c r="E19" t="n">
-        <v>106.0695621410307</v>
+        <v>106.8475917989687</v>
       </c>
       <c r="F19" t="n">
         <v>0.1079101413440182</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178492387816372</v>
+        <v>0.7178694707984518</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6923854174881561</v>
+        <v>0.6924775858273601</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.559031705754179</v>
+        <v>2.567741251490446</v>
       </c>
       <c r="E20" t="n">
-        <v>140.8436463389792</v>
+        <v>141.3257185251632</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3346536395926935</v>
+        <v>-0.3321191046191277</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7842763148250534</v>
+        <v>0.7841153423576658</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4267037436510419</v>
+        <v>-0.4235589927631274</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7330745528566429</v>
+        <v>0.732930084159553</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144291841752433</v>
+        <v>1.143951536417004</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.7658517070221</v>
+        <v>566.9135279420477</v>
       </c>
       <c r="E2" t="n">
-        <v>15538.9835799124</v>
+        <v>15433.42824373891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6230854901104925</v>
+        <v>0.6223905917943915</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5023829293197475</v>
+        <v>0.502409429993714</v>
       </c>
       <c r="H2" t="n">
-        <v>1.240260076022453</v>
+        <v>1.238811524302358</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.2645016548149</v>
+        <v>222.0494913473746</v>
       </c>
       <c r="E3" t="n">
-        <v>6480.101567042692</v>
+        <v>6406.561093228773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2490361193090049</v>
+        <v>0.2458584656474316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022010753533102</v>
+        <v>0.602294719100931</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4135431328529194</v>
+        <v>0.4082029243331806</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907426650689023</v>
+        <v>0.8908523910819808</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067723761024062</v>
+        <v>1.067965007451846</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.98827704512574</v>
+        <v>37.14165037795622</v>
       </c>
       <c r="E4" t="n">
-        <v>2248.144143500798</v>
+        <v>2255.257625376516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7665462098472597</v>
+        <v>0.7668912261261824</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116735462345519</v>
+        <v>1.116726998727126</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6864170035733046</v>
+        <v>0.6867311590033239</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735524632855084</v>
+        <v>0.4735580764749741</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052648882293967</v>
+        <v>1.052597857232705</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.65815069233209</v>
+        <v>36.73232779524347</v>
       </c>
       <c r="E5" t="n">
-        <v>443.9151174214174</v>
+        <v>450.2623215120407</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3475406028128432</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367901602224809</v>
+        <v>0.7367735139547054</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8294222654550378</v>
+        <v>0.8293597776680874</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.70902502655492</v>
+        <v>10.68464998623574</v>
       </c>
       <c r="E6" t="n">
-        <v>243.673727347538</v>
+        <v>244.5375426104955</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3210549111220211</v>
+        <v>-0.3262286830497974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194700830386538</v>
+        <v>0.719854139450458</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4462380280859744</v>
+        <v>-0.4531872016445481</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7510805264548271</v>
+        <v>0.7513357793164819</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075633619694986</v>
+        <v>1.076516758184599</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.49181892908708</v>
+        <v>10.40805572590726</v>
       </c>
       <c r="E7" t="n">
-        <v>1417.341699233821</v>
+        <v>1429.055306223737</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5154379333672071</v>
+        <v>-0.5239487878616402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8099989114899693</v>
+        <v>0.8091805621228303</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6363439827580436</v>
+        <v>-0.6475054053289369</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6757934163461783</v>
+        <v>0.6778518784933103</v>
       </c>
       <c r="N7" t="n">
-        <v>1.089591026458023</v>
+        <v>1.091748146690033</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.456516306331842</v>
+        <v>9.474169652039265</v>
       </c>
       <c r="E8" t="n">
-        <v>488.0546119290651</v>
+        <v>496.8745964438133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3633528493715977</v>
+        <v>-0.3652163741213189</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176352898933633</v>
+        <v>1.176482260537257</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3088808211387739</v>
+        <v>-0.3104308380770125</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394624908176659</v>
+        <v>0.7395311218880464</v>
       </c>
       <c r="N8" t="n">
-        <v>1.7314856734959</v>
+        <v>1.73174545316036</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.283318349711405</v>
+        <v>7.293085126499318</v>
       </c>
       <c r="E9" t="n">
-        <v>226.8618498974971</v>
+        <v>226.8028017143813</v>
       </c>
       <c r="F9" t="n">
         <v>0.4100750966758369</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6791000646138861</v>
+        <v>0.6791094006573383</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536200070579347</v>
+        <v>0.653594515732511</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.761893642870032</v>
+        <v>6.776626769420204</v>
       </c>
       <c r="E10" t="n">
-        <v>275.9079126850893</v>
+        <v>275.8090850082694</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2577048300863667</v>
+        <v>-0.2585460247437544</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9648060908694359</v>
+        <v>0.9648521193069972</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2671053100982558</v>
+        <v>-0.2679644057054614</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7140766662130914</v>
+        <v>0.7141118671617439</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371355348086766</v>
+        <v>1.371416035049155</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.515960842802135</v>
+        <v>6.521184228560358</v>
       </c>
       <c r="E11" t="n">
-        <v>561.2517796769536</v>
+        <v>561.7354472004282</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9297825912928859</v>
+        <v>0.9262059049548113</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8277191591654924</v>
+        <v>0.8278247586699232</v>
       </c>
       <c r="H11" t="n">
-        <v>1.123306837829263</v>
+        <v>1.118842961936725</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6644795998752154</v>
+        <v>0.664545464297956</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094787389444279</v>
+        <v>1.094977832351854</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.310067290582637</v>
+        <v>6.311751698477576</v>
       </c>
       <c r="E12" t="n">
-        <v>146.973310446876</v>
+        <v>145.3574892062674</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2766961904680564</v>
+        <v>-0.2795423260112724</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6629108863827258</v>
+        <v>0.6630895803534602</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4173957558275914</v>
+        <v>-0.4215755069809153</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889325892489113</v>
+        <v>0.7890846498895872</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041022637340351</v>
+        <v>1.041449021697682</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.636103632642828</v>
+        <v>4.63916246484619</v>
       </c>
       <c r="E13" t="n">
-        <v>274.5136134815581</v>
+        <v>272.7656440165482</v>
       </c>
       <c r="F13" t="n">
-        <v>1.723913504479288</v>
+        <v>1.714522758949518</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8668215352977922</v>
+        <v>0.8670031604547731</v>
       </c>
       <c r="H13" t="n">
-        <v>1.988775583300484</v>
+        <v>1.977527692113823</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040071102155709</v>
+        <v>0.6041371879262977</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042165925734737</v>
+        <v>1.042553781856588</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.517039217583304</v>
+        <v>4.521431061685702</v>
       </c>
       <c r="E14" t="n">
-        <v>138.8731257366147</v>
+        <v>137.967520400609</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4140282642687257</v>
+        <v>-0.4146438418897163</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8565405500079426</v>
+        <v>0.8565819682624118</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4833726368995449</v>
+        <v>-0.4840679085631781</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7606111298875377</v>
+        <v>0.7606435328222658</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296808146762055</v>
+        <v>1.296857693334146</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.075866272761591</v>
+        <v>4.088247578416525</v>
       </c>
       <c r="E15" t="n">
-        <v>326.5515423142537</v>
+        <v>320.8996692341292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04805672087573953</v>
+        <v>-0.04719498058693072</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7963758145257916</v>
+        <v>0.7963328816307764</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06034427464921859</v>
+        <v>-0.05926539224436158</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7177407312790247</v>
+        <v>0.7177126405139473</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137760314158435</v>
+        <v>1.13759444206781</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.955324584986753</v>
+        <v>3.960408173344015</v>
       </c>
       <c r="E16" t="n">
-        <v>198.9546992689867</v>
+        <v>198.4400107179984</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4443673415536176</v>
+        <v>0.4362007006651876</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9639632243573716</v>
+        <v>0.9643467035815642</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4609795584783394</v>
+        <v>0.4523276732788602</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159441518664352</v>
+        <v>0.5161213880978446</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899842514452819</v>
+        <v>0.9906660375907451</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.328988148291044</v>
+        <v>3.326723349727502</v>
       </c>
       <c r="E17" t="n">
-        <v>107.9072027592894</v>
+        <v>108.0114559793033</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2272268098392293</v>
+        <v>-0.2299830619848606</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7589773178209217</v>
+        <v>0.7592479412697257</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.299385507977516</v>
+        <v>-0.302909036012991</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245214223407672</v>
+        <v>0.7245735442708771</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094574066393103</v>
+        <v>1.094985362422547</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.118063737912202</v>
+        <v>3.119498018677228</v>
       </c>
       <c r="E18" t="n">
-        <v>77.99292311972808</v>
+        <v>77.74603717943769</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4710622832587276</v>
+        <v>-0.4723518772958639</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7512853393483612</v>
+        <v>0.7513777732854701</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6270084861063716</v>
+        <v>-0.6286476577959724</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764575370963833</v>
+        <v>0.7646743268000895</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14337934971188</v>
+        <v>1.143607700529837</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.953846585508366</v>
+        <v>2.943157857042891</v>
       </c>
       <c r="E19" t="n">
-        <v>106.8475917989687</v>
+        <v>106.9891796617568</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1079101413440182</v>
+        <v>0.100372438189656</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4846130560048412</v>
+        <v>0.4848719656762882</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2226727901918932</v>
+        <v>0.2070081285265872</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7178694707984518</v>
+        <v>0.7183626491929582</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6924775858273601</v>
+        <v>0.6932869667413959</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.567741251490446</v>
+        <v>2.569354951577375</v>
       </c>
       <c r="E20" t="n">
-        <v>141.3257185251632</v>
+        <v>140.6159129158891</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3321191046191277</v>
+        <v>-0.3326262206779702</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7841153423576658</v>
+        <v>0.7841465523743212</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4235589927631274</v>
+        <v>-0.4241888454024438</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732930084159553</v>
+        <v>0.7329571367019869</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143951536417004</v>
+        <v>1.143978949181364</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-24.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.9135279420477</v>
+        <v>567.5004694938506</v>
       </c>
       <c r="E2" t="n">
-        <v>15433.42824373891</v>
+        <v>15386.41318883272</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6223905917943915</v>
+        <v>0.6248062833771784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.502409429993714</v>
+        <v>0.5023183730342174</v>
       </c>
       <c r="H2" t="n">
-        <v>1.238811524302358</v>
+        <v>1.243845172540836</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.0494913473746</v>
+        <v>222.4677086904826</v>
       </c>
       <c r="E3" t="n">
-        <v>6406.561093228773</v>
+        <v>6346.762377343494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2458584656474316</v>
+        <v>0.2500927350521673</v>
       </c>
       <c r="G3" t="n">
-        <v>0.602294719100931</v>
+        <v>0.6021715897169708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4082029243331806</v>
+        <v>0.4153180577146033</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908523910819808</v>
+        <v>0.8907415196621966</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067965007451846</v>
+        <v>1.067807322439623</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.14165037795622</v>
+        <v>37.11913083910717</v>
       </c>
       <c r="E4" t="n">
-        <v>2255.257625376516</v>
+        <v>2262.427732692731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7668912261261824</v>
+        <v>0.773450005635089</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116726998727126</v>
+        <v>1.116570401612148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6867311590033239</v>
+        <v>0.6927015121647072</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735580764749741</v>
+        <v>0.4733833559647743</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052597857232705</v>
+        <v>1.052252659390758</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.73232779524347</v>
+        <v>36.76493453436808</v>
       </c>
       <c r="E5" t="n">
-        <v>450.2623215120407</v>
+        <v>451.7133848071059</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3475406028128432</v>
+        <v>-0.3460392260542724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5655444519461287</v>
+        <v>0.5654868366231797</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.614523936388909</v>
+        <v>-0.6119315316350337</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367735139547054</v>
+        <v>0.7366563929761022</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8293597776680874</v>
+        <v>0.8292937620936305</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.68464998623574</v>
+        <v>10.69288734002986</v>
       </c>
       <c r="E6" t="n">
-        <v>244.5375426104955</v>
+        <v>244.7181557981423</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3262286830497974</v>
+        <v>-0.3222732346575625</v>
       </c>
       <c r="G6" t="n">
-        <v>0.719854139450458</v>
+        <v>0.7195556043405842</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4531872016445481</v>
+        <v>-0.4478781524506372</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7513357793164819</v>
+        <v>0.7511378253818384</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076516758184599</v>
+        <v>1.075981809347204</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.40805572590726</v>
+        <v>10.46556070147541</v>
       </c>
       <c r="E7" t="n">
-        <v>1429.055306223737</v>
+        <v>1442.068533610156</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5239487878616402</v>
+        <v>-0.5184568706594299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8091805621228303</v>
+        <v>0.8096750002585369</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6475054053289369</v>
+        <v>-0.6403271318663436</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6778518784933103</v>
+        <v>0.6767568301596867</v>
       </c>
       <c r="N7" t="n">
-        <v>1.091748146690033</v>
+        <v>1.090848187225644</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.474169652039265</v>
+        <v>9.474628971921444</v>
       </c>
       <c r="E8" t="n">
-        <v>496.8745964438133</v>
+        <v>491.6933446026362</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3652163741213189</v>
+        <v>-0.3622340236717833</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176482260537257</v>
+        <v>1.176277527262255</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3104308380770125</v>
+        <v>-0.3079494551892616</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7395311218880464</v>
+        <v>0.7394233679693879</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73174545316036</v>
+        <v>1.731505629828341</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.293085126499318</v>
+        <v>7.302861562870976</v>
       </c>
       <c r="E9" t="n">
-        <v>226.8028017143813</v>
+        <v>227.0429594371275</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4100750966758369</v>
+        <v>0.4153167878848762</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483533356743911</v>
+        <v>0.4833451483774713</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8480802636601158</v>
+        <v>0.8592551084438157</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6791094006573383</v>
+        <v>0.6788748071633266</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653594515732511</v>
+        <v>0.653232814113557</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.776626769420204</v>
+        <v>6.791793341057047</v>
       </c>
       <c r="E10" t="n">
-        <v>275.8090850082694</v>
+        <v>274.5096893922724</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2585460247437544</v>
+        <v>-0.2544778557449672</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9648521193069972</v>
+        <v>0.9646377932979709</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2679644057054614</v>
+        <v>-0.26380664070287</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7141118671617439</v>
+        <v>0.7139389227214575</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371416035049155</v>
+        <v>1.371027826044986</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.521184228560358</v>
+        <v>6.550857121156028</v>
       </c>
       <c r="E11" t="n">
-        <v>561.7354472004282</v>
+        <v>559.1439299088115</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9262059049548113</v>
+        <v>0.9411206253781268</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8278247586699232</v>
+        <v>0.8274025767786782</v>
       </c>
       <c r="H11" t="n">
-        <v>1.118842961936725</v>
+        <v>1.137439804746785</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664545464297956</v>
+        <v>0.6642785525830737</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094977832351854</v>
+        <v>1.09417814599548</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.311751698477576</v>
+        <v>6.313759972881294</v>
       </c>
       <c r="E12" t="n">
-        <v>145.3574892062674</v>
+        <v>144.1815971808396</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2795423260112724</v>
+        <v>-0.2780247658071355</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6630895803534602</v>
+        <v>0.6629923162277848</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4215755069809153</v>
+        <v>-0.4193483981669772</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890846498895872</v>
+        <v>0.7890124099322898</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041449021697682</v>
+        <v>1.041389670924582</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.63916246484619</v>
+        <v>4.653821457570217</v>
       </c>
       <c r="E13" t="n">
-        <v>272.7656440165482</v>
+        <v>270.6823447721852</v>
       </c>
       <c r="F13" t="n">
-        <v>1.714522758949518</v>
+        <v>1.728612174111085</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8670031604547731</v>
+        <v>0.8667340947707688</v>
       </c>
       <c r="H13" t="n">
-        <v>1.977527692113823</v>
+        <v>1.994397341168704</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6041371879262977</v>
+        <v>0.6039176601795534</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042553781856588</v>
+        <v>1.042040376405165</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.521431061685702</v>
+        <v>4.536033852903211</v>
       </c>
       <c r="E14" t="n">
-        <v>137.967520400609</v>
+        <v>137.5285687972252</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4146438418897163</v>
+        <v>-0.4109477460873996</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8565819682624118</v>
+        <v>0.8563463595824282</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4840679085631781</v>
+        <v>-0.4798849688434316</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7606435328222658</v>
+        <v>0.7604312335412098</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296857693334146</v>
+        <v>1.296374079694337</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.088247578416525</v>
+        <v>4.091575648260151</v>
       </c>
       <c r="E15" t="n">
-        <v>320.8996692341292</v>
+        <v>319.2252492155225</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04719498058693072</v>
+        <v>-0.04391843985402588</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7963328816307764</v>
+        <v>0.7961759413041197</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05926539224436158</v>
+        <v>-0.0551617269194148</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7177126405139473</v>
+        <v>0.7175858480141698</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13759444206781</v>
+        <v>1.137375454849785</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.960408173344015</v>
+        <v>3.976073009249739</v>
       </c>
       <c r="E16" t="n">
-        <v>198.4400107179984</v>
+        <v>197.221010411342</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4362007006651876</v>
+        <v>0.4539109406024837</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9643467035815642</v>
+        <v>0.9635419341593063</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4523276732788602</v>
+        <v>0.4710858183858107</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5161213880978446</v>
+        <v>0.5156944412111573</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9906660375907451</v>
+        <v>0.9891997704928728</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.326723349727502</v>
+        <v>3.346112041067541</v>
       </c>
       <c r="E17" t="n">
-        <v>108.0114559793033</v>
+        <v>108.1478480607318</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2299830619848606</v>
+        <v>-0.222074668129207</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7592479412697257</v>
+        <v>0.758500388359566</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.302909036012991</v>
+        <v>-0.2927812187538825</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245735442708771</v>
+        <v>0.7243958966289593</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094985362422547</v>
+        <v>1.093837292074749</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.119498018677228</v>
+        <v>3.128696186457062</v>
       </c>
       <c r="E18" t="n">
-        <v>77.74603717943769</v>
+        <v>77.41533816414261</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4723518772958639</v>
+        <v>-0.4693683961975755</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7513777732854701</v>
+        <v>0.7511721339576261</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6286476577959724</v>
+        <v>-0.6248479875373716</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646743268000895</v>
+        <v>0.7644545439286836</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143607700529837</v>
+        <v>1.14317329785864</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.943157857042891</v>
+        <v>2.953372317870728</v>
       </c>
       <c r="E19" t="n">
-        <v>106.9891796617568</v>
+        <v>106.9639351482041</v>
       </c>
       <c r="F19" t="n">
-        <v>0.100372438189656</v>
+        <v>0.1107403750832798</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4848719656762882</v>
+        <v>0.4845331067602686</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2070081285265872</v>
+        <v>0.2285506883600228</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7183626491929582</v>
+        <v>0.7176892552205711</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6932869667413959</v>
+        <v>0.692278489476631</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.569354951577375</v>
+        <v>2.576495695604073</v>
       </c>
       <c r="E20" t="n">
-        <v>140.6159129158891</v>
+        <v>140.7699667215292</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3326262206779702</v>
+        <v>-0.3290742158872906</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7841465523743212</v>
+        <v>0.7839384237555521</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4241888454024438</v>
+        <v>-0.4197704895122</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7329571367019869</v>
+        <v>0.7327546594514203</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143978949181364</v>
+        <v>1.143566637350039</v>
       </c>
     </row>
   </sheetData>
